--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129739257</v>
+        <v>129738278</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,42 +2490,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407574</v>
+        <v>407601</v>
       </c>
       <c r="R16" t="n">
-        <v>6839050</v>
+        <v>6838838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2572,22 +2564,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129739256</v>
+        <v>129739237</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>79695</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,42 +2587,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407082</v>
+        <v>407617</v>
       </c>
       <c r="R17" t="n">
-        <v>6838747</v>
+        <v>6839035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2689,10 +2673,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738266</v>
+        <v>129738187</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>79695</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,42 +2684,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407598</v>
+        <v>407437</v>
       </c>
       <c r="R18" t="n">
-        <v>6838839</v>
+        <v>6838840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2794,54 +2770,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738245</v>
+        <v>129738167</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407233</v>
+        <v>407714</v>
       </c>
       <c r="R19" t="n">
-        <v>6838838</v>
+        <v>6839244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2882,7 +2849,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2901,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129739265</v>
+        <v>129738159</v>
       </c>
       <c r="B20" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2912,21 +2878,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2902,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407615</v>
+        <v>407516</v>
       </c>
       <c r="R20" t="n">
-        <v>6839034</v>
+        <v>6839209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2986,54 +2952,63 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738278</v>
+        <v>129738245</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407601</v>
+        <v>407233</v>
       </c>
       <c r="R21" t="n">
         <v>6838838</v>
@@ -3077,6 +3052,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3095,10 +3071,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129739237</v>
+        <v>129739265</v>
       </c>
       <c r="B22" t="n">
-        <v>79694</v>
+        <v>78834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3106,21 +3082,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3130,10 +3106,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407617</v>
+        <v>407615</v>
       </c>
       <c r="R22" t="n">
-        <v>6839035</v>
+        <v>6839034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3192,10 +3168,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129738187</v>
+        <v>129739257</v>
       </c>
       <c r="B23" t="n">
-        <v>79694</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,34 +3179,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407437</v>
+        <v>407574</v>
       </c>
       <c r="R23" t="n">
-        <v>6838840</v>
+        <v>6839050</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3277,22 +3261,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738167</v>
+        <v>129738266</v>
       </c>
       <c r="B24" t="n">
-        <v>79694</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,34 +3284,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407714</v>
+        <v>407598</v>
       </c>
       <c r="R24" t="n">
-        <v>6839244</v>
+        <v>6838839</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3386,10 +3378,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129738159</v>
+        <v>129739256</v>
       </c>
       <c r="B25" t="n">
-        <v>79694</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,34 +3389,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407516</v>
+        <v>407082</v>
       </c>
       <c r="R25" t="n">
-        <v>6839209</v>
+        <v>6838747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,12 +3471,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3486,7 +3486,7 @@
         <v>129739291</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>129738154</v>
       </c>
       <c r="B27" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>129739233</v>
       </c>
       <c r="B28" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>129739272</v>
       </c>
       <c r="B29" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>129739266</v>
       </c>
       <c r="B30" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>129739227</v>
       </c>
       <c r="B31" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>129738155</v>
       </c>
       <c r="B32" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>129738179</v>
       </c>
       <c r="B33" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>129738197</v>
       </c>
       <c r="B34" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>129739248</v>
       </c>
       <c r="B35" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,54 +4453,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738246</v>
+        <v>129738287</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407154</v>
+        <v>407591</v>
       </c>
       <c r="R36" t="n">
-        <v>6838842</v>
+        <v>6838814</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4541,7 +4532,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4560,43 +4550,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129739270</v>
+        <v>129738283</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4604,10 +4588,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407283</v>
+        <v>407598</v>
       </c>
       <c r="R37" t="n">
-        <v>6839055</v>
+        <v>6838839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4642,6 +4626,11 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4655,12 +4644,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4670,7 +4659,7 @@
         <v>129738184</v>
       </c>
       <c r="B38" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4767,7 +4756,7 @@
         <v>129738149</v>
       </c>
       <c r="B39" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4864,7 +4853,7 @@
         <v>129738158</v>
       </c>
       <c r="B40" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4958,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738287</v>
+        <v>129739271</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4969,21 +4958,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4993,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407591</v>
+        <v>407647</v>
       </c>
       <c r="R41" t="n">
-        <v>6838814</v>
+        <v>6838874</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5043,49 +5032,55 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129738283</v>
+        <v>129738246</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5093,10 +5088,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407598</v>
+        <v>407154</v>
       </c>
       <c r="R42" t="n">
-        <v>6838839</v>
+        <v>6838842</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5129,11 +5124,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5161,45 +5151,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129739271</v>
+        <v>129739270</v>
       </c>
       <c r="B43" t="n">
-        <v>78832</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407647</v>
+        <v>407283</v>
       </c>
       <c r="R43" t="n">
-        <v>6838874</v>
+        <v>6839055</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5240,6 +5239,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5258,54 +5258,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738247</v>
+        <v>129738292</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>78742</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407158</v>
+        <v>407528</v>
       </c>
       <c r="R44" t="n">
-        <v>6838902</v>
+        <v>6839142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5346,7 +5337,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5365,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129739250</v>
+        <v>129738290</v>
       </c>
       <c r="B45" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,37 +5366,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407493</v>
+        <v>407575</v>
       </c>
       <c r="R45" t="n">
-        <v>6839112</v>
+        <v>6838839</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5447,19 +5434,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5469,7 +5455,7 @@
         <v>129739240</v>
       </c>
       <c r="B46" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5552,7 @@
         <v>129738186</v>
       </c>
       <c r="B47" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738290</v>
+        <v>129738204</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,34 +5657,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407575</v>
+        <v>407170</v>
       </c>
       <c r="R48" t="n">
-        <v>6838839</v>
+        <v>6838942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5757,40 +5751,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129738204</v>
+        <v>129738247</v>
       </c>
       <c r="B49" t="n">
-        <v>57732</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5800,10 +5795,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407170</v>
+        <v>407158</v>
       </c>
       <c r="R49" t="n">
-        <v>6838942</v>
+        <v>6838902</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5844,6 +5839,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5862,10 +5858,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129738292</v>
+        <v>129739250</v>
       </c>
       <c r="B50" t="n">
-        <v>78741</v>
+        <v>79666</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,34 +5869,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407528</v>
+        <v>407493</v>
       </c>
       <c r="R50" t="n">
-        <v>6839142</v>
+        <v>6839112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,18 +5940,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5962,7 +5962,7 @@
         <v>129738152</v>
       </c>
       <c r="B51" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>129739234</v>
       </c>
       <c r="B52" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>129738196</v>
       </c>
       <c r="B53" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6250,45 +6250,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738160</v>
+        <v>129738255</v>
       </c>
       <c r="B54" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407512</v>
+        <v>407645</v>
       </c>
       <c r="R54" t="n">
-        <v>6839214</v>
+        <v>6838797</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6329,6 +6338,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6347,10 +6357,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738291</v>
+        <v>129738198</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6358,34 +6368,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407574</v>
+        <v>407575</v>
       </c>
       <c r="R55" t="n">
-        <v>6838848</v>
+        <v>6838839</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,10 +6462,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738168</v>
+        <v>129738291</v>
       </c>
       <c r="B56" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6455,21 +6473,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6479,10 +6497,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407717</v>
+        <v>407574</v>
       </c>
       <c r="R56" t="n">
-        <v>6839236</v>
+        <v>6838848</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6541,10 +6559,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129739229</v>
+        <v>129738160</v>
       </c>
       <c r="B57" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6576,10 +6594,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407296</v>
+        <v>407512</v>
       </c>
       <c r="R57" t="n">
-        <v>6838974</v>
+        <v>6839214</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,22 +6644,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738198</v>
+        <v>129738168</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>79695</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6649,42 +6667,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407575</v>
+        <v>407717</v>
       </c>
       <c r="R58" t="n">
-        <v>6838839</v>
+        <v>6839236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6743,54 +6753,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738255</v>
+        <v>129739229</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407645</v>
+        <v>407296</v>
       </c>
       <c r="R59" t="n">
-        <v>6838797</v>
+        <v>6838974</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6831,29 +6832,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129739232</v>
+        <v>129738289</v>
       </c>
       <c r="B60" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6861,21 +6861,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407441</v>
+        <v>407581</v>
       </c>
       <c r="R60" t="n">
-        <v>6839017</v>
+        <v>6838815</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6935,22 +6935,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129739244</v>
+        <v>129738277</v>
       </c>
       <c r="B61" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6958,21 +6958,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407448</v>
+        <v>407593</v>
       </c>
       <c r="R61" t="n">
-        <v>6838869</v>
+        <v>6838795</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7032,22 +7032,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129738289</v>
+        <v>129739232</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407581</v>
+        <v>407441</v>
       </c>
       <c r="R62" t="n">
-        <v>6838815</v>
+        <v>6839017</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7129,22 +7129,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129738277</v>
+        <v>129739244</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407593</v>
+        <v>407448</v>
       </c>
       <c r="R63" t="n">
-        <v>6838795</v>
+        <v>6838869</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7226,12 +7226,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7241,7 +7241,7 @@
         <v>129739228</v>
       </c>
       <c r="B64" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>129738189</v>
       </c>
       <c r="B65" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>129739292</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>129738169</v>
       </c>
       <c r="B68" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>129739245</v>
       </c>
       <c r="B69" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>129739225</v>
       </c>
       <c r="B70" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7931,45 +7931,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129739264</v>
+        <v>129738257</v>
       </c>
       <c r="B71" t="n">
-        <v>78833</v>
+        <v>58106</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407129</v>
+        <v>407464</v>
       </c>
       <c r="R71" t="n">
-        <v>6838913</v>
+        <v>6839159</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8016,22 +8024,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129738193</v>
+        <v>129739264</v>
       </c>
       <c r="B72" t="n">
-        <v>79665</v>
+        <v>78834</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8039,21 +8047,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8063,10 +8071,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407714</v>
+        <v>407129</v>
       </c>
       <c r="R72" t="n">
-        <v>6839244</v>
+        <v>6838913</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8113,65 +8121,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129738257</v>
+        <v>129738193</v>
       </c>
       <c r="B73" t="n">
-        <v>58105</v>
+        <v>79666</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407464</v>
+        <v>407714</v>
       </c>
       <c r="R73" t="n">
-        <v>6839159</v>
+        <v>6839244</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8233,7 +8233,7 @@
         <v>129738199</v>
       </c>
       <c r="B74" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8335,10 +8335,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738275</v>
+        <v>129738147</v>
       </c>
       <c r="B75" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407608</v>
+        <v>407190</v>
       </c>
       <c r="R75" t="n">
-        <v>6839252</v>
+        <v>6838950</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738285</v>
+        <v>129738176</v>
       </c>
       <c r="B76" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8443,21 +8443,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407587</v>
+        <v>407519</v>
       </c>
       <c r="R76" t="n">
-        <v>6838806</v>
+        <v>6838831</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,10 +8529,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738147</v>
+        <v>129738171</v>
       </c>
       <c r="B77" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407190</v>
+        <v>407620</v>
       </c>
       <c r="R77" t="n">
-        <v>6838950</v>
+        <v>6838898</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,10 +8626,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738176</v>
+        <v>129738181</v>
       </c>
       <c r="B78" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407519</v>
+        <v>407467</v>
       </c>
       <c r="R78" t="n">
-        <v>6838831</v>
+        <v>6838834</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738171</v>
+        <v>129738275</v>
       </c>
       <c r="B79" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8734,21 +8734,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407620</v>
+        <v>407608</v>
       </c>
       <c r="R79" t="n">
-        <v>6838898</v>
+        <v>6839252</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738181</v>
+        <v>129738285</v>
       </c>
       <c r="B80" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8831,21 +8831,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407467</v>
+        <v>407587</v>
       </c>
       <c r="R80" t="n">
-        <v>6838834</v>
+        <v>6838806</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,45 +8917,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B81" t="n">
-        <v>79665</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R81" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8996,6 +9005,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9014,54 +9024,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738244</v>
+        <v>129738194</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79666</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407231</v>
+        <v>407549</v>
       </c>
       <c r="R82" t="n">
-        <v>6838827</v>
+        <v>6838809</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9102,7 +9103,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9124,7 +9124,7 @@
         <v>129738174</v>
       </c>
       <c r="B83" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>129738143</v>
       </c>
       <c r="B84" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>129738165</v>
       </c>
       <c r="B85" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>129739238</v>
       </c>
       <c r="B86" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>129738148</v>
       </c>
       <c r="B87" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>129739259</v>
       </c>
       <c r="B88" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>129739267</v>
       </c>
       <c r="B89" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>129739255</v>
       </c>
       <c r="B90" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739246</v>
+        <v>129739258</v>
       </c>
       <c r="B91" t="n">
-        <v>79694</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9916,34 +9916,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407427</v>
+        <v>407616</v>
       </c>
       <c r="R91" t="n">
-        <v>6838886</v>
+        <v>6838890</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10002,10 +10010,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129739239</v>
+        <v>129739246</v>
       </c>
       <c r="B92" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10037,10 +10045,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407614</v>
+        <v>407427</v>
       </c>
       <c r="R92" t="n">
-        <v>6838900</v>
+        <v>6838886</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10099,10 +10107,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129738170</v>
+        <v>129739239</v>
       </c>
       <c r="B93" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10134,10 +10142,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407660</v>
+        <v>407614</v>
       </c>
       <c r="R93" t="n">
-        <v>6838791</v>
+        <v>6838900</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10184,22 +10192,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129738188</v>
+        <v>129738170</v>
       </c>
       <c r="B94" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10231,10 +10239,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407408</v>
+        <v>407660</v>
       </c>
       <c r="R94" t="n">
-        <v>6838841</v>
+        <v>6838791</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10293,10 +10301,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129739258</v>
+        <v>129738188</v>
       </c>
       <c r="B95" t="n">
-        <v>57735</v>
+        <v>79695</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10304,42 +10312,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407616</v>
+        <v>407408</v>
       </c>
       <c r="R95" t="n">
-        <v>6838890</v>
+        <v>6838841</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10386,12 +10386,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10505,54 +10505,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129738250</v>
+        <v>129739252</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79666</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407525</v>
+        <v>407615</v>
       </c>
       <c r="R97" t="n">
-        <v>6839244</v>
+        <v>6839041</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10593,29 +10584,28 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129739252</v>
+        <v>129738191</v>
       </c>
       <c r="B98" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10647,10 +10637,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407615</v>
+        <v>407474</v>
       </c>
       <c r="R98" t="n">
-        <v>6839041</v>
+        <v>6839108</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10697,22 +10687,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129738191</v>
+        <v>129739251</v>
       </c>
       <c r="B99" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10744,10 +10734,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407474</v>
+        <v>407563</v>
       </c>
       <c r="R99" t="n">
-        <v>6839108</v>
+        <v>6839056</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10794,22 +10784,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129739251</v>
+        <v>129739289</v>
       </c>
       <c r="B100" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10817,21 +10807,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10841,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407563</v>
+        <v>407649</v>
       </c>
       <c r="R100" t="n">
-        <v>6839056</v>
+        <v>6839041</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10906,7 +10896,7 @@
         <v>129738144</v>
       </c>
       <c r="B101" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11003,7 +10993,7 @@
         <v>129738185</v>
       </c>
       <c r="B102" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11097,10 +11087,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129739289</v>
+        <v>129738172</v>
       </c>
       <c r="B103" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11108,21 +11098,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11132,10 +11122,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407649</v>
+        <v>407585</v>
       </c>
       <c r="R103" t="n">
-        <v>6839041</v>
+        <v>6838872</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11182,22 +11172,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129738172</v>
+        <v>129739242</v>
       </c>
       <c r="B104" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11229,10 +11219,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407585</v>
+        <v>407515</v>
       </c>
       <c r="R104" t="n">
-        <v>6838872</v>
+        <v>6838875</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11279,57 +11269,66 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129739242</v>
+        <v>129738250</v>
       </c>
       <c r="B105" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407515</v>
+        <v>407525</v>
       </c>
       <c r="R105" t="n">
-        <v>6838875</v>
+        <v>6839244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11370,18 +11369,19 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
         <v>129739273</v>
       </c>
       <c r="B106" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>129738173</v>
       </c>
       <c r="B107" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>129738182</v>
       </c>
       <c r="B108" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>129738180</v>
       </c>
       <c r="B109" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11776,10 +11776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738276</v>
+        <v>129738190</v>
       </c>
       <c r="B110" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407607</v>
+        <v>407412</v>
       </c>
       <c r="R110" t="n">
-        <v>6838798</v>
+        <v>6838831</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11873,10 +11873,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129738190</v>
+        <v>129738175</v>
       </c>
       <c r="B111" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>407412</v>
+        <v>407547</v>
       </c>
       <c r="R111" t="n">
-        <v>6838831</v>
+        <v>6838816</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,10 +11970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129738175</v>
+        <v>129738268</v>
       </c>
       <c r="B112" t="n">
-        <v>79694</v>
+        <v>57736</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11981,34 +11981,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>407547</v>
+        <v>407593</v>
       </c>
       <c r="R112" t="n">
-        <v>6838816</v>
+        <v>6838811</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12067,10 +12075,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129738268</v>
+        <v>129738276</v>
       </c>
       <c r="B113" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12078,42 +12086,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>407593</v>
+        <v>407607</v>
       </c>
       <c r="R113" t="n">
-        <v>6838811</v>
+        <v>6838798</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12282,7 +12282,7 @@
         <v>129739243</v>
       </c>
       <c r="B115" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12376,10 +12376,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129738280</v>
+        <v>129739224</v>
       </c>
       <c r="B116" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12387,37 +12387,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407623</v>
+        <v>407121</v>
       </c>
       <c r="R116" t="n">
-        <v>6838894</v>
+        <v>6838895</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12452,40 +12449,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129739224</v>
+        <v>129738145</v>
       </c>
       <c r="B117" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12517,10 +12508,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407121</v>
+        <v>407194</v>
       </c>
       <c r="R117" t="n">
-        <v>6838895</v>
+        <v>6838873</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12567,22 +12558,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129739290</v>
+        <v>129738192</v>
       </c>
       <c r="B118" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12590,37 +12581,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407657</v>
+        <v>407464</v>
       </c>
       <c r="R118" t="n">
-        <v>6839033</v>
+        <v>6839157</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12655,40 +12643,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129738282</v>
+        <v>129738280</v>
       </c>
       <c r="B119" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12714,16 +12696,19 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407588</v>
+        <v>407623</v>
       </c>
       <c r="R119" t="n">
-        <v>6838831</v>
+        <v>6838894</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12769,6 +12754,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12787,10 +12773,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738145</v>
+        <v>129739290</v>
       </c>
       <c r="B120" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12798,34 +12784,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407194</v>
+        <v>407657</v>
       </c>
       <c r="R120" t="n">
-        <v>6838873</v>
+        <v>6839033</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12860,34 +12849,40 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129738192</v>
+        <v>129738282</v>
       </c>
       <c r="B121" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12895,21 +12890,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12919,10 +12914,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407464</v>
+        <v>407588</v>
       </c>
       <c r="R121" t="n">
-        <v>6839157</v>
+        <v>6838831</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12955,6 +12950,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12981,10 +12981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739249</v>
+        <v>129738279</v>
       </c>
       <c r="B122" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407437</v>
+        <v>407617</v>
       </c>
       <c r="R122" t="n">
-        <v>6839060</v>
+        <v>6838855</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13066,22 +13066,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129739286</v>
+        <v>129738288</v>
       </c>
       <c r="B123" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407570</v>
+        <v>407592</v>
       </c>
       <c r="R123" t="n">
-        <v>6839041</v>
+        <v>6838822</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13163,22 +13163,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129738279</v>
+        <v>129739286</v>
       </c>
       <c r="B124" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407617</v>
+        <v>407570</v>
       </c>
       <c r="R124" t="n">
-        <v>6838855</v>
+        <v>6839041</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13260,22 +13260,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738288</v>
+        <v>129738146</v>
       </c>
       <c r="B125" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407592</v>
+        <v>407163</v>
       </c>
       <c r="R125" t="n">
-        <v>6838822</v>
+        <v>6838891</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,10 +13369,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129738146</v>
+        <v>129739241</v>
       </c>
       <c r="B126" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407163</v>
+        <v>407524</v>
       </c>
       <c r="R126" t="n">
-        <v>6838891</v>
+        <v>6838914</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13454,22 +13454,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739241</v>
+        <v>129739249</v>
       </c>
       <c r="B127" t="n">
-        <v>79694</v>
+        <v>79666</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407524</v>
+        <v>407437</v>
       </c>
       <c r="R127" t="n">
-        <v>6838914</v>
+        <v>6839060</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13563,10 +13563,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129738242</v>
+        <v>129739254</v>
       </c>
       <c r="B128" t="n">
-        <v>78833</v>
+        <v>79666</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13574,21 +13574,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13598,10 +13598,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407719</v>
+        <v>407418</v>
       </c>
       <c r="R128" t="n">
-        <v>6839222</v>
+        <v>6838867</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,22 +13648,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129739254</v>
+        <v>129739268</v>
       </c>
       <c r="B129" t="n">
-        <v>79665</v>
+        <v>78834</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,34 +13671,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407418</v>
+        <v>407573</v>
       </c>
       <c r="R129" t="n">
-        <v>6838867</v>
+        <v>6838884</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13739,6 +13742,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13757,10 +13761,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129739268</v>
+        <v>129739287</v>
       </c>
       <c r="B130" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,37 +13772,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407573</v>
+        <v>407622</v>
       </c>
       <c r="R130" t="n">
-        <v>6838884</v>
+        <v>6839045</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13839,7 +13840,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13858,10 +13858,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738157</v>
+        <v>129738281</v>
       </c>
       <c r="B131" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13869,21 +13869,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13893,10 +13893,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407535</v>
+        <v>407587</v>
       </c>
       <c r="R131" t="n">
-        <v>6839193</v>
+        <v>6838872</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13955,10 +13955,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129739287</v>
+        <v>129738157</v>
       </c>
       <c r="B132" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13966,21 +13966,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13990,10 +13990,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407622</v>
+        <v>407535</v>
       </c>
       <c r="R132" t="n">
-        <v>6839045</v>
+        <v>6839193</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14040,22 +14040,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738281</v>
+        <v>129738177</v>
       </c>
       <c r="B133" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14063,21 +14063,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14087,10 +14087,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407587</v>
+        <v>407476</v>
       </c>
       <c r="R133" t="n">
-        <v>6838872</v>
+        <v>6838854</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14149,10 +14149,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738177</v>
+        <v>129738156</v>
       </c>
       <c r="B134" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407476</v>
+        <v>407477</v>
       </c>
       <c r="R134" t="n">
-        <v>6838854</v>
+        <v>6839132</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14246,10 +14246,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129738156</v>
+        <v>129739230</v>
       </c>
       <c r="B135" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407477</v>
+        <v>407404</v>
       </c>
       <c r="R135" t="n">
-        <v>6839132</v>
+        <v>6839005</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14331,22 +14331,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129739230</v>
+        <v>129738151</v>
       </c>
       <c r="B136" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14378,10 +14378,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407404</v>
+        <v>407378</v>
       </c>
       <c r="R136" t="n">
-        <v>6839005</v>
+        <v>6839143</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14428,22 +14428,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129738151</v>
+        <v>129739235</v>
       </c>
       <c r="B137" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407378</v>
+        <v>407604</v>
       </c>
       <c r="R137" t="n">
-        <v>6839143</v>
+        <v>6839024</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14525,22 +14525,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129739235</v>
+        <v>129739231</v>
       </c>
       <c r="B138" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14572,10 +14572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407604</v>
+        <v>407422</v>
       </c>
       <c r="R138" t="n">
-        <v>6839024</v>
+        <v>6839006</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14634,45 +14634,54 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129739231</v>
+        <v>129738248</v>
       </c>
       <c r="B139" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407422</v>
+        <v>407481</v>
       </c>
       <c r="R139" t="n">
-        <v>6839006</v>
+        <v>6839152</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14713,25 +14722,26 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129738248</v>
+        <v>129738256</v>
       </c>
       <c r="B140" t="n">
         <v>8450</v>
@@ -14775,10 +14785,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407481</v>
+        <v>407616</v>
       </c>
       <c r="R140" t="n">
-        <v>6839152</v>
+        <v>6838794</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14838,54 +14848,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129738256</v>
+        <v>129738242</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>78834</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407616</v>
+        <v>407719</v>
       </c>
       <c r="R141" t="n">
-        <v>6838794</v>
+        <v>6839222</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14926,7 +14927,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14945,10 +14945,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129739253</v>
+        <v>129738150</v>
       </c>
       <c r="B142" t="n">
-        <v>79665</v>
+        <v>79695</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,37 +14956,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407589</v>
+        <v>407203</v>
       </c>
       <c r="R142" t="n">
-        <v>6838889</v>
+        <v>6839015</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15027,29 +15024,28 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738195</v>
+        <v>129739253</v>
       </c>
       <c r="B143" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15075,16 +15071,19 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407479</v>
+        <v>407589</v>
       </c>
       <c r="R143" t="n">
-        <v>6838852</v>
+        <v>6838889</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15125,28 +15124,29 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738201</v>
+        <v>129738195</v>
       </c>
       <c r="B144" t="n">
-        <v>57895</v>
+        <v>79666</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15154,42 +15154,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407530</v>
+        <v>407479</v>
       </c>
       <c r="R144" t="n">
-        <v>6839196</v>
+        <v>6838852</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15248,10 +15240,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738150</v>
+        <v>129738286</v>
       </c>
       <c r="B145" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15259,21 +15251,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15283,10 +15275,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407203</v>
+        <v>407586</v>
       </c>
       <c r="R145" t="n">
-        <v>6839015</v>
+        <v>6838820</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15345,10 +15337,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129738286</v>
+        <v>129738284</v>
       </c>
       <c r="B146" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15380,10 +15372,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407586</v>
+        <v>407595</v>
       </c>
       <c r="R146" t="n">
-        <v>6838820</v>
+        <v>6838836</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15442,10 +15434,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738284</v>
+        <v>129738201</v>
       </c>
       <c r="B147" t="n">
-        <v>79075</v>
+        <v>57896</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15453,34 +15445,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407595</v>
+        <v>407530</v>
       </c>
       <c r="R147" t="n">
-        <v>6838836</v>
+        <v>6839196</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738164</v>
+        <v>129738274</v>
       </c>
       <c r="B148" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15550,21 +15550,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407666</v>
+        <v>407522</v>
       </c>
       <c r="R148" t="n">
-        <v>6839269</v>
+        <v>6839200</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129738153</v>
+        <v>129739288</v>
       </c>
       <c r="B149" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407474</v>
+        <v>407625</v>
       </c>
       <c r="R149" t="n">
-        <v>6839108</v>
+        <v>6839051</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15721,22 +15721,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129738166</v>
+        <v>129738164</v>
       </c>
       <c r="B150" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407704</v>
+        <v>407666</v>
       </c>
       <c r="R150" t="n">
-        <v>6839251</v>
+        <v>6839269</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738274</v>
+        <v>129738153</v>
       </c>
       <c r="B151" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407522</v>
+        <v>407474</v>
       </c>
       <c r="R151" t="n">
-        <v>6839200</v>
+        <v>6839108</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15927,10 +15927,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129739288</v>
+        <v>129738166</v>
       </c>
       <c r="B152" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15938,21 +15938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407625</v>
+        <v>407704</v>
       </c>
       <c r="R152" t="n">
-        <v>6839051</v>
+        <v>6839251</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16012,12 +16012,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
         <v>129739247</v>
       </c>
       <c r="B153" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -3483,10 +3483,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129739291</v>
+        <v>129739266</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,21 +3494,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407656</v>
+        <v>407649</v>
       </c>
       <c r="R26" t="n">
-        <v>6839031</v>
+        <v>6838875</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129739266</v>
+        <v>129739291</v>
       </c>
       <c r="B30" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407649</v>
+        <v>407656</v>
       </c>
       <c r="R30" t="n">
-        <v>6838875</v>
+        <v>6839031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738290</v>
+        <v>129739240</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407575</v>
+        <v>407581</v>
       </c>
       <c r="R45" t="n">
-        <v>6838839</v>
+        <v>6838885</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5440,19 +5440,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129739240</v>
+        <v>129738186</v>
       </c>
       <c r="B46" t="n">
         <v>79695</v>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407581</v>
+        <v>407479</v>
       </c>
       <c r="R46" t="n">
-        <v>6838885</v>
+        <v>6838810</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,22 +5537,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738186</v>
+        <v>129738204</v>
       </c>
       <c r="B47" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,34 +5560,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407479</v>
+        <v>407170</v>
       </c>
       <c r="R47" t="n">
-        <v>6838810</v>
+        <v>6838942</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5646,40 +5654,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738204</v>
+        <v>129738247</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5689,10 +5698,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407170</v>
+        <v>407158</v>
       </c>
       <c r="R48" t="n">
-        <v>6838942</v>
+        <v>6838902</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5733,6 +5742,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5751,54 +5761,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129738247</v>
+        <v>129738290</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407158</v>
+        <v>407575</v>
       </c>
       <c r="R49" t="n">
-        <v>6838902</v>
+        <v>6838839</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5839,7 +5840,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6250,54 +6250,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738255</v>
+        <v>129738291</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407645</v>
+        <v>407574</v>
       </c>
       <c r="R54" t="n">
-        <v>6838797</v>
+        <v>6838848</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6338,7 +6329,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6357,10 +6347,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738198</v>
+        <v>129738160</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79695</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6368,42 +6358,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407575</v>
+        <v>407512</v>
       </c>
       <c r="R55" t="n">
-        <v>6838839</v>
+        <v>6839214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6462,10 +6444,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738291</v>
+        <v>129738168</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6473,21 +6455,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6497,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407574</v>
+        <v>407717</v>
       </c>
       <c r="R56" t="n">
-        <v>6838848</v>
+        <v>6839236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6559,7 +6541,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738160</v>
+        <v>129739229</v>
       </c>
       <c r="B57" t="n">
         <v>79695</v>
@@ -6594,10 +6576,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407512</v>
+        <v>407296</v>
       </c>
       <c r="R57" t="n">
-        <v>6839214</v>
+        <v>6838974</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6644,22 +6626,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738168</v>
+        <v>129738198</v>
       </c>
       <c r="B58" t="n">
-        <v>79695</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6667,34 +6649,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407717</v>
+        <v>407575</v>
       </c>
       <c r="R58" t="n">
-        <v>6839236</v>
+        <v>6838839</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6753,45 +6743,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129739229</v>
+        <v>129738255</v>
       </c>
       <c r="B59" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407296</v>
+        <v>407645</v>
       </c>
       <c r="R59" t="n">
-        <v>6838974</v>
+        <v>6838797</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6832,18 +6831,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738147</v>
+        <v>129738194</v>
       </c>
       <c r="B75" t="n">
-        <v>79695</v>
+        <v>79666</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407190</v>
+        <v>407549</v>
       </c>
       <c r="R75" t="n">
-        <v>6838950</v>
+        <v>6838809</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738176</v>
+        <v>129738147</v>
       </c>
       <c r="B76" t="n">
         <v>79695</v>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407519</v>
+        <v>407190</v>
       </c>
       <c r="R76" t="n">
-        <v>6838831</v>
+        <v>6838950</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738171</v>
+        <v>129738176</v>
       </c>
       <c r="B77" t="n">
         <v>79695</v>
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407620</v>
+        <v>407519</v>
       </c>
       <c r="R77" t="n">
-        <v>6838898</v>
+        <v>6838831</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738181</v>
+        <v>129738171</v>
       </c>
       <c r="B78" t="n">
         <v>79695</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407467</v>
+        <v>407620</v>
       </c>
       <c r="R78" t="n">
-        <v>6838834</v>
+        <v>6838898</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738275</v>
+        <v>129738181</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8734,21 +8734,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407608</v>
+        <v>407467</v>
       </c>
       <c r="R79" t="n">
-        <v>6839252</v>
+        <v>6838834</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,7 +8820,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738285</v>
+        <v>129738275</v>
       </c>
       <c r="B80" t="n">
         <v>79076</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407587</v>
+        <v>407608</v>
       </c>
       <c r="R80" t="n">
-        <v>6838806</v>
+        <v>6839252</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,54 +8917,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738244</v>
+        <v>129738285</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407231</v>
+        <v>407587</v>
       </c>
       <c r="R81" t="n">
-        <v>6838827</v>
+        <v>6838806</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9005,7 +8996,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9024,45 +9014,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B82" t="n">
-        <v>79666</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R82" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,6 +9102,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9808,45 +9808,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129739255</v>
+        <v>129738227</v>
       </c>
       <c r="B90" t="n">
-        <v>79666</v>
+        <v>5480</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>101920</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407411</v>
+        <v>407545</v>
       </c>
       <c r="R90" t="n">
-        <v>6838819</v>
+        <v>6839241</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9887,18 +9896,19 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10398,54 +10408,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129738227</v>
+        <v>129739255</v>
       </c>
       <c r="B96" t="n">
-        <v>5480</v>
+        <v>79666</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>101920</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407545</v>
+        <v>407411</v>
       </c>
       <c r="R96" t="n">
-        <v>6839241</v>
+        <v>6838819</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10486,29 +10487,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129739252</v>
+        <v>129739289</v>
       </c>
       <c r="B97" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10516,21 +10516,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407615</v>
+        <v>407649</v>
       </c>
       <c r="R97" t="n">
         <v>6839041</v>
@@ -10602,45 +10602,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129738191</v>
+        <v>129738250</v>
       </c>
       <c r="B98" t="n">
-        <v>79666</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407474</v>
+        <v>407525</v>
       </c>
       <c r="R98" t="n">
-        <v>6839108</v>
+        <v>6839244</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10681,6 +10690,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10699,7 +10709,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129739251</v>
+        <v>129739252</v>
       </c>
       <c r="B99" t="n">
         <v>79666</v>
@@ -10734,10 +10744,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407563</v>
+        <v>407615</v>
       </c>
       <c r="R99" t="n">
-        <v>6839056</v>
+        <v>6839041</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10796,10 +10806,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129739289</v>
+        <v>129738191</v>
       </c>
       <c r="B100" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10807,21 +10817,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10831,10 +10841,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407649</v>
+        <v>407474</v>
       </c>
       <c r="R100" t="n">
-        <v>6839041</v>
+        <v>6839108</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10881,22 +10891,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129738144</v>
+        <v>129739251</v>
       </c>
       <c r="B101" t="n">
-        <v>79695</v>
+        <v>79666</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10904,21 +10914,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10928,10 +10938,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407223</v>
+        <v>407563</v>
       </c>
       <c r="R101" t="n">
-        <v>6838821</v>
+        <v>6839056</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,19 +10988,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129738185</v>
+        <v>129738144</v>
       </c>
       <c r="B102" t="n">
         <v>79695</v>
@@ -11025,10 +11035,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407439</v>
+        <v>407223</v>
       </c>
       <c r="R102" t="n">
-        <v>6838837</v>
+        <v>6838821</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11087,7 +11097,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129738172</v>
+        <v>129738185</v>
       </c>
       <c r="B103" t="n">
         <v>79695</v>
@@ -11122,10 +11132,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407585</v>
+        <v>407439</v>
       </c>
       <c r="R103" t="n">
-        <v>6838872</v>
+        <v>6838837</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11184,7 +11194,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129739242</v>
+        <v>129738172</v>
       </c>
       <c r="B104" t="n">
         <v>79695</v>
@@ -11219,10 +11229,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407515</v>
+        <v>407585</v>
       </c>
       <c r="R104" t="n">
-        <v>6838875</v>
+        <v>6838872</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11269,66 +11279,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129738250</v>
+        <v>129739242</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407525</v>
+        <v>407515</v>
       </c>
       <c r="R105" t="n">
-        <v>6839244</v>
+        <v>6838875</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11369,19 +11370,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11970,40 +11970,41 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129738268</v>
+        <v>129738249</v>
       </c>
       <c r="B112" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -12013,10 +12014,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>407593</v>
+        <v>407512</v>
       </c>
       <c r="R112" t="n">
-        <v>6838811</v>
+        <v>6839241</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12057,6 +12058,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12172,41 +12174,40 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129738249</v>
+        <v>129738268</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12216,10 +12217,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>407512</v>
+        <v>407593</v>
       </c>
       <c r="R114" t="n">
-        <v>6839241</v>
+        <v>6838811</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12260,7 +12261,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -13563,10 +13563,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129739254</v>
+        <v>129739287</v>
       </c>
       <c r="B128" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13574,21 +13574,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13598,10 +13598,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407418</v>
+        <v>407622</v>
       </c>
       <c r="R128" t="n">
-        <v>6838867</v>
+        <v>6839045</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13660,10 +13660,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129739268</v>
+        <v>129738281</v>
       </c>
       <c r="B129" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,37 +13671,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407573</v>
+        <v>407587</v>
       </c>
       <c r="R129" t="n">
-        <v>6838884</v>
+        <v>6838872</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13742,29 +13739,28 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129739287</v>
+        <v>129738157</v>
       </c>
       <c r="B130" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13772,21 +13768,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13796,10 +13792,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407622</v>
+        <v>407535</v>
       </c>
       <c r="R130" t="n">
-        <v>6839045</v>
+        <v>6839193</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13846,22 +13842,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738281</v>
+        <v>129738177</v>
       </c>
       <c r="B131" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13869,21 +13865,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13893,10 +13889,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407587</v>
+        <v>407476</v>
       </c>
       <c r="R131" t="n">
-        <v>6838872</v>
+        <v>6838854</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13955,7 +13951,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738157</v>
+        <v>129738156</v>
       </c>
       <c r="B132" t="n">
         <v>79695</v>
@@ -13990,10 +13986,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407535</v>
+        <v>407477</v>
       </c>
       <c r="R132" t="n">
-        <v>6839193</v>
+        <v>6839132</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14052,7 +14048,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738177</v>
+        <v>129739230</v>
       </c>
       <c r="B133" t="n">
         <v>79695</v>
@@ -14087,10 +14083,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407476</v>
+        <v>407404</v>
       </c>
       <c r="R133" t="n">
-        <v>6838854</v>
+        <v>6839005</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14137,19 +14133,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738156</v>
+        <v>129738151</v>
       </c>
       <c r="B134" t="n">
         <v>79695</v>
@@ -14184,10 +14180,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407477</v>
+        <v>407378</v>
       </c>
       <c r="R134" t="n">
-        <v>6839132</v>
+        <v>6839143</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14246,7 +14242,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739230</v>
+        <v>129739235</v>
       </c>
       <c r="B135" t="n">
         <v>79695</v>
@@ -14281,10 +14277,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407404</v>
+        <v>407604</v>
       </c>
       <c r="R135" t="n">
-        <v>6839005</v>
+        <v>6839024</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14343,7 +14339,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129738151</v>
+        <v>129739231</v>
       </c>
       <c r="B136" t="n">
         <v>79695</v>
@@ -14378,10 +14374,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407378</v>
+        <v>407422</v>
       </c>
       <c r="R136" t="n">
-        <v>6839143</v>
+        <v>6839006</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14428,57 +14424,66 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129739235</v>
+        <v>129738248</v>
       </c>
       <c r="B137" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407604</v>
+        <v>407481</v>
       </c>
       <c r="R137" t="n">
-        <v>6839024</v>
+        <v>6839152</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14519,63 +14524,73 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129739231</v>
+        <v>129738256</v>
       </c>
       <c r="B138" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407422</v>
+        <v>407616</v>
       </c>
       <c r="R138" t="n">
-        <v>6839006</v>
+        <v>6838794</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14616,72 +14631,64 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129738248</v>
+        <v>129738242</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>78834</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407481</v>
+        <v>407719</v>
       </c>
       <c r="R139" t="n">
-        <v>6839152</v>
+        <v>6839222</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14722,7 +14729,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14741,54 +14747,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129738256</v>
+        <v>129739254</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79666</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407616</v>
+        <v>407418</v>
       </c>
       <c r="R140" t="n">
-        <v>6838794</v>
+        <v>6838867</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14829,26 +14826,25 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129738242</v>
+        <v>129739268</v>
       </c>
       <c r="B141" t="n">
         <v>78834</v>
@@ -14877,16 +14873,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407719</v>
+        <v>407573</v>
       </c>
       <c r="R141" t="n">
-        <v>6839222</v>
+        <v>6838884</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14927,28 +14926,29 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738150</v>
+        <v>129738201</v>
       </c>
       <c r="B142" t="n">
-        <v>79695</v>
+        <v>57896</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,34 +14956,42 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407203</v>
+        <v>407530</v>
       </c>
       <c r="R142" t="n">
-        <v>6839015</v>
+        <v>6839196</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15042,10 +15050,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129739253</v>
+        <v>129738286</v>
       </c>
       <c r="B143" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15053,37 +15061,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407589</v>
+        <v>407586</v>
       </c>
       <c r="R143" t="n">
-        <v>6838889</v>
+        <v>6838820</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15124,29 +15129,28 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738195</v>
+        <v>129738284</v>
       </c>
       <c r="B144" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15154,21 +15158,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15178,10 +15182,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407479</v>
+        <v>407595</v>
       </c>
       <c r="R144" t="n">
-        <v>6838852</v>
+        <v>6838836</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15240,10 +15244,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738286</v>
+        <v>129738150</v>
       </c>
       <c r="B145" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15251,21 +15255,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15275,10 +15279,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407586</v>
+        <v>407203</v>
       </c>
       <c r="R145" t="n">
-        <v>6838820</v>
+        <v>6839015</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15337,10 +15341,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129738284</v>
+        <v>129739253</v>
       </c>
       <c r="B146" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15348,34 +15352,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407595</v>
+        <v>407589</v>
       </c>
       <c r="R146" t="n">
-        <v>6838836</v>
+        <v>6838889</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15416,28 +15423,29 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738201</v>
+        <v>129738195</v>
       </c>
       <c r="B147" t="n">
-        <v>57896</v>
+        <v>79666</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15445,42 +15453,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407530</v>
+        <v>407479</v>
       </c>
       <c r="R147" t="n">
-        <v>6839196</v>
+        <v>6838852</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129738278</v>
+        <v>129739257</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,34 +2490,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407601</v>
+        <v>407574</v>
       </c>
       <c r="R16" t="n">
-        <v>6838838</v>
+        <v>6839050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,22 +2572,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129739237</v>
+        <v>129738266</v>
       </c>
       <c r="B17" t="n">
-        <v>79695</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,34 +2595,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407617</v>
+        <v>407598</v>
       </c>
       <c r="R17" t="n">
-        <v>6839035</v>
+        <v>6838839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2661,22 +2677,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738187</v>
+        <v>129739256</v>
       </c>
       <c r="B18" t="n">
-        <v>79695</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,34 +2700,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407437</v>
+        <v>407082</v>
       </c>
       <c r="R18" t="n">
-        <v>6838840</v>
+        <v>6838747</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2758,57 +2782,66 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738167</v>
+        <v>129738245</v>
       </c>
       <c r="B19" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407714</v>
+        <v>407233</v>
       </c>
       <c r="R19" t="n">
-        <v>6839244</v>
+        <v>6838838</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2849,6 +2882,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2867,10 +2901,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738159</v>
+        <v>129739237</v>
       </c>
       <c r="B20" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407516</v>
+        <v>407617</v>
       </c>
       <c r="R20" t="n">
-        <v>6839209</v>
+        <v>6839035</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2952,66 +2986,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738245</v>
+        <v>129738187</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407233</v>
+        <v>407437</v>
       </c>
       <c r="R21" t="n">
-        <v>6838838</v>
+        <v>6838840</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3052,7 +3077,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3071,10 +3095,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129739265</v>
+        <v>129738167</v>
       </c>
       <c r="B22" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3082,21 +3106,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3106,10 +3130,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407615</v>
+        <v>407714</v>
       </c>
       <c r="R22" t="n">
-        <v>6839034</v>
+        <v>6839244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,22 +3180,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739257</v>
+        <v>129738159</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3179,42 +3203,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407574</v>
+        <v>407516</v>
       </c>
       <c r="R23" t="n">
-        <v>6839050</v>
+        <v>6839209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3261,22 +3277,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738266</v>
+        <v>129738278</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,42 +3300,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407598</v>
+        <v>407601</v>
       </c>
       <c r="R24" t="n">
-        <v>6838839</v>
+        <v>6838838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3378,10 +3386,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129739256</v>
+        <v>129739265</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,42 +3397,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407082</v>
+        <v>407615</v>
       </c>
       <c r="R25" t="n">
-        <v>6838747</v>
+        <v>6839034</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129739266</v>
+        <v>129738154</v>
       </c>
       <c r="B26" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,21 +3494,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407649</v>
+        <v>407536</v>
       </c>
       <c r="R26" t="n">
-        <v>6838875</v>
+        <v>6839138</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3568,22 +3568,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129738154</v>
+        <v>129739233</v>
       </c>
       <c r="B27" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407536</v>
+        <v>407429</v>
       </c>
       <c r="R27" t="n">
-        <v>6839138</v>
+        <v>6839067</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,22 +3665,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129739233</v>
+        <v>129739266</v>
       </c>
       <c r="B28" t="n">
-        <v>79695</v>
+        <v>78839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407429</v>
+        <v>407649</v>
       </c>
       <c r="R28" t="n">
-        <v>6839067</v>
+        <v>6838875</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3774,10 +3774,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129739272</v>
+        <v>129739291</v>
       </c>
       <c r="B29" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,21 +3785,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407597</v>
+        <v>407656</v>
       </c>
       <c r="R29" t="n">
-        <v>6838888</v>
+        <v>6839031</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129739291</v>
+        <v>129739272</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407656</v>
+        <v>407597</v>
       </c>
       <c r="R30" t="n">
-        <v>6839031</v>
+        <v>6838888</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
         <v>129739227</v>
       </c>
       <c r="B31" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>129738155</v>
       </c>
       <c r="B32" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>129738179</v>
       </c>
       <c r="B33" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>129738197</v>
       </c>
       <c r="B34" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>129739248</v>
       </c>
       <c r="B35" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,45 +4453,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738287</v>
+        <v>129738246</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407591</v>
+        <v>407154</v>
       </c>
       <c r="R36" t="n">
-        <v>6838814</v>
+        <v>6838842</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4532,6 +4541,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4550,10 +4560,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129738283</v>
+        <v>129738184</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4561,37 +4571,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407598</v>
+        <v>407445</v>
       </c>
       <c r="R37" t="n">
-        <v>6838839</v>
+        <v>6838844</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,18 +4633,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4656,10 +4657,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129738184</v>
+        <v>129738149</v>
       </c>
       <c r="B38" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4691,10 +4692,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407445</v>
+        <v>407199</v>
       </c>
       <c r="R38" t="n">
-        <v>6838844</v>
+        <v>6838976</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4753,10 +4754,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738149</v>
+        <v>129738158</v>
       </c>
       <c r="B39" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4788,10 +4789,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407199</v>
+        <v>407519</v>
       </c>
       <c r="R39" t="n">
-        <v>6838976</v>
+        <v>6839207</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4850,10 +4851,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738158</v>
+        <v>129738287</v>
       </c>
       <c r="B40" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,21 +4862,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4885,10 +4886,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407519</v>
+        <v>407591</v>
       </c>
       <c r="R40" t="n">
-        <v>6839207</v>
+        <v>6838814</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4947,10 +4948,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129739271</v>
+        <v>129738283</v>
       </c>
       <c r="B41" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4958,34 +4959,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407647</v>
+        <v>407598</v>
       </c>
       <c r="R41" t="n">
-        <v>6838874</v>
+        <v>6838839</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5020,78 +5024,75 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129738246</v>
+        <v>129739271</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>78838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407154</v>
+        <v>407647</v>
       </c>
       <c r="R42" t="n">
-        <v>6838842</v>
+        <v>6838874</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5132,19 +5133,18 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738292</v>
+        <v>129738204</v>
       </c>
       <c r="B44" t="n">
-        <v>78742</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,34 +5269,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407528</v>
+        <v>407170</v>
       </c>
       <c r="R44" t="n">
-        <v>6839142</v>
+        <v>6838942</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,45 +5363,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129739240</v>
+        <v>129738247</v>
       </c>
       <c r="B45" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407581</v>
+        <v>407158</v>
       </c>
       <c r="R45" t="n">
-        <v>6838885</v>
+        <v>6838902</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5434,28 +5451,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738186</v>
+        <v>129738292</v>
       </c>
       <c r="B46" t="n">
-        <v>79695</v>
+        <v>78747</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5463,21 +5481,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5487,10 +5505,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407479</v>
+        <v>407528</v>
       </c>
       <c r="R46" t="n">
-        <v>6838810</v>
+        <v>6839142</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5549,10 +5567,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738204</v>
+        <v>129739240</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,42 +5578,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407170</v>
+        <v>407581</v>
       </c>
       <c r="R47" t="n">
-        <v>6838942</v>
+        <v>6838885</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,66 +5652,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738247</v>
+        <v>129738186</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407158</v>
+        <v>407479</v>
       </c>
       <c r="R48" t="n">
-        <v>6838902</v>
+        <v>6838810</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5742,7 +5743,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>129738290</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>129739250</v>
       </c>
       <c r="B50" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>129738152</v>
       </c>
       <c r="B51" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>129739234</v>
       </c>
       <c r="B52" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>129738196</v>
       </c>
       <c r="B53" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738291</v>
+        <v>129738160</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,21 +6261,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6285,10 +6285,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407574</v>
+        <v>407512</v>
       </c>
       <c r="R54" t="n">
-        <v>6838848</v>
+        <v>6839214</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,10 +6347,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738160</v>
+        <v>129738168</v>
       </c>
       <c r="B55" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407512</v>
+        <v>407717</v>
       </c>
       <c r="R55" t="n">
-        <v>6839214</v>
+        <v>6839236</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,10 +6444,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738168</v>
+        <v>129739229</v>
       </c>
       <c r="B56" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407717</v>
+        <v>407296</v>
       </c>
       <c r="R56" t="n">
-        <v>6839236</v>
+        <v>6838974</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6529,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129739229</v>
+        <v>129738291</v>
       </c>
       <c r="B57" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,21 +6552,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407296</v>
+        <v>407574</v>
       </c>
       <c r="R57" t="n">
-        <v>6838974</v>
+        <v>6838848</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,12 +6626,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6850,45 +6850,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129738289</v>
+        <v>129738243</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407581</v>
+        <v>407117</v>
       </c>
       <c r="R60" t="n">
-        <v>6838815</v>
+        <v>6838831</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6929,6 +6938,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6947,10 +6957,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129738277</v>
+        <v>129739232</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6958,21 +6968,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6982,10 +6992,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407593</v>
+        <v>407441</v>
       </c>
       <c r="R61" t="n">
-        <v>6838795</v>
+        <v>6839017</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7032,22 +7042,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129739232</v>
+        <v>129739244</v>
       </c>
       <c r="B62" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7079,10 +7089,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407441</v>
+        <v>407448</v>
       </c>
       <c r="R62" t="n">
-        <v>6839017</v>
+        <v>6838869</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7141,10 +7151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129739244</v>
+        <v>129739228</v>
       </c>
       <c r="B63" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7176,10 +7186,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407448</v>
+        <v>407244</v>
       </c>
       <c r="R63" t="n">
-        <v>6838869</v>
+        <v>6839107</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7238,10 +7248,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129739228</v>
+        <v>129738189</v>
       </c>
       <c r="B64" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7273,10 +7283,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407244</v>
+        <v>407407</v>
       </c>
       <c r="R64" t="n">
-        <v>6839107</v>
+        <v>6838839</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7323,22 +7333,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129738189</v>
+        <v>129738289</v>
       </c>
       <c r="B65" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7346,21 +7356,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7370,10 +7380,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407407</v>
+        <v>407581</v>
       </c>
       <c r="R65" t="n">
-        <v>6838839</v>
+        <v>6838815</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7432,54 +7442,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129738243</v>
+        <v>129738277</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>407117</v>
+        <v>407593</v>
       </c>
       <c r="R66" t="n">
-        <v>6838831</v>
+        <v>6838795</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7520,7 +7521,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>129739292</v>
       </c>
       <c r="B67" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738169</v>
+        <v>129738199</v>
       </c>
       <c r="B68" t="n">
-        <v>79695</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7651,34 +7651,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407672</v>
+        <v>407576</v>
       </c>
       <c r="R68" t="n">
-        <v>6838825</v>
+        <v>6838847</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7737,45 +7745,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739245</v>
+        <v>129738257</v>
       </c>
       <c r="B69" t="n">
-        <v>79695</v>
+        <v>58106</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407443</v>
+        <v>407464</v>
       </c>
       <c r="R69" t="n">
-        <v>6838872</v>
+        <v>6839159</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7822,22 +7838,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129739225</v>
+        <v>129738169</v>
       </c>
       <c r="B70" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7869,10 +7885,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407184</v>
+        <v>407672</v>
       </c>
       <c r="R70" t="n">
-        <v>6839011</v>
+        <v>6838825</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7919,65 +7935,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129738257</v>
+        <v>129739245</v>
       </c>
       <c r="B71" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407464</v>
+        <v>407443</v>
       </c>
       <c r="R71" t="n">
-        <v>6839159</v>
+        <v>6838872</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8024,22 +8032,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129739264</v>
+        <v>129739225</v>
       </c>
       <c r="B72" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8047,21 +8055,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8071,10 +8079,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407129</v>
+        <v>407184</v>
       </c>
       <c r="R72" t="n">
-        <v>6838913</v>
+        <v>6839011</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8133,10 +8141,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129738193</v>
+        <v>129739264</v>
       </c>
       <c r="B73" t="n">
-        <v>79666</v>
+        <v>78839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8144,21 +8152,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8168,10 +8176,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407714</v>
+        <v>407129</v>
       </c>
       <c r="R73" t="n">
-        <v>6839244</v>
+        <v>6838913</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8218,22 +8226,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129738199</v>
+        <v>129738193</v>
       </c>
       <c r="B74" t="n">
-        <v>57736</v>
+        <v>79671</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8241,42 +8249,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407576</v>
+        <v>407714</v>
       </c>
       <c r="R74" t="n">
-        <v>6838847</v>
+        <v>6839244</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8335,45 +8335,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B75" t="n">
-        <v>79666</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R75" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8414,6 +8423,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8432,10 +8442,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738147</v>
+        <v>129738194</v>
       </c>
       <c r="B76" t="n">
-        <v>79695</v>
+        <v>79671</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8443,21 +8453,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8467,10 +8477,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407190</v>
+        <v>407549</v>
       </c>
       <c r="R76" t="n">
-        <v>6838950</v>
+        <v>6838809</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,10 +8539,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738176</v>
+        <v>129738147</v>
       </c>
       <c r="B77" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8564,10 +8574,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407519</v>
+        <v>407190</v>
       </c>
       <c r="R77" t="n">
-        <v>6838831</v>
+        <v>6838950</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,10 +8636,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738171</v>
+        <v>129738176</v>
       </c>
       <c r="B78" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8661,10 +8671,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407620</v>
+        <v>407519</v>
       </c>
       <c r="R78" t="n">
-        <v>6838898</v>
+        <v>6838831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,10 +8733,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738181</v>
+        <v>129738171</v>
       </c>
       <c r="B79" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8758,10 +8768,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407467</v>
+        <v>407620</v>
       </c>
       <c r="R79" t="n">
-        <v>6838834</v>
+        <v>6838898</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,10 +8830,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738275</v>
+        <v>129738181</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8831,21 +8841,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8855,10 +8865,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407608</v>
+        <v>407467</v>
       </c>
       <c r="R80" t="n">
-        <v>6839252</v>
+        <v>6838834</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,10 +8927,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738285</v>
+        <v>129738275</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8952,10 +8962,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407587</v>
+        <v>407608</v>
       </c>
       <c r="R81" t="n">
-        <v>6838806</v>
+        <v>6839252</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9014,54 +9024,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738244</v>
+        <v>129738285</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407231</v>
+        <v>407587</v>
       </c>
       <c r="R82" t="n">
-        <v>6838827</v>
+        <v>6838806</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9102,7 +9103,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129738174</v>
+        <v>129739259</v>
       </c>
       <c r="B83" t="n">
-        <v>79695</v>
+        <v>57896</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9132,34 +9132,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407572</v>
+        <v>407549</v>
       </c>
       <c r="R83" t="n">
-        <v>6838852</v>
+        <v>6839053</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9206,22 +9214,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738143</v>
+        <v>129739267</v>
       </c>
       <c r="B84" t="n">
-        <v>79695</v>
+        <v>78839</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9229,21 +9237,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9253,10 +9261,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407137</v>
+        <v>407597</v>
       </c>
       <c r="R84" t="n">
-        <v>6838823</v>
+        <v>6838888</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9303,22 +9311,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738165</v>
+        <v>129738174</v>
       </c>
       <c r="B85" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9350,10 +9358,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407691</v>
+        <v>407572</v>
       </c>
       <c r="R85" t="n">
-        <v>6839279</v>
+        <v>6838852</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9412,10 +9420,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129739238</v>
+        <v>129738143</v>
       </c>
       <c r="B86" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9447,10 +9455,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407627</v>
+        <v>407137</v>
       </c>
       <c r="R86" t="n">
-        <v>6839039</v>
+        <v>6838823</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,22 +9505,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129738148</v>
+        <v>129738165</v>
       </c>
       <c r="B87" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9544,10 +9552,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407233</v>
+        <v>407691</v>
       </c>
       <c r="R87" t="n">
-        <v>6838964</v>
+        <v>6839279</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9606,10 +9614,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129739259</v>
+        <v>129739238</v>
       </c>
       <c r="B88" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,42 +9625,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407549</v>
+        <v>407627</v>
       </c>
       <c r="R88" t="n">
-        <v>6839053</v>
+        <v>6839039</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9711,10 +9711,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129739267</v>
+        <v>129738148</v>
       </c>
       <c r="B89" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9722,21 +9722,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407597</v>
+        <v>407233</v>
       </c>
       <c r="R89" t="n">
-        <v>6838888</v>
+        <v>6838964</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9796,53 +9796,52 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129738227</v>
+        <v>129739258</v>
       </c>
       <c r="B90" t="n">
-        <v>5480</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>101920</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -9852,10 +9851,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407545</v>
+        <v>407616</v>
       </c>
       <c r="R90" t="n">
-        <v>6839241</v>
+        <v>6838890</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9896,59 +9895,59 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739258</v>
+        <v>129738227</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>5480</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>101920</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -9958,10 +9957,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407616</v>
+        <v>407545</v>
       </c>
       <c r="R91" t="n">
-        <v>6838890</v>
+        <v>6839241</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10002,18 +10001,19 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
         <v>129739246</v>
       </c>
       <c r="B92" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>129739239</v>
       </c>
       <c r="B93" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>129738170</v>
       </c>
       <c r="B94" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>129738188</v>
       </c>
       <c r="B95" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>129739255</v>
       </c>
       <c r="B96" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>129739289</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10709,10 +10709,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129739252</v>
+        <v>129738144</v>
       </c>
       <c r="B99" t="n">
-        <v>79666</v>
+        <v>79700</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10720,21 +10720,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407615</v>
+        <v>407223</v>
       </c>
       <c r="R99" t="n">
-        <v>6839041</v>
+        <v>6838821</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10794,22 +10794,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129738191</v>
+        <v>129738185</v>
       </c>
       <c r="B100" t="n">
-        <v>79666</v>
+        <v>79700</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10817,21 +10817,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407474</v>
+        <v>407439</v>
       </c>
       <c r="R100" t="n">
-        <v>6839108</v>
+        <v>6838837</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10903,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129739251</v>
+        <v>129738172</v>
       </c>
       <c r="B101" t="n">
-        <v>79666</v>
+        <v>79700</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10914,21 +10914,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407563</v>
+        <v>407585</v>
       </c>
       <c r="R101" t="n">
-        <v>6839056</v>
+        <v>6838872</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10988,22 +10988,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129738144</v>
+        <v>129739242</v>
       </c>
       <c r="B102" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11035,10 +11035,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407223</v>
+        <v>407515</v>
       </c>
       <c r="R102" t="n">
-        <v>6838821</v>
+        <v>6838875</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11085,22 +11085,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129738185</v>
+        <v>129739252</v>
       </c>
       <c r="B103" t="n">
-        <v>79695</v>
+        <v>79671</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11108,21 +11108,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11132,10 +11132,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407439</v>
+        <v>407615</v>
       </c>
       <c r="R103" t="n">
-        <v>6838837</v>
+        <v>6839041</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11182,22 +11182,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129738172</v>
+        <v>129738191</v>
       </c>
       <c r="B104" t="n">
-        <v>79695</v>
+        <v>79671</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11205,21 +11205,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407585</v>
+        <v>407474</v>
       </c>
       <c r="R104" t="n">
-        <v>6838872</v>
+        <v>6839108</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11291,10 +11291,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129739242</v>
+        <v>129739251</v>
       </c>
       <c r="B105" t="n">
-        <v>79695</v>
+        <v>79671</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11302,21 +11302,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11326,10 +11326,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407515</v>
+        <v>407563</v>
       </c>
       <c r="R105" t="n">
-        <v>6838875</v>
+        <v>6839056</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11388,10 +11388,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129739273</v>
+        <v>129738173</v>
       </c>
       <c r="B106" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11399,21 +11399,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>407582</v>
+        <v>407587</v>
       </c>
       <c r="R106" t="n">
-        <v>6838890</v>
+        <v>6838860</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11473,22 +11473,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129738173</v>
+        <v>129738182</v>
       </c>
       <c r="B107" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>407587</v>
+        <v>407447</v>
       </c>
       <c r="R107" t="n">
-        <v>6838860</v>
+        <v>6838843</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129738182</v>
+        <v>129739273</v>
       </c>
       <c r="B108" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11593,21 +11593,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>407447</v>
+        <v>407582</v>
       </c>
       <c r="R108" t="n">
-        <v>6838843</v>
+        <v>6838890</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11667,57 +11667,66 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738180</v>
+        <v>129738249</v>
       </c>
       <c r="B109" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407480</v>
+        <v>407512</v>
       </c>
       <c r="R109" t="n">
-        <v>6838840</v>
+        <v>6839241</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11758,6 +11767,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11776,10 +11786,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738190</v>
+        <v>129738180</v>
       </c>
       <c r="B110" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11811,10 +11821,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407412</v>
+        <v>407480</v>
       </c>
       <c r="R110" t="n">
-        <v>6838831</v>
+        <v>6838840</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11873,10 +11883,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129738175</v>
+        <v>129738190</v>
       </c>
       <c r="B111" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11908,10 +11918,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>407547</v>
+        <v>407412</v>
       </c>
       <c r="R111" t="n">
-        <v>6838816</v>
+        <v>6838831</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,54 +11980,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129738249</v>
+        <v>129738175</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>407512</v>
+        <v>407547</v>
       </c>
       <c r="R112" t="n">
-        <v>6839241</v>
+        <v>6838816</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12058,7 +12059,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12080,7 +12080,7 @@
         <v>129738276</v>
       </c>
       <c r="B113" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129739243</v>
+        <v>129738280</v>
       </c>
       <c r="B115" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,34 +12290,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407451</v>
+        <v>407623</v>
       </c>
       <c r="R115" t="n">
-        <v>6838866</v>
+        <v>6838894</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12352,34 +12355,40 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129739224</v>
+        <v>129739290</v>
       </c>
       <c r="B116" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12387,34 +12396,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407121</v>
+        <v>407657</v>
       </c>
       <c r="R116" t="n">
-        <v>6838895</v>
+        <v>6839033</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12449,12 +12461,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12473,10 +12491,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129738145</v>
+        <v>129738282</v>
       </c>
       <c r="B117" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12484,21 +12502,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12508,10 +12526,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407194</v>
+        <v>407588</v>
       </c>
       <c r="R117" t="n">
-        <v>6838873</v>
+        <v>6838831</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12544,6 +12562,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12570,10 +12593,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129738192</v>
+        <v>129739243</v>
       </c>
       <c r="B118" t="n">
-        <v>79666</v>
+        <v>79700</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12581,21 +12604,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12605,10 +12628,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407464</v>
+        <v>407451</v>
       </c>
       <c r="R118" t="n">
-        <v>6839157</v>
+        <v>6838866</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12655,22 +12678,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129738280</v>
+        <v>129739224</v>
       </c>
       <c r="B119" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12678,37 +12701,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407623</v>
+        <v>407121</v>
       </c>
       <c r="R119" t="n">
-        <v>6838894</v>
+        <v>6838895</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12743,40 +12763,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129739290</v>
+        <v>129738145</v>
       </c>
       <c r="B120" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12784,37 +12798,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407657</v>
+        <v>407194</v>
       </c>
       <c r="R120" t="n">
-        <v>6839033</v>
+        <v>6838873</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12849,40 +12860,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129738282</v>
+        <v>129738192</v>
       </c>
       <c r="B121" t="n">
-        <v>79076</v>
+        <v>79671</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12890,21 +12895,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12914,10 +12919,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407588</v>
+        <v>407464</v>
       </c>
       <c r="R121" t="n">
-        <v>6838831</v>
+        <v>6839157</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12950,11 +12955,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12981,10 +12981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129738279</v>
+        <v>129739286</v>
       </c>
       <c r="B122" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407617</v>
+        <v>407570</v>
       </c>
       <c r="R122" t="n">
-        <v>6838855</v>
+        <v>6839041</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13066,22 +13066,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129738288</v>
+        <v>129738279</v>
       </c>
       <c r="B123" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407592</v>
+        <v>407617</v>
       </c>
       <c r="R123" t="n">
-        <v>6838822</v>
+        <v>6838855</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13175,10 +13175,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129739286</v>
+        <v>129738288</v>
       </c>
       <c r="B124" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407570</v>
+        <v>407592</v>
       </c>
       <c r="R124" t="n">
-        <v>6839041</v>
+        <v>6838822</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13260,12 +13260,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13275,7 +13275,7 @@
         <v>129738146</v>
       </c>
       <c r="B125" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13369,10 +13369,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129739241</v>
+        <v>129739249</v>
       </c>
       <c r="B126" t="n">
-        <v>79695</v>
+        <v>79671</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13380,21 +13380,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407524</v>
+        <v>407437</v>
       </c>
       <c r="R126" t="n">
-        <v>6838914</v>
+        <v>6839060</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13466,10 +13466,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739249</v>
+        <v>129739241</v>
       </c>
       <c r="B127" t="n">
-        <v>79666</v>
+        <v>79700</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407437</v>
+        <v>407524</v>
       </c>
       <c r="R127" t="n">
-        <v>6839060</v>
+        <v>6838914</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>129739287</v>
       </c>
       <c r="B128" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>129738281</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13757,45 +13757,54 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129738157</v>
+        <v>129738248</v>
       </c>
       <c r="B130" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407535</v>
+        <v>407481</v>
       </c>
       <c r="R130" t="n">
-        <v>6839193</v>
+        <v>6839152</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13836,6 +13845,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13854,45 +13864,54 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738177</v>
+        <v>129738256</v>
       </c>
       <c r="B131" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407476</v>
+        <v>407616</v>
       </c>
       <c r="R131" t="n">
-        <v>6838854</v>
+        <v>6838794</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13933,6 +13952,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13951,10 +13971,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738156</v>
+        <v>129738157</v>
       </c>
       <c r="B132" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13986,10 +14006,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407477</v>
+        <v>407535</v>
       </c>
       <c r="R132" t="n">
-        <v>6839132</v>
+        <v>6839193</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14048,10 +14068,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129739230</v>
+        <v>129738177</v>
       </c>
       <c r="B133" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14083,10 +14103,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407404</v>
+        <v>407476</v>
       </c>
       <c r="R133" t="n">
-        <v>6839005</v>
+        <v>6838854</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14133,22 +14153,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738151</v>
+        <v>129738156</v>
       </c>
       <c r="B134" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14180,10 +14200,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407378</v>
+        <v>407477</v>
       </c>
       <c r="R134" t="n">
-        <v>6839143</v>
+        <v>6839132</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14242,10 +14262,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739235</v>
+        <v>129739230</v>
       </c>
       <c r="B135" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14277,10 +14297,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407604</v>
+        <v>407404</v>
       </c>
       <c r="R135" t="n">
-        <v>6839024</v>
+        <v>6839005</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14339,10 +14359,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129739231</v>
+        <v>129738151</v>
       </c>
       <c r="B136" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14374,10 +14394,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407422</v>
+        <v>407378</v>
       </c>
       <c r="R136" t="n">
-        <v>6839006</v>
+        <v>6839143</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14424,66 +14444,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129738248</v>
+        <v>129739235</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407481</v>
+        <v>407604</v>
       </c>
       <c r="R137" t="n">
-        <v>6839152</v>
+        <v>6839024</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14524,73 +14535,63 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129738256</v>
+        <v>129739231</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407616</v>
+        <v>407422</v>
       </c>
       <c r="R138" t="n">
-        <v>6838794</v>
+        <v>6839006</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14631,19 +14632,18 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -14653,7 +14653,7 @@
         <v>129738242</v>
       </c>
       <c r="B139" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>129739254</v>
       </c>
       <c r="B140" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>129739268</v>
       </c>
       <c r="B141" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14945,10 +14945,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738201</v>
+        <v>129738150</v>
       </c>
       <c r="B142" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,42 +14956,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407530</v>
+        <v>407203</v>
       </c>
       <c r="R142" t="n">
-        <v>6839196</v>
+        <v>6839015</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15053,7 +15045,7 @@
         <v>129738286</v>
       </c>
       <c r="B143" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15150,7 +15142,7 @@
         <v>129738284</v>
       </c>
       <c r="B144" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15244,10 +15236,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738150</v>
+        <v>129739253</v>
       </c>
       <c r="B145" t="n">
-        <v>79695</v>
+        <v>79671</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15255,34 +15247,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407203</v>
+        <v>407589</v>
       </c>
       <c r="R145" t="n">
-        <v>6839015</v>
+        <v>6838889</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15323,28 +15318,29 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129739253</v>
+        <v>129738195</v>
       </c>
       <c r="B146" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15370,19 +15366,16 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407589</v>
+        <v>407479</v>
       </c>
       <c r="R146" t="n">
-        <v>6838889</v>
+        <v>6838852</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15423,29 +15416,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738195</v>
+        <v>129738201</v>
       </c>
       <c r="B147" t="n">
-        <v>79666</v>
+        <v>57896</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15453,34 +15445,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407479</v>
+        <v>407530</v>
       </c>
       <c r="R147" t="n">
-        <v>6838852</v>
+        <v>6839196</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15542,7 +15542,7 @@
         <v>129738274</v>
       </c>
       <c r="B148" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>129739288</v>
       </c>
       <c r="B149" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>129738164</v>
       </c>
       <c r="B150" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>129738153</v>
       </c>
       <c r="B151" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>129738166</v>
       </c>
       <c r="B152" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>129739247</v>
       </c>
       <c r="B153" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129739257</v>
+        <v>129738278</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,42 +2490,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407574</v>
+        <v>407601</v>
       </c>
       <c r="R16" t="n">
-        <v>6839050</v>
+        <v>6838838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2572,22 +2564,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129738266</v>
+        <v>129739237</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,42 +2587,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407598</v>
+        <v>407617</v>
       </c>
       <c r="R17" t="n">
-        <v>6838839</v>
+        <v>6839035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2677,22 +2661,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129739256</v>
+        <v>129738187</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,42 +2684,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407082</v>
+        <v>407437</v>
       </c>
       <c r="R18" t="n">
-        <v>6838747</v>
+        <v>6838840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2782,66 +2758,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738245</v>
+        <v>129738167</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407233</v>
+        <v>407714</v>
       </c>
       <c r="R19" t="n">
-        <v>6838838</v>
+        <v>6839244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2882,7 +2849,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2901,7 +2867,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129739237</v>
+        <v>129738159</v>
       </c>
       <c r="B20" t="n">
         <v>79700</v>
@@ -2936,10 +2902,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407617</v>
+        <v>407516</v>
       </c>
       <c r="R20" t="n">
-        <v>6839035</v>
+        <v>6839209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2986,22 +2952,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738187</v>
+        <v>129739257</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3009,34 +2975,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407437</v>
+        <v>407574</v>
       </c>
       <c r="R21" t="n">
-        <v>6838840</v>
+        <v>6839050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3083,22 +3057,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738167</v>
+        <v>129738266</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3106,34 +3080,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407714</v>
+        <v>407598</v>
       </c>
       <c r="R22" t="n">
-        <v>6839244</v>
+        <v>6838839</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3192,10 +3174,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129738159</v>
+        <v>129739256</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,34 +3185,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407516</v>
+        <v>407082</v>
       </c>
       <c r="R23" t="n">
-        <v>6839209</v>
+        <v>6838747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3277,54 +3267,63 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738278</v>
+        <v>129738245</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407601</v>
+        <v>407233</v>
       </c>
       <c r="R24" t="n">
         <v>6838838</v>
@@ -3368,6 +3367,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129738154</v>
+        <v>129739233</v>
       </c>
       <c r="B26" t="n">
         <v>79700</v>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407536</v>
+        <v>407429</v>
       </c>
       <c r="R26" t="n">
-        <v>6839138</v>
+        <v>6839067</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3568,22 +3568,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129739233</v>
+        <v>129739272</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,21 +3591,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407429</v>
+        <v>407597</v>
       </c>
       <c r="R27" t="n">
-        <v>6839067</v>
+        <v>6838888</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129739272</v>
+        <v>129738154</v>
       </c>
       <c r="B30" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407597</v>
+        <v>407536</v>
       </c>
       <c r="R30" t="n">
-        <v>6838888</v>
+        <v>6839138</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,12 +3956,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4560,45 +4560,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129738184</v>
+        <v>129739270</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407445</v>
+        <v>407283</v>
       </c>
       <c r="R37" t="n">
-        <v>6838844</v>
+        <v>6839055</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4639,25 +4648,26 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129738149</v>
+        <v>129738184</v>
       </c>
       <c r="B38" t="n">
         <v>79700</v>
@@ -4692,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407199</v>
+        <v>407445</v>
       </c>
       <c r="R38" t="n">
-        <v>6838976</v>
+        <v>6838844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4754,7 +4764,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738158</v>
+        <v>129738149</v>
       </c>
       <c r="B39" t="n">
         <v>79700</v>
@@ -4789,10 +4799,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407519</v>
+        <v>407199</v>
       </c>
       <c r="R39" t="n">
-        <v>6839207</v>
+        <v>6838976</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4851,10 +4861,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738287</v>
+        <v>129738158</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,21 +4872,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4886,10 +4896,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407591</v>
+        <v>407519</v>
       </c>
       <c r="R40" t="n">
-        <v>6838814</v>
+        <v>6839207</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4948,7 +4958,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738283</v>
+        <v>129738287</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -4977,19 +4987,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407598</v>
+        <v>407591</v>
       </c>
       <c r="R41" t="n">
-        <v>6838839</v>
+        <v>6838814</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5024,18 +5031,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5054,10 +5055,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129739271</v>
+        <v>129738283</v>
       </c>
       <c r="B42" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5065,34 +5066,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407647</v>
+        <v>407598</v>
       </c>
       <c r="R42" t="n">
-        <v>6838874</v>
+        <v>6838839</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5127,78 +5131,75 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129739270</v>
+        <v>129739271</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>78838</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407283</v>
+        <v>407647</v>
       </c>
       <c r="R43" t="n">
-        <v>6839055</v>
+        <v>6838874</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,7 +5240,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738204</v>
+        <v>129738292</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>78747</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,42 +5269,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407170</v>
+        <v>407528</v>
       </c>
       <c r="R44" t="n">
-        <v>6838942</v>
+        <v>6839142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,41 +5355,40 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738247</v>
+        <v>129738204</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5407,10 +5398,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407158</v>
+        <v>407170</v>
       </c>
       <c r="R45" t="n">
-        <v>6838902</v>
+        <v>6838942</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5451,7 +5442,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5470,45 +5460,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738292</v>
+        <v>129738247</v>
       </c>
       <c r="B46" t="n">
-        <v>78747</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407528</v>
+        <v>407158</v>
       </c>
       <c r="R46" t="n">
-        <v>6839142</v>
+        <v>6838902</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5549,6 +5548,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738160</v>
+        <v>129738198</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,34 +6261,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407512</v>
+        <v>407575</v>
       </c>
       <c r="R54" t="n">
-        <v>6839214</v>
+        <v>6838839</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,45 +6355,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738168</v>
+        <v>129738255</v>
       </c>
       <c r="B55" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407717</v>
+        <v>407645</v>
       </c>
       <c r="R55" t="n">
-        <v>6839236</v>
+        <v>6838797</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6426,6 +6443,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6444,7 +6462,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129739229</v>
+        <v>129738160</v>
       </c>
       <c r="B56" t="n">
         <v>79700</v>
@@ -6479,10 +6497,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407296</v>
+        <v>407512</v>
       </c>
       <c r="R56" t="n">
-        <v>6838974</v>
+        <v>6839214</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6529,12 +6547,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6638,10 +6656,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738198</v>
+        <v>129738168</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6649,42 +6667,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407575</v>
+        <v>407717</v>
       </c>
       <c r="R58" t="n">
-        <v>6838839</v>
+        <v>6839236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6743,54 +6753,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738255</v>
+        <v>129739229</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407645</v>
+        <v>407296</v>
       </c>
       <c r="R59" t="n">
-        <v>6838797</v>
+        <v>6838974</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6831,73 +6832,63 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129738243</v>
+        <v>129739232</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407117</v>
+        <v>407441</v>
       </c>
       <c r="R60" t="n">
-        <v>6838831</v>
+        <v>6839017</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6938,26 +6929,25 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129739232</v>
+        <v>129739244</v>
       </c>
       <c r="B61" t="n">
         <v>79700</v>
@@ -6992,10 +6982,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407441</v>
+        <v>407448</v>
       </c>
       <c r="R61" t="n">
-        <v>6839017</v>
+        <v>6838869</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7054,10 +7044,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129739244</v>
+        <v>129738289</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7065,21 +7055,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7089,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407448</v>
+        <v>407581</v>
       </c>
       <c r="R62" t="n">
-        <v>6838869</v>
+        <v>6838815</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7139,22 +7129,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129739228</v>
+        <v>129738277</v>
       </c>
       <c r="B63" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7162,21 +7152,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7186,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407244</v>
+        <v>407593</v>
       </c>
       <c r="R63" t="n">
-        <v>6839107</v>
+        <v>6838795</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7236,19 +7226,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129738189</v>
+        <v>129739228</v>
       </c>
       <c r="B64" t="n">
         <v>79700</v>
@@ -7283,10 +7273,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407407</v>
+        <v>407244</v>
       </c>
       <c r="R64" t="n">
-        <v>6838839</v>
+        <v>6839107</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7333,22 +7323,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129738289</v>
+        <v>129738189</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7356,21 +7346,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7380,10 +7370,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407581</v>
+        <v>407407</v>
       </c>
       <c r="R65" t="n">
-        <v>6838815</v>
+        <v>6838839</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7442,45 +7432,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129738277</v>
+        <v>129738243</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>407593</v>
+        <v>407117</v>
       </c>
       <c r="R66" t="n">
-        <v>6838795</v>
+        <v>6838831</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7521,6 +7520,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129739292</v>
+        <v>129738199</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7550,26 +7550,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7577,10 +7582,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407632</v>
+        <v>407576</v>
       </c>
       <c r="R67" t="n">
-        <v>6838901</v>
+        <v>6838847</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7621,29 +7626,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738199</v>
+        <v>129739292</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7651,31 +7655,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7683,10 +7682,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407576</v>
+        <v>407632</v>
       </c>
       <c r="R68" t="n">
-        <v>6838847</v>
+        <v>6838901</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7727,71 +7726,64 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129738257</v>
+        <v>129738169</v>
       </c>
       <c r="B69" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407464</v>
+        <v>407672</v>
       </c>
       <c r="R69" t="n">
-        <v>6839159</v>
+        <v>6838825</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7850,7 +7842,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129738169</v>
+        <v>129739245</v>
       </c>
       <c r="B70" t="n">
         <v>79700</v>
@@ -7885,10 +7877,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407672</v>
+        <v>407443</v>
       </c>
       <c r="R70" t="n">
-        <v>6838825</v>
+        <v>6838872</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7935,19 +7927,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129739245</v>
+        <v>129739225</v>
       </c>
       <c r="B71" t="n">
         <v>79700</v>
@@ -7982,10 +7974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407443</v>
+        <v>407184</v>
       </c>
       <c r="R71" t="n">
-        <v>6838872</v>
+        <v>6839011</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8044,45 +8036,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129739225</v>
+        <v>129738257</v>
       </c>
       <c r="B72" t="n">
-        <v>79700</v>
+        <v>58106</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407184</v>
+        <v>407464</v>
       </c>
       <c r="R72" t="n">
-        <v>6839011</v>
+        <v>6839159</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8129,12 +8129,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8335,54 +8335,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738244</v>
+        <v>129738285</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407231</v>
+        <v>407587</v>
       </c>
       <c r="R75" t="n">
-        <v>6838827</v>
+        <v>6838806</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8423,7 +8414,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8442,10 +8432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738194</v>
+        <v>129738147</v>
       </c>
       <c r="B76" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8453,21 +8443,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8477,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407549</v>
+        <v>407190</v>
       </c>
       <c r="R76" t="n">
-        <v>6838809</v>
+        <v>6838950</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8539,7 +8529,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738147</v>
+        <v>129738176</v>
       </c>
       <c r="B77" t="n">
         <v>79700</v>
@@ -8574,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407190</v>
+        <v>407519</v>
       </c>
       <c r="R77" t="n">
-        <v>6838950</v>
+        <v>6838831</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,7 +8626,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738176</v>
+        <v>129738171</v>
       </c>
       <c r="B78" t="n">
         <v>79700</v>
@@ -8671,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407519</v>
+        <v>407620</v>
       </c>
       <c r="R78" t="n">
-        <v>6838831</v>
+        <v>6838898</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8733,7 +8723,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738171</v>
+        <v>129738181</v>
       </c>
       <c r="B79" t="n">
         <v>79700</v>
@@ -8768,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407620</v>
+        <v>407467</v>
       </c>
       <c r="R79" t="n">
-        <v>6838898</v>
+        <v>6838834</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8830,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738181</v>
+        <v>129738194</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8841,21 +8831,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8865,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407467</v>
+        <v>407549</v>
       </c>
       <c r="R80" t="n">
-        <v>6838834</v>
+        <v>6838809</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9024,45 +9014,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738285</v>
+        <v>129738244</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407587</v>
+        <v>407231</v>
       </c>
       <c r="R82" t="n">
-        <v>6838806</v>
+        <v>6838827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,6 +9102,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129739259</v>
+        <v>129738174</v>
       </c>
       <c r="B83" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9132,42 +9132,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407549</v>
+        <v>407572</v>
       </c>
       <c r="R83" t="n">
-        <v>6839053</v>
+        <v>6838852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9214,22 +9206,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129739267</v>
+        <v>129738143</v>
       </c>
       <c r="B84" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9237,21 +9229,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9261,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407597</v>
+        <v>407137</v>
       </c>
       <c r="R84" t="n">
-        <v>6838888</v>
+        <v>6838823</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9311,19 +9303,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738174</v>
+        <v>129738165</v>
       </c>
       <c r="B85" t="n">
         <v>79700</v>
@@ -9358,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407572</v>
+        <v>407691</v>
       </c>
       <c r="R85" t="n">
-        <v>6838852</v>
+        <v>6839279</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9420,7 +9412,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129738143</v>
+        <v>129739238</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9455,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407137</v>
+        <v>407627</v>
       </c>
       <c r="R86" t="n">
-        <v>6838823</v>
+        <v>6839039</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9505,19 +9497,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129738165</v>
+        <v>129738148</v>
       </c>
       <c r="B87" t="n">
         <v>79700</v>
@@ -9552,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407691</v>
+        <v>407233</v>
       </c>
       <c r="R87" t="n">
-        <v>6839279</v>
+        <v>6838964</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9614,10 +9606,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129739238</v>
+        <v>129739259</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9625,34 +9617,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407627</v>
+        <v>407549</v>
       </c>
       <c r="R88" t="n">
-        <v>6839039</v>
+        <v>6839053</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9711,10 +9711,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129738148</v>
+        <v>129739267</v>
       </c>
       <c r="B89" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9722,21 +9722,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407233</v>
+        <v>407597</v>
       </c>
       <c r="R89" t="n">
-        <v>6838964</v>
+        <v>6838888</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9796,22 +9796,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129739258</v>
+        <v>129739246</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9819,42 +9819,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407616</v>
+        <v>407427</v>
       </c>
       <c r="R90" t="n">
-        <v>6838890</v>
+        <v>6838886</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9913,54 +9905,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129738227</v>
+        <v>129739239</v>
       </c>
       <c r="B91" t="n">
-        <v>5480</v>
+        <v>79700</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407545</v>
+        <v>407614</v>
       </c>
       <c r="R91" t="n">
-        <v>6839241</v>
+        <v>6838900</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10001,26 +9984,25 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129739246</v>
+        <v>129738170</v>
       </c>
       <c r="B92" t="n">
         <v>79700</v>
@@ -10055,10 +10037,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407427</v>
+        <v>407660</v>
       </c>
       <c r="R92" t="n">
-        <v>6838886</v>
+        <v>6838791</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10105,19 +10087,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129739239</v>
+        <v>129738188</v>
       </c>
       <c r="B93" t="n">
         <v>79700</v>
@@ -10152,10 +10134,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407614</v>
+        <v>407408</v>
       </c>
       <c r="R93" t="n">
-        <v>6838900</v>
+        <v>6838841</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10202,22 +10184,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129738170</v>
+        <v>129739258</v>
       </c>
       <c r="B94" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10225,34 +10207,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407660</v>
+        <v>407616</v>
       </c>
       <c r="R94" t="n">
-        <v>6838791</v>
+        <v>6838890</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10299,57 +10289,66 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129738188</v>
+        <v>129738227</v>
       </c>
       <c r="B95" t="n">
-        <v>79700</v>
+        <v>5480</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407408</v>
+        <v>407545</v>
       </c>
       <c r="R95" t="n">
-        <v>6838841</v>
+        <v>6839241</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10390,6 +10389,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10505,45 +10505,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129739289</v>
+        <v>129738250</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407649</v>
+        <v>407525</v>
       </c>
       <c r="R97" t="n">
-        <v>6839041</v>
+        <v>6839244</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10584,72 +10593,64 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129738250</v>
+        <v>129738144</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407525</v>
+        <v>407223</v>
       </c>
       <c r="R98" t="n">
-        <v>6839244</v>
+        <v>6838821</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10690,7 +10691,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10709,7 +10709,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129738144</v>
+        <v>129738185</v>
       </c>
       <c r="B99" t="n">
         <v>79700</v>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407223</v>
+        <v>407439</v>
       </c>
       <c r="R99" t="n">
-        <v>6838821</v>
+        <v>6838837</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10806,10 +10806,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129738185</v>
+        <v>129739289</v>
       </c>
       <c r="B100" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10817,21 +10817,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407439</v>
+        <v>407649</v>
       </c>
       <c r="R100" t="n">
-        <v>6838837</v>
+        <v>6839041</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10891,12 +10891,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11388,7 +11388,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129738173</v>
+        <v>129738182</v>
       </c>
       <c r="B106" t="n">
         <v>79700</v>
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>407587</v>
+        <v>407447</v>
       </c>
       <c r="R106" t="n">
-        <v>6838860</v>
+        <v>6838843</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11485,10 +11485,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129738182</v>
+        <v>129739273</v>
       </c>
       <c r="B107" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11496,21 +11496,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>407447</v>
+        <v>407582</v>
       </c>
       <c r="R107" t="n">
-        <v>6838843</v>
+        <v>6838890</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11570,22 +11570,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129739273</v>
+        <v>129738173</v>
       </c>
       <c r="B108" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11593,21 +11593,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>407582</v>
+        <v>407587</v>
       </c>
       <c r="R108" t="n">
-        <v>6838890</v>
+        <v>6838860</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11667,66 +11667,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738249</v>
+        <v>129738180</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407512</v>
+        <v>407480</v>
       </c>
       <c r="R109" t="n">
-        <v>6839241</v>
+        <v>6838840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11767,7 +11758,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11786,10 +11776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738180</v>
+        <v>129738276</v>
       </c>
       <c r="B110" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11797,21 +11787,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11821,10 +11811,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407480</v>
+        <v>407607</v>
       </c>
       <c r="R110" t="n">
-        <v>6838840</v>
+        <v>6838798</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12077,10 +12067,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129738276</v>
+        <v>129738268</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12088,34 +12078,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>407607</v>
+        <v>407593</v>
       </c>
       <c r="R113" t="n">
-        <v>6838798</v>
+        <v>6838811</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12174,40 +12172,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129738268</v>
+        <v>129738249</v>
       </c>
       <c r="B114" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12217,10 +12216,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>407593</v>
+        <v>407512</v>
       </c>
       <c r="R114" t="n">
-        <v>6838811</v>
+        <v>6839241</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12261,6 +12260,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129738280</v>
+        <v>129739243</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,37 +12290,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407623</v>
+        <v>407451</v>
       </c>
       <c r="R115" t="n">
-        <v>6838894</v>
+        <v>6838866</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12355,37 +12352,31 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129739290</v>
+        <v>129738280</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -12423,10 +12414,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407657</v>
+        <v>407623</v>
       </c>
       <c r="R116" t="n">
-        <v>6839033</v>
+        <v>6838894</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12463,7 +12454,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12479,22 +12470,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129738282</v>
+        <v>129739224</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12502,21 +12493,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12526,10 +12517,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407588</v>
+        <v>407121</v>
       </c>
       <c r="R117" t="n">
-        <v>6838831</v>
+        <v>6838895</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12564,11 +12555,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12581,22 +12567,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129739243</v>
+        <v>129739290</v>
       </c>
       <c r="B118" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12604,34 +12590,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407451</v>
+        <v>407657</v>
       </c>
       <c r="R118" t="n">
-        <v>6838866</v>
+        <v>6839033</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12666,12 +12655,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12690,10 +12685,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129739224</v>
+        <v>129738282</v>
       </c>
       <c r="B119" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12701,21 +12696,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12725,10 +12720,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407121</v>
+        <v>407588</v>
       </c>
       <c r="R119" t="n">
-        <v>6838895</v>
+        <v>6838831</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12763,6 +12758,11 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12775,12 +12775,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12981,10 +12981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739286</v>
+        <v>129739249</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407570</v>
+        <v>407437</v>
       </c>
       <c r="R122" t="n">
-        <v>6839041</v>
+        <v>6839060</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13078,7 +13078,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129738279</v>
+        <v>129739286</v>
       </c>
       <c r="B123" t="n">
         <v>79081</v>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407617</v>
+        <v>407570</v>
       </c>
       <c r="R123" t="n">
-        <v>6838855</v>
+        <v>6839041</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13163,19 +13163,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129738288</v>
+        <v>129738279</v>
       </c>
       <c r="B124" t="n">
         <v>79081</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407592</v>
+        <v>407617</v>
       </c>
       <c r="R124" t="n">
-        <v>6838822</v>
+        <v>6838855</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13272,10 +13272,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738146</v>
+        <v>129738288</v>
       </c>
       <c r="B125" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407163</v>
+        <v>407592</v>
       </c>
       <c r="R125" t="n">
-        <v>6838891</v>
+        <v>6838822</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,10 +13369,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129739249</v>
+        <v>129738146</v>
       </c>
       <c r="B126" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13380,21 +13380,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407437</v>
+        <v>407163</v>
       </c>
       <c r="R126" t="n">
-        <v>6839060</v>
+        <v>6838891</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13454,12 +13454,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -13563,10 +13563,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129739287</v>
+        <v>129738242</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13574,21 +13574,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13598,10 +13598,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407622</v>
+        <v>407719</v>
       </c>
       <c r="R128" t="n">
-        <v>6839045</v>
+        <v>6839222</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,22 +13648,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738281</v>
+        <v>129739254</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,21 +13671,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13695,10 +13695,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407587</v>
+        <v>407418</v>
       </c>
       <c r="R129" t="n">
-        <v>6838872</v>
+        <v>6838867</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13745,55 +13745,49 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129738248</v>
+        <v>129739268</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -13801,10 +13795,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407481</v>
+        <v>407573</v>
       </c>
       <c r="R130" t="n">
-        <v>6839152</v>
+        <v>6838884</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13852,66 +13846,57 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738256</v>
+        <v>129738157</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407616</v>
+        <v>407535</v>
       </c>
       <c r="R131" t="n">
-        <v>6838794</v>
+        <v>6839193</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13952,7 +13937,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13971,10 +13955,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738157</v>
+        <v>129739287</v>
       </c>
       <c r="B132" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13982,21 +13966,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14006,10 +13990,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407535</v>
+        <v>407622</v>
       </c>
       <c r="R132" t="n">
-        <v>6839193</v>
+        <v>6839045</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14056,22 +14040,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738177</v>
+        <v>129738281</v>
       </c>
       <c r="B133" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14079,21 +14063,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14103,10 +14087,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407476</v>
+        <v>407587</v>
       </c>
       <c r="R133" t="n">
-        <v>6838854</v>
+        <v>6838872</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14165,7 +14149,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738156</v>
+        <v>129738177</v>
       </c>
       <c r="B134" t="n">
         <v>79700</v>
@@ -14200,10 +14184,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407477</v>
+        <v>407476</v>
       </c>
       <c r="R134" t="n">
-        <v>6839132</v>
+        <v>6838854</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14262,7 +14246,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739230</v>
+        <v>129738156</v>
       </c>
       <c r="B135" t="n">
         <v>79700</v>
@@ -14297,10 +14281,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407404</v>
+        <v>407477</v>
       </c>
       <c r="R135" t="n">
-        <v>6839005</v>
+        <v>6839132</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14347,19 +14331,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129738151</v>
+        <v>129739230</v>
       </c>
       <c r="B136" t="n">
         <v>79700</v>
@@ -14394,10 +14378,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407378</v>
+        <v>407404</v>
       </c>
       <c r="R136" t="n">
-        <v>6839143</v>
+        <v>6839005</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14444,19 +14428,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129739235</v>
+        <v>129738151</v>
       </c>
       <c r="B137" t="n">
         <v>79700</v>
@@ -14491,10 +14475,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407604</v>
+        <v>407378</v>
       </c>
       <c r="R137" t="n">
-        <v>6839024</v>
+        <v>6839143</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14541,19 +14525,19 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129739231</v>
+        <v>129739235</v>
       </c>
       <c r="B138" t="n">
         <v>79700</v>
@@ -14588,10 +14572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407422</v>
+        <v>407604</v>
       </c>
       <c r="R138" t="n">
-        <v>6839006</v>
+        <v>6839024</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14650,10 +14634,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129738242</v>
+        <v>129739231</v>
       </c>
       <c r="B139" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14661,21 +14645,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14685,10 +14669,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407719</v>
+        <v>407422</v>
       </c>
       <c r="R139" t="n">
-        <v>6839222</v>
+        <v>6839006</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14735,57 +14719,66 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129739254</v>
+        <v>129738248</v>
       </c>
       <c r="B140" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407418</v>
+        <v>407481</v>
       </c>
       <c r="R140" t="n">
-        <v>6838867</v>
+        <v>6839152</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14826,55 +14819,62 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129739268</v>
+        <v>129738256</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -14882,10 +14882,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407573</v>
+        <v>407616</v>
       </c>
       <c r="R141" t="n">
-        <v>6838884</v>
+        <v>6838794</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14933,12 +14933,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738274</v>
+        <v>129738164</v>
       </c>
       <c r="B148" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15550,21 +15550,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407522</v>
+        <v>407666</v>
       </c>
       <c r="R148" t="n">
-        <v>6839200</v>
+        <v>6839269</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129739288</v>
+        <v>129738153</v>
       </c>
       <c r="B149" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407625</v>
+        <v>407474</v>
       </c>
       <c r="R149" t="n">
-        <v>6839051</v>
+        <v>6839108</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15721,19 +15721,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129738164</v>
+        <v>129738166</v>
       </c>
       <c r="B150" t="n">
         <v>79700</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407666</v>
+        <v>407704</v>
       </c>
       <c r="R150" t="n">
-        <v>6839269</v>
+        <v>6839251</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738153</v>
+        <v>129738274</v>
       </c>
       <c r="B151" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407474</v>
+        <v>407522</v>
       </c>
       <c r="R151" t="n">
-        <v>6839108</v>
+        <v>6839200</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15927,10 +15927,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129738166</v>
+        <v>129739288</v>
       </c>
       <c r="B152" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15938,21 +15938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407704</v>
+        <v>407625</v>
       </c>
       <c r="R152" t="n">
-        <v>6839251</v>
+        <v>6839051</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16012,12 +16012,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129738278</v>
+        <v>129739265</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407601</v>
+        <v>407615</v>
       </c>
       <c r="R16" t="n">
-        <v>6838838</v>
+        <v>6839034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,57 +2564,66 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129739237</v>
+        <v>129738245</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407617</v>
+        <v>407233</v>
       </c>
       <c r="R17" t="n">
-        <v>6839035</v>
+        <v>6838838</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2655,25 +2664,26 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738187</v>
+        <v>129738159</v>
       </c>
       <c r="B18" t="n">
         <v>79700</v>
@@ -2708,10 +2718,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407437</v>
+        <v>407516</v>
       </c>
       <c r="R18" t="n">
-        <v>6838840</v>
+        <v>6839209</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2867,10 +2877,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738159</v>
+        <v>129738278</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2878,21 +2888,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2902,10 +2912,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407516</v>
+        <v>407601</v>
       </c>
       <c r="R20" t="n">
-        <v>6839209</v>
+        <v>6838838</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2964,10 +2974,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129739257</v>
+        <v>129739237</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,42 +2985,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407574</v>
+        <v>407617</v>
       </c>
       <c r="R21" t="n">
-        <v>6839050</v>
+        <v>6839035</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3069,10 +3071,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738266</v>
+        <v>129738187</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,42 +3082,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407598</v>
+        <v>407437</v>
       </c>
       <c r="R22" t="n">
-        <v>6838839</v>
+        <v>6838840</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3174,7 +3168,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739256</v>
+        <v>129739257</v>
       </c>
       <c r="B23" t="n">
         <v>57736</v>
@@ -3207,7 +3201,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3217,10 +3211,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407082</v>
+        <v>407574</v>
       </c>
       <c r="R23" t="n">
-        <v>6838747</v>
+        <v>6839050</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,41 +3273,40 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738245</v>
+        <v>129738266</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3323,10 +3316,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407233</v>
+        <v>407598</v>
       </c>
       <c r="R24" t="n">
-        <v>6838838</v>
+        <v>6838839</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3367,7 +3360,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3386,10 +3378,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129739265</v>
+        <v>129739256</v>
       </c>
       <c r="B25" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,34 +3389,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407615</v>
+        <v>407082</v>
       </c>
       <c r="R25" t="n">
-        <v>6839034</v>
+        <v>6838747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129739233</v>
+        <v>129738154</v>
       </c>
       <c r="B26" t="n">
         <v>79700</v>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407429</v>
+        <v>407536</v>
       </c>
       <c r="R26" t="n">
-        <v>6839067</v>
+        <v>6839138</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3568,12 +3568,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129739266</v>
+        <v>129739291</v>
       </c>
       <c r="B28" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407649</v>
+        <v>407656</v>
       </c>
       <c r="R28" t="n">
-        <v>6838875</v>
+        <v>6839031</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3774,10 +3774,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129739291</v>
+        <v>129739233</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,21 +3785,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407656</v>
+        <v>407429</v>
       </c>
       <c r="R29" t="n">
-        <v>6839031</v>
+        <v>6839067</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129738154</v>
+        <v>129739266</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407536</v>
+        <v>407649</v>
       </c>
       <c r="R30" t="n">
-        <v>6839138</v>
+        <v>6838875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,19 +3956,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129739227</v>
+        <v>129738179</v>
       </c>
       <c r="B31" t="n">
         <v>79700</v>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407211</v>
+        <v>407483</v>
       </c>
       <c r="R31" t="n">
-        <v>6839027</v>
+        <v>6838820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,19 +4053,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129738155</v>
+        <v>129739227</v>
       </c>
       <c r="B32" t="n">
         <v>79700</v>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407503</v>
+        <v>407211</v>
       </c>
       <c r="R32" t="n">
-        <v>6839131</v>
+        <v>6839027</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,19 +4150,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129738179</v>
+        <v>129738155</v>
       </c>
       <c r="B33" t="n">
         <v>79700</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407483</v>
+        <v>407503</v>
       </c>
       <c r="R33" t="n">
-        <v>6838820</v>
+        <v>6839131</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4453,54 +4453,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738246</v>
+        <v>129738158</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407154</v>
+        <v>407519</v>
       </c>
       <c r="R36" t="n">
-        <v>6838842</v>
+        <v>6839207</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4541,7 +4532,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4560,54 +4550,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129739270</v>
+        <v>129739271</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>78838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407283</v>
+        <v>407647</v>
       </c>
       <c r="R37" t="n">
-        <v>6839055</v>
+        <v>6838874</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4648,7 +4629,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4764,10 +4744,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738149</v>
+        <v>129738287</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4775,21 +4755,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4799,10 +4779,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407199</v>
+        <v>407591</v>
       </c>
       <c r="R39" t="n">
-        <v>6838976</v>
+        <v>6838814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,10 +4841,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738158</v>
+        <v>129738283</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4872,34 +4852,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407519</v>
+        <v>407598</v>
       </c>
       <c r="R40" t="n">
-        <v>6839207</v>
+        <v>6838839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4934,12 +4917,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4958,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738287</v>
+        <v>129738149</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4969,21 +4958,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4993,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407591</v>
+        <v>407199</v>
       </c>
       <c r="R41" t="n">
-        <v>6838814</v>
+        <v>6838976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5055,37 +5044,43 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129738283</v>
+        <v>129739270</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5093,10 +5088,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407598</v>
+        <v>407283</v>
       </c>
       <c r="R42" t="n">
-        <v>6838839</v>
+        <v>6839055</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5131,11 +5126,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5149,57 +5139,66 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129739271</v>
+        <v>129738246</v>
       </c>
       <c r="B43" t="n">
-        <v>78838</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407647</v>
+        <v>407154</v>
       </c>
       <c r="R43" t="n">
-        <v>6838874</v>
+        <v>6838842</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5240,28 +5239,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738292</v>
+        <v>129738186</v>
       </c>
       <c r="B44" t="n">
-        <v>78747</v>
+        <v>79700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407528</v>
+        <v>407479</v>
       </c>
       <c r="R44" t="n">
-        <v>6839142</v>
+        <v>6838810</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738204</v>
+        <v>129739240</v>
       </c>
       <c r="B45" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,42 +5366,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407170</v>
+        <v>407581</v>
       </c>
       <c r="R45" t="n">
-        <v>6838942</v>
+        <v>6838885</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5448,66 +5440,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738247</v>
+        <v>129738292</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>78747</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407158</v>
+        <v>407528</v>
       </c>
       <c r="R46" t="n">
-        <v>6838902</v>
+        <v>6839142</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5548,7 +5531,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5567,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129739240</v>
+        <v>129738290</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5578,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5584,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407581</v>
+        <v>407575</v>
       </c>
       <c r="R47" t="n">
-        <v>6838885</v>
+        <v>6838839</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5652,22 +5634,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738186</v>
+        <v>129738204</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5675,34 +5657,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407479</v>
+        <v>407170</v>
       </c>
       <c r="R48" t="n">
-        <v>6838810</v>
+        <v>6838942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5761,45 +5751,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129738290</v>
+        <v>129738247</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407575</v>
+        <v>407158</v>
       </c>
       <c r="R49" t="n">
-        <v>6838839</v>
+        <v>6838902</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5840,6 +5839,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5959,10 +5959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129738152</v>
+        <v>129738196</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5970,21 +5970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407440</v>
+        <v>407436</v>
       </c>
       <c r="R51" t="n">
-        <v>6839113</v>
+        <v>6838838</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129739234</v>
+        <v>129738152</v>
       </c>
       <c r="B52" t="n">
         <v>79700</v>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407466</v>
+        <v>407440</v>
       </c>
       <c r="R52" t="n">
-        <v>6839082</v>
+        <v>6839113</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6141,22 +6141,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129738196</v>
+        <v>129739234</v>
       </c>
       <c r="B53" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407436</v>
+        <v>407466</v>
       </c>
       <c r="R53" t="n">
-        <v>6838838</v>
+        <v>6839082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6238,22 +6238,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738198</v>
+        <v>129739229</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,42 +6261,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407575</v>
+        <v>407296</v>
       </c>
       <c r="R54" t="n">
-        <v>6838839</v>
+        <v>6838974</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6343,12 +6335,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6559,10 +6551,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738291</v>
+        <v>129738168</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6570,21 +6562,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6594,10 +6586,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407574</v>
+        <v>407717</v>
       </c>
       <c r="R57" t="n">
-        <v>6838848</v>
+        <v>6839236</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6656,10 +6648,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738168</v>
+        <v>129738291</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6667,21 +6659,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6691,10 +6683,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407717</v>
+        <v>407574</v>
       </c>
       <c r="R58" t="n">
-        <v>6839236</v>
+        <v>6838848</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6753,10 +6745,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129739229</v>
+        <v>129738198</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6764,34 +6756,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407296</v>
+        <v>407575</v>
       </c>
       <c r="R59" t="n">
-        <v>6838974</v>
+        <v>6838839</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6838,22 +6838,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129739232</v>
+        <v>129738289</v>
       </c>
       <c r="B60" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6861,21 +6861,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407441</v>
+        <v>407581</v>
       </c>
       <c r="R60" t="n">
-        <v>6839017</v>
+        <v>6838815</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6935,22 +6935,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129739244</v>
+        <v>129738277</v>
       </c>
       <c r="B61" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6958,21 +6958,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407448</v>
+        <v>407593</v>
       </c>
       <c r="R61" t="n">
-        <v>6838869</v>
+        <v>6838795</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7032,22 +7032,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129738289</v>
+        <v>129738189</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407581</v>
+        <v>407407</v>
       </c>
       <c r="R62" t="n">
-        <v>6838815</v>
+        <v>6838839</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7141,10 +7141,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129738277</v>
+        <v>129739232</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407593</v>
+        <v>407441</v>
       </c>
       <c r="R63" t="n">
-        <v>6838795</v>
+        <v>6839017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7226,19 +7226,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129739228</v>
+        <v>129739244</v>
       </c>
       <c r="B64" t="n">
         <v>79700</v>
@@ -7273,10 +7273,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407244</v>
+        <v>407448</v>
       </c>
       <c r="R64" t="n">
-        <v>6839107</v>
+        <v>6838869</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129738189</v>
+        <v>129739228</v>
       </c>
       <c r="B65" t="n">
         <v>79700</v>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407407</v>
+        <v>407244</v>
       </c>
       <c r="R65" t="n">
-        <v>6838839</v>
+        <v>6839107</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7420,12 +7420,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129738199</v>
+        <v>129738169</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7550,42 +7550,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407576</v>
+        <v>407672</v>
       </c>
       <c r="R67" t="n">
-        <v>6838847</v>
+        <v>6838825</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7745,45 +7737,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129738169</v>
+        <v>129738257</v>
       </c>
       <c r="B69" t="n">
-        <v>79700</v>
+        <v>58106</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407672</v>
+        <v>407464</v>
       </c>
       <c r="R69" t="n">
-        <v>6838825</v>
+        <v>6839159</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8036,27 +8036,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129738257</v>
+        <v>129738199</v>
       </c>
       <c r="B72" t="n">
-        <v>58106</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8069,7 +8069,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407464</v>
+        <v>407576</v>
       </c>
       <c r="R72" t="n">
-        <v>6839159</v>
+        <v>6838847</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8335,10 +8335,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738285</v>
+        <v>129738181</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407587</v>
+        <v>407467</v>
       </c>
       <c r="R75" t="n">
-        <v>6838806</v>
+        <v>6838834</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738147</v>
+        <v>129738171</v>
       </c>
       <c r="B76" t="n">
         <v>79700</v>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407190</v>
+        <v>407620</v>
       </c>
       <c r="R76" t="n">
-        <v>6838950</v>
+        <v>6838898</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738171</v>
+        <v>129738147</v>
       </c>
       <c r="B78" t="n">
         <v>79700</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407620</v>
+        <v>407190</v>
       </c>
       <c r="R78" t="n">
-        <v>6838898</v>
+        <v>6838950</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738181</v>
+        <v>129738275</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8734,21 +8734,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407467</v>
+        <v>407608</v>
       </c>
       <c r="R79" t="n">
-        <v>6838834</v>
+        <v>6839252</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738194</v>
+        <v>129738285</v>
       </c>
       <c r="B80" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8831,21 +8831,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407549</v>
+        <v>407587</v>
       </c>
       <c r="R80" t="n">
-        <v>6838809</v>
+        <v>6838806</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,10 +8917,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738275</v>
+        <v>129738194</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8928,21 +8928,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8952,10 +8952,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407608</v>
+        <v>407549</v>
       </c>
       <c r="R81" t="n">
-        <v>6839252</v>
+        <v>6838809</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9218,7 +9218,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738143</v>
+        <v>129738148</v>
       </c>
       <c r="B84" t="n">
         <v>79700</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407137</v>
+        <v>407233</v>
       </c>
       <c r="R84" t="n">
-        <v>6838823</v>
+        <v>6838964</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9315,7 +9315,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738165</v>
+        <v>129738143</v>
       </c>
       <c r="B85" t="n">
         <v>79700</v>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407691</v>
+        <v>407137</v>
       </c>
       <c r="R85" t="n">
-        <v>6839279</v>
+        <v>6838823</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9412,7 +9412,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129739238</v>
+        <v>129738165</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407627</v>
+        <v>407691</v>
       </c>
       <c r="R86" t="n">
-        <v>6839039</v>
+        <v>6839279</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,19 +9497,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129738148</v>
+        <v>129739238</v>
       </c>
       <c r="B87" t="n">
         <v>79700</v>
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407233</v>
+        <v>407627</v>
       </c>
       <c r="R87" t="n">
-        <v>6838964</v>
+        <v>6839039</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9594,12 +9594,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9808,7 +9808,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129739246</v>
+        <v>129738188</v>
       </c>
       <c r="B90" t="n">
         <v>79700</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407427</v>
+        <v>407408</v>
       </c>
       <c r="R90" t="n">
-        <v>6838886</v>
+        <v>6838841</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9893,57 +9893,66 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739239</v>
+        <v>129738227</v>
       </c>
       <c r="B91" t="n">
-        <v>79700</v>
+        <v>5480</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407614</v>
+        <v>407545</v>
       </c>
       <c r="R91" t="n">
-        <v>6838900</v>
+        <v>6839241</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9984,18 +9993,19 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10099,10 +10109,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129738188</v>
+        <v>129739255</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10110,21 +10120,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10134,10 +10144,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407408</v>
+        <v>407411</v>
       </c>
       <c r="R93" t="n">
-        <v>6838841</v>
+        <v>6838819</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10184,22 +10194,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129739258</v>
+        <v>129739246</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10207,42 +10217,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407616</v>
+        <v>407427</v>
       </c>
       <c r="R94" t="n">
-        <v>6838890</v>
+        <v>6838886</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10301,54 +10303,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129738227</v>
+        <v>129739239</v>
       </c>
       <c r="B95" t="n">
-        <v>5480</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407545</v>
+        <v>407614</v>
       </c>
       <c r="R95" t="n">
-        <v>6839241</v>
+        <v>6838900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10389,29 +10382,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129739255</v>
+        <v>129739258</v>
       </c>
       <c r="B96" t="n">
-        <v>79671</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10419,34 +10411,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407411</v>
+        <v>407616</v>
       </c>
       <c r="R96" t="n">
-        <v>6838819</v>
+        <v>6838890</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10505,54 +10505,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129738250</v>
+        <v>129739289</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407525</v>
+        <v>407649</v>
       </c>
       <c r="R97" t="n">
-        <v>6839244</v>
+        <v>6839041</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10593,19 +10584,18 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10806,10 +10796,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129739289</v>
+        <v>129738172</v>
       </c>
       <c r="B100" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10817,21 +10807,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10841,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407649</v>
+        <v>407585</v>
       </c>
       <c r="R100" t="n">
-        <v>6839041</v>
+        <v>6838872</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10891,19 +10881,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129738172</v>
+        <v>129739242</v>
       </c>
       <c r="B101" t="n">
         <v>79700</v>
@@ -10938,10 +10928,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407585</v>
+        <v>407515</v>
       </c>
       <c r="R101" t="n">
-        <v>6838872</v>
+        <v>6838875</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10988,57 +10978,66 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129739242</v>
+        <v>129738250</v>
       </c>
       <c r="B102" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407515</v>
+        <v>407525</v>
       </c>
       <c r="R102" t="n">
-        <v>6838875</v>
+        <v>6839244</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11079,18 +11078,19 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11679,7 +11679,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738180</v>
+        <v>129738175</v>
       </c>
       <c r="B109" t="n">
         <v>79700</v>
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407480</v>
+        <v>407547</v>
       </c>
       <c r="R109" t="n">
-        <v>6838840</v>
+        <v>6838816</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11873,7 +11873,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129738190</v>
+        <v>129738180</v>
       </c>
       <c r="B111" t="n">
         <v>79700</v>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>407412</v>
+        <v>407480</v>
       </c>
       <c r="R111" t="n">
-        <v>6838831</v>
+        <v>6838840</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,10 +11970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129738175</v>
+        <v>129738268</v>
       </c>
       <c r="B112" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11981,34 +11981,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>407547</v>
+        <v>407593</v>
       </c>
       <c r="R112" t="n">
-        <v>6838816</v>
+        <v>6838811</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12067,40 +12075,41 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129738268</v>
+        <v>129738249</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12110,10 +12119,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>407593</v>
+        <v>407512</v>
       </c>
       <c r="R113" t="n">
-        <v>6838811</v>
+        <v>6839241</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12154,6 +12163,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12172,54 +12182,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129738249</v>
+        <v>129738190</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>407512</v>
+        <v>407412</v>
       </c>
       <c r="R114" t="n">
-        <v>6839241</v>
+        <v>6838831</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12260,7 +12261,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129739243</v>
+        <v>129738192</v>
       </c>
       <c r="B115" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,21 +12290,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407451</v>
+        <v>407464</v>
       </c>
       <c r="R115" t="n">
-        <v>6838866</v>
+        <v>6839157</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12364,12 +12364,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129739224</v>
+        <v>129739290</v>
       </c>
       <c r="B117" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12493,34 +12493,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407121</v>
+        <v>407657</v>
       </c>
       <c r="R117" t="n">
-        <v>6838895</v>
+        <v>6839033</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12555,12 +12558,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12579,7 +12588,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129739290</v>
+        <v>129738282</v>
       </c>
       <c r="B118" t="n">
         <v>79081</v>
@@ -12608,19 +12617,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407657</v>
+        <v>407588</v>
       </c>
       <c r="R118" t="n">
-        <v>6839033</v>
+        <v>6838831</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12657,7 +12663,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12666,29 +12672,28 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129738282</v>
+        <v>129738145</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12696,21 +12701,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12720,10 +12725,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407588</v>
+        <v>407194</v>
       </c>
       <c r="R119" t="n">
-        <v>6838831</v>
+        <v>6838873</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12756,11 +12761,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12787,7 +12787,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738145</v>
+        <v>129739243</v>
       </c>
       <c r="B120" t="n">
         <v>79700</v>
@@ -12822,10 +12822,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407194</v>
+        <v>407451</v>
       </c>
       <c r="R120" t="n">
-        <v>6838873</v>
+        <v>6838866</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12872,22 +12872,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129738192</v>
+        <v>129739224</v>
       </c>
       <c r="B121" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12895,21 +12895,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12919,10 +12919,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407464</v>
+        <v>407121</v>
       </c>
       <c r="R121" t="n">
-        <v>6839157</v>
+        <v>6838895</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12969,22 +12969,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739249</v>
+        <v>129739241</v>
       </c>
       <c r="B122" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407437</v>
+        <v>407524</v>
       </c>
       <c r="R122" t="n">
-        <v>6839060</v>
+        <v>6838914</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13078,10 +13078,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129739286</v>
+        <v>129738146</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13089,21 +13089,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407570</v>
+        <v>407163</v>
       </c>
       <c r="R123" t="n">
-        <v>6839041</v>
+        <v>6838891</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13163,19 +13163,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129738279</v>
+        <v>129739286</v>
       </c>
       <c r="B124" t="n">
         <v>79081</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407617</v>
+        <v>407570</v>
       </c>
       <c r="R124" t="n">
-        <v>6838855</v>
+        <v>6839041</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13260,19 +13260,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738288</v>
+        <v>129738279</v>
       </c>
       <c r="B125" t="n">
         <v>79081</v>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407592</v>
+        <v>407617</v>
       </c>
       <c r="R125" t="n">
-        <v>6838822</v>
+        <v>6838855</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,10 +13369,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129738146</v>
+        <v>129738288</v>
       </c>
       <c r="B126" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13380,21 +13380,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407163</v>
+        <v>407592</v>
       </c>
       <c r="R126" t="n">
-        <v>6838891</v>
+        <v>6838822</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13466,10 +13466,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739241</v>
+        <v>129739249</v>
       </c>
       <c r="B127" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407524</v>
+        <v>407437</v>
       </c>
       <c r="R127" t="n">
-        <v>6838914</v>
+        <v>6839060</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13563,45 +13563,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129738242</v>
+        <v>129738256</v>
       </c>
       <c r="B128" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407719</v>
+        <v>407616</v>
       </c>
       <c r="R128" t="n">
-        <v>6839222</v>
+        <v>6838794</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13642,6 +13651,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13660,45 +13670,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129739254</v>
+        <v>129738248</v>
       </c>
       <c r="B129" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407418</v>
+        <v>407481</v>
       </c>
       <c r="R129" t="n">
-        <v>6838867</v>
+        <v>6839152</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13739,25 +13758,26 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129739268</v>
+        <v>129738242</v>
       </c>
       <c r="B130" t="n">
         <v>78839</v>
@@ -13786,19 +13806,16 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407573</v>
+        <v>407719</v>
       </c>
       <c r="R130" t="n">
-        <v>6838884</v>
+        <v>6839222</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13839,29 +13856,28 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738157</v>
+        <v>129739254</v>
       </c>
       <c r="B131" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13869,21 +13885,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13893,10 +13909,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407535</v>
+        <v>407418</v>
       </c>
       <c r="R131" t="n">
-        <v>6839193</v>
+        <v>6838867</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13943,22 +13959,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129739287</v>
+        <v>129739268</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13966,34 +13982,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407622</v>
+        <v>407573</v>
       </c>
       <c r="R132" t="n">
-        <v>6839045</v>
+        <v>6838884</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14034,6 +14053,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14052,10 +14072,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738281</v>
+        <v>129738151</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14063,21 +14083,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14087,10 +14107,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407587</v>
+        <v>407378</v>
       </c>
       <c r="R133" t="n">
-        <v>6838872</v>
+        <v>6839143</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14149,7 +14169,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738177</v>
+        <v>129738156</v>
       </c>
       <c r="B134" t="n">
         <v>79700</v>
@@ -14184,10 +14204,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407476</v>
+        <v>407477</v>
       </c>
       <c r="R134" t="n">
-        <v>6838854</v>
+        <v>6839132</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14246,7 +14266,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129738156</v>
+        <v>129738177</v>
       </c>
       <c r="B135" t="n">
         <v>79700</v>
@@ -14281,10 +14301,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407477</v>
+        <v>407476</v>
       </c>
       <c r="R135" t="n">
-        <v>6839132</v>
+        <v>6838854</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14343,10 +14363,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129739230</v>
+        <v>129738281</v>
       </c>
       <c r="B136" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14354,21 +14374,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14378,10 +14398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407404</v>
+        <v>407587</v>
       </c>
       <c r="R136" t="n">
-        <v>6839005</v>
+        <v>6838872</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14428,19 +14448,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129738151</v>
+        <v>129739235</v>
       </c>
       <c r="B137" t="n">
         <v>79700</v>
@@ -14475,10 +14495,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407378</v>
+        <v>407604</v>
       </c>
       <c r="R137" t="n">
-        <v>6839143</v>
+        <v>6839024</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14525,22 +14545,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129739235</v>
+        <v>129739287</v>
       </c>
       <c r="B138" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14548,21 +14568,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14572,10 +14592,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407604</v>
+        <v>407622</v>
       </c>
       <c r="R138" t="n">
-        <v>6839024</v>
+        <v>6839045</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14634,7 +14654,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129739231</v>
+        <v>129739230</v>
       </c>
       <c r="B139" t="n">
         <v>79700</v>
@@ -14669,10 +14689,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407422</v>
+        <v>407404</v>
       </c>
       <c r="R139" t="n">
-        <v>6839006</v>
+        <v>6839005</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14731,54 +14751,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129738248</v>
+        <v>129738157</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407481</v>
+        <v>407535</v>
       </c>
       <c r="R140" t="n">
-        <v>6839152</v>
+        <v>6839193</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14819,7 +14830,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14838,54 +14848,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129738256</v>
+        <v>129739231</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407616</v>
+        <v>407422</v>
       </c>
       <c r="R141" t="n">
-        <v>6838794</v>
+        <v>6839006</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14926,19 +14927,18 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15236,10 +15236,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129739253</v>
+        <v>129738201</v>
       </c>
       <c r="B145" t="n">
-        <v>79671</v>
+        <v>57896</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15247,26 +15247,31 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15274,10 +15279,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407589</v>
+        <v>407530</v>
       </c>
       <c r="R145" t="n">
-        <v>6838889</v>
+        <v>6839196</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15318,26 +15323,25 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129738195</v>
+        <v>129739253</v>
       </c>
       <c r="B146" t="n">
         <v>79671</v>
@@ -15366,16 +15370,19 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407479</v>
+        <v>407589</v>
       </c>
       <c r="R146" t="n">
-        <v>6838852</v>
+        <v>6838889</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15416,28 +15423,29 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738201</v>
+        <v>129738195</v>
       </c>
       <c r="B147" t="n">
-        <v>57896</v>
+        <v>79671</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15445,42 +15453,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407530</v>
+        <v>407479</v>
       </c>
       <c r="R147" t="n">
-        <v>6839196</v>
+        <v>6838852</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129739265</v>
+        <v>129738278</v>
       </c>
       <c r="B16" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407615</v>
+        <v>407601</v>
       </c>
       <c r="R16" t="n">
-        <v>6839034</v>
+        <v>6838838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,66 +2564,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129738245</v>
+        <v>129738159</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407233</v>
+        <v>407516</v>
       </c>
       <c r="R17" t="n">
-        <v>6838838</v>
+        <v>6839209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2664,7 +2655,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2683,7 +2673,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738159</v>
+        <v>129739237</v>
       </c>
       <c r="B18" t="n">
         <v>79700</v>
@@ -2718,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407516</v>
+        <v>407617</v>
       </c>
       <c r="R18" t="n">
-        <v>6839209</v>
+        <v>6839035</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2768,19 +2758,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738167</v>
+        <v>129738187</v>
       </c>
       <c r="B19" t="n">
         <v>79700</v>
@@ -2815,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407714</v>
+        <v>407437</v>
       </c>
       <c r="R19" t="n">
-        <v>6839244</v>
+        <v>6838840</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2877,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738278</v>
+        <v>129738167</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2888,21 +2878,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2912,10 +2902,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407601</v>
+        <v>407714</v>
       </c>
       <c r="R20" t="n">
-        <v>6838838</v>
+        <v>6839244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2974,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129739237</v>
+        <v>129738266</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2985,34 +2975,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407617</v>
+        <v>407598</v>
       </c>
       <c r="R21" t="n">
-        <v>6839035</v>
+        <v>6838839</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3059,22 +3057,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738187</v>
+        <v>129739265</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3082,21 +3080,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3106,10 +3104,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407437</v>
+        <v>407615</v>
       </c>
       <c r="R22" t="n">
-        <v>6838840</v>
+        <v>6839034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,12 +3154,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3273,7 +3271,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738266</v>
+        <v>129739256</v>
       </c>
       <c r="B24" t="n">
         <v>57736</v>
@@ -3306,7 +3304,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3316,10 +3314,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407598</v>
+        <v>407082</v>
       </c>
       <c r="R24" t="n">
-        <v>6838839</v>
+        <v>6838747</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3366,52 +3364,53 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129739256</v>
+        <v>129738245</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3421,10 +3420,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407082</v>
+        <v>407233</v>
       </c>
       <c r="R25" t="n">
-        <v>6838747</v>
+        <v>6838838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3465,28 +3464,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129738154</v>
+        <v>129739266</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,21 +3494,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407536</v>
+        <v>407649</v>
       </c>
       <c r="R26" t="n">
-        <v>6839138</v>
+        <v>6838875</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3568,22 +3568,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129739272</v>
+        <v>129739291</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,21 +3591,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407597</v>
+        <v>407656</v>
       </c>
       <c r="R27" t="n">
-        <v>6838888</v>
+        <v>6839031</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129739291</v>
+        <v>129739233</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407656</v>
+        <v>407429</v>
       </c>
       <c r="R28" t="n">
-        <v>6839031</v>
+        <v>6839067</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129739233</v>
+        <v>129738154</v>
       </c>
       <c r="B29" t="n">
         <v>79700</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407429</v>
+        <v>407536</v>
       </c>
       <c r="R29" t="n">
-        <v>6839067</v>
+        <v>6839138</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,22 +3859,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129739266</v>
+        <v>129739272</v>
       </c>
       <c r="B30" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407649</v>
+        <v>407597</v>
       </c>
       <c r="R30" t="n">
-        <v>6838875</v>
+        <v>6838888</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3968,10 +3968,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129738179</v>
+        <v>129738197</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407483</v>
+        <v>407408</v>
       </c>
       <c r="R31" t="n">
-        <v>6838820</v>
+        <v>6838841</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129739227</v>
+        <v>129739248</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407211</v>
+        <v>407440</v>
       </c>
       <c r="R32" t="n">
         <v>6839027</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129738155</v>
+        <v>129739227</v>
       </c>
       <c r="B33" t="n">
         <v>79700</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407503</v>
+        <v>407211</v>
       </c>
       <c r="R33" t="n">
-        <v>6839131</v>
+        <v>6839027</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,22 +4247,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129738197</v>
+        <v>129738155</v>
       </c>
       <c r="B34" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407408</v>
+        <v>407503</v>
       </c>
       <c r="R34" t="n">
-        <v>6838841</v>
+        <v>6839131</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129739248</v>
+        <v>129738179</v>
       </c>
       <c r="B35" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,21 +4367,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407440</v>
+        <v>407483</v>
       </c>
       <c r="R35" t="n">
-        <v>6839027</v>
+        <v>6838820</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,22 +4441,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738158</v>
+        <v>129738287</v>
       </c>
       <c r="B36" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4464,21 +4464,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407519</v>
+        <v>407591</v>
       </c>
       <c r="R36" t="n">
-        <v>6839207</v>
+        <v>6838814</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129739271</v>
+        <v>129738283</v>
       </c>
       <c r="B37" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4561,34 +4561,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407647</v>
+        <v>407598</v>
       </c>
       <c r="R37" t="n">
-        <v>6838874</v>
+        <v>6838839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4623,31 +4626,37 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129738184</v>
+        <v>129738158</v>
       </c>
       <c r="B38" t="n">
         <v>79700</v>
@@ -4682,10 +4691,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407445</v>
+        <v>407519</v>
       </c>
       <c r="R38" t="n">
-        <v>6838844</v>
+        <v>6839207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4744,10 +4753,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738287</v>
+        <v>129739271</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4755,21 +4764,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4779,10 +4788,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407591</v>
+        <v>407647</v>
       </c>
       <c r="R39" t="n">
-        <v>6838814</v>
+        <v>6838874</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4829,22 +4838,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738283</v>
+        <v>129738149</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4852,37 +4861,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407598</v>
+        <v>407199</v>
       </c>
       <c r="R40" t="n">
-        <v>6838839</v>
+        <v>6838976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4917,18 +4923,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4947,7 +4947,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738149</v>
+        <v>129738184</v>
       </c>
       <c r="B41" t="n">
         <v>79700</v>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407199</v>
+        <v>407445</v>
       </c>
       <c r="R41" t="n">
-        <v>6838976</v>
+        <v>6838844</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5044,7 +5044,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129739270</v>
+        <v>129738246</v>
       </c>
       <c r="B42" t="n">
         <v>8450</v>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407283</v>
+        <v>407154</v>
       </c>
       <c r="R42" t="n">
-        <v>6839055</v>
+        <v>6838842</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,19 +5139,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129738246</v>
+        <v>129739270</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407154</v>
+        <v>407283</v>
       </c>
       <c r="R43" t="n">
-        <v>6838842</v>
+        <v>6839055</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5246,22 +5246,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738186</v>
+        <v>129738292</v>
       </c>
       <c r="B44" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407479</v>
+        <v>407528</v>
       </c>
       <c r="R44" t="n">
-        <v>6838810</v>
+        <v>6839142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129739240</v>
+        <v>129738290</v>
       </c>
       <c r="B45" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407581</v>
+        <v>407575</v>
       </c>
       <c r="R45" t="n">
-        <v>6838885</v>
+        <v>6838839</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5440,22 +5440,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738292</v>
+        <v>129738186</v>
       </c>
       <c r="B46" t="n">
-        <v>78747</v>
+        <v>79700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407528</v>
+        <v>407479</v>
       </c>
       <c r="R46" t="n">
-        <v>6839142</v>
+        <v>6838810</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738290</v>
+        <v>129739240</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407575</v>
+        <v>407581</v>
       </c>
       <c r="R47" t="n">
-        <v>6838839</v>
+        <v>6838885</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5634,12 +5634,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5959,10 +5959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129738196</v>
+        <v>129739234</v>
       </c>
       <c r="B51" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5970,21 +5970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407436</v>
+        <v>407466</v>
       </c>
       <c r="R51" t="n">
-        <v>6838838</v>
+        <v>6839082</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6044,12 +6044,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129739234</v>
+        <v>129738196</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407466</v>
+        <v>407436</v>
       </c>
       <c r="R53" t="n">
-        <v>6839082</v>
+        <v>6838838</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6238,57 +6238,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129739229</v>
+        <v>129738255</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407296</v>
+        <v>407645</v>
       </c>
       <c r="R54" t="n">
-        <v>6838974</v>
+        <v>6838797</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6329,59 +6338,59 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738255</v>
+        <v>129738198</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6391,10 +6400,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407645</v>
+        <v>407575</v>
       </c>
       <c r="R55" t="n">
-        <v>6838797</v>
+        <v>6838839</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6435,7 +6444,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6454,10 +6462,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738160</v>
+        <v>129738291</v>
       </c>
       <c r="B56" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6465,21 +6473,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6489,10 +6497,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407512</v>
+        <v>407574</v>
       </c>
       <c r="R56" t="n">
-        <v>6839214</v>
+        <v>6838848</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6551,7 +6559,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738168</v>
+        <v>129738160</v>
       </c>
       <c r="B57" t="n">
         <v>79700</v>
@@ -6586,10 +6594,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407717</v>
+        <v>407512</v>
       </c>
       <c r="R57" t="n">
-        <v>6839236</v>
+        <v>6839214</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6648,10 +6656,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738291</v>
+        <v>129738168</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6659,21 +6667,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6683,10 +6691,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407574</v>
+        <v>407717</v>
       </c>
       <c r="R58" t="n">
-        <v>6838848</v>
+        <v>6839236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6745,10 +6753,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738198</v>
+        <v>129739229</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6756,42 +6764,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407575</v>
+        <v>407296</v>
       </c>
       <c r="R59" t="n">
-        <v>6838839</v>
+        <v>6838974</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6838,12 +6838,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129738169</v>
+        <v>129739292</v>
       </c>
       <c r="B67" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7550,34 +7550,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407672</v>
+        <v>407632</v>
       </c>
       <c r="R67" t="n">
-        <v>6838825</v>
+        <v>6838901</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7618,28 +7621,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129739292</v>
+        <v>129739245</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7647,37 +7651,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407632</v>
+        <v>407443</v>
       </c>
       <c r="R68" t="n">
-        <v>6838901</v>
+        <v>6838872</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7718,7 +7719,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7737,53 +7737,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129738257</v>
+        <v>129739225</v>
       </c>
       <c r="B69" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407464</v>
+        <v>407184</v>
       </c>
       <c r="R69" t="n">
-        <v>6839159</v>
+        <v>6839011</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7830,19 +7822,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129739245</v>
+        <v>129738169</v>
       </c>
       <c r="B70" t="n">
         <v>79700</v>
@@ -7877,10 +7869,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407443</v>
+        <v>407672</v>
       </c>
       <c r="R70" t="n">
-        <v>6838872</v>
+        <v>6838825</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7927,22 +7919,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129739225</v>
+        <v>129738199</v>
       </c>
       <c r="B71" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7950,34 +7942,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407184</v>
+        <v>407576</v>
       </c>
       <c r="R71" t="n">
-        <v>6839011</v>
+        <v>6838847</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8024,39 +8024,39 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129738199</v>
+        <v>129738257</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>58106</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8069,7 +8069,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407576</v>
+        <v>407464</v>
       </c>
       <c r="R72" t="n">
-        <v>6838847</v>
+        <v>6839159</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8723,45 +8723,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738275</v>
+        <v>129738244</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407608</v>
+        <v>407231</v>
       </c>
       <c r="R79" t="n">
-        <v>6839252</v>
+        <v>6838827</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8802,6 +8811,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8820,7 +8830,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738285</v>
+        <v>129738275</v>
       </c>
       <c r="B80" t="n">
         <v>79081</v>
@@ -8855,10 +8865,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407587</v>
+        <v>407608</v>
       </c>
       <c r="R80" t="n">
-        <v>6838806</v>
+        <v>6839252</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,10 +8927,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738194</v>
+        <v>129738285</v>
       </c>
       <c r="B81" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8928,21 +8938,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8952,10 +8962,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407549</v>
+        <v>407587</v>
       </c>
       <c r="R81" t="n">
-        <v>6838809</v>
+        <v>6838806</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9014,54 +9024,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738244</v>
+        <v>129738194</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407231</v>
+        <v>407549</v>
       </c>
       <c r="R82" t="n">
-        <v>6838827</v>
+        <v>6838809</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9102,7 +9103,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9315,7 +9315,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738143</v>
+        <v>129738165</v>
       </c>
       <c r="B85" t="n">
         <v>79700</v>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407137</v>
+        <v>407691</v>
       </c>
       <c r="R85" t="n">
-        <v>6838823</v>
+        <v>6839279</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9412,7 +9412,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129738165</v>
+        <v>129738143</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407691</v>
+        <v>407137</v>
       </c>
       <c r="R86" t="n">
-        <v>6839279</v>
+        <v>6838823</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9905,54 +9905,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129738227</v>
+        <v>129739246</v>
       </c>
       <c r="B91" t="n">
-        <v>5480</v>
+        <v>79700</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407545</v>
+        <v>407427</v>
       </c>
       <c r="R91" t="n">
-        <v>6839241</v>
+        <v>6838886</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9993,19 +9984,18 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10109,10 +10099,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129739255</v>
+        <v>129739239</v>
       </c>
       <c r="B93" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10120,21 +10110,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10144,10 +10134,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407411</v>
+        <v>407614</v>
       </c>
       <c r="R93" t="n">
-        <v>6838819</v>
+        <v>6838900</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10206,10 +10196,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129739246</v>
+        <v>129739258</v>
       </c>
       <c r="B94" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10217,34 +10207,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407427</v>
+        <v>407616</v>
       </c>
       <c r="R94" t="n">
-        <v>6838886</v>
+        <v>6838890</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10303,45 +10301,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129739239</v>
+        <v>129738227</v>
       </c>
       <c r="B95" t="n">
-        <v>79700</v>
+        <v>5480</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407614</v>
+        <v>407545</v>
       </c>
       <c r="R95" t="n">
-        <v>6838900</v>
+        <v>6839241</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10382,28 +10389,29 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129739258</v>
+        <v>129739255</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>79671</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10411,42 +10419,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407616</v>
+        <v>407411</v>
       </c>
       <c r="R96" t="n">
-        <v>6838890</v>
+        <v>6838819</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129739289</v>
+        <v>129738144</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10516,21 +10516,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407649</v>
+        <v>407223</v>
       </c>
       <c r="R97" t="n">
-        <v>6839041</v>
+        <v>6838821</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10590,22 +10590,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129738144</v>
+        <v>129739289</v>
       </c>
       <c r="B98" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10613,21 +10613,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407223</v>
+        <v>407649</v>
       </c>
       <c r="R98" t="n">
-        <v>6838821</v>
+        <v>6839041</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10687,12 +10687,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129738172</v>
+        <v>129739242</v>
       </c>
       <c r="B100" t="n">
         <v>79700</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407585</v>
+        <v>407515</v>
       </c>
       <c r="R100" t="n">
-        <v>6838872</v>
+        <v>6838875</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10881,19 +10881,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129739242</v>
+        <v>129738172</v>
       </c>
       <c r="B101" t="n">
         <v>79700</v>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407515</v>
+        <v>407585</v>
       </c>
       <c r="R101" t="n">
-        <v>6838875</v>
+        <v>6838872</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,12 +10978,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11485,10 +11485,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129739273</v>
+        <v>129738173</v>
       </c>
       <c r="B107" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11496,21 +11496,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>407582</v>
+        <v>407587</v>
       </c>
       <c r="R107" t="n">
-        <v>6838890</v>
+        <v>6838860</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11570,22 +11570,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129738173</v>
+        <v>129739273</v>
       </c>
       <c r="B108" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11593,21 +11593,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>407587</v>
+        <v>407582</v>
       </c>
       <c r="R108" t="n">
-        <v>6838860</v>
+        <v>6838890</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11667,22 +11667,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738175</v>
+        <v>129738276</v>
       </c>
       <c r="B109" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11690,21 +11690,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407547</v>
+        <v>407607</v>
       </c>
       <c r="R109" t="n">
-        <v>6838816</v>
+        <v>6838798</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11776,10 +11776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738276</v>
+        <v>129738180</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407607</v>
+        <v>407480</v>
       </c>
       <c r="R110" t="n">
-        <v>6838798</v>
+        <v>6838840</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11873,7 +11873,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129738180</v>
+        <v>129738175</v>
       </c>
       <c r="B111" t="n">
         <v>79700</v>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>407480</v>
+        <v>407547</v>
       </c>
       <c r="R111" t="n">
-        <v>6838840</v>
+        <v>6838816</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,10 +11970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129738268</v>
+        <v>129738190</v>
       </c>
       <c r="B112" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11981,42 +11981,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>407593</v>
+        <v>407412</v>
       </c>
       <c r="R112" t="n">
-        <v>6838811</v>
+        <v>6838831</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12075,41 +12067,40 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129738249</v>
+        <v>129738268</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12119,10 +12110,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>407512</v>
+        <v>407593</v>
       </c>
       <c r="R113" t="n">
-        <v>6839241</v>
+        <v>6838811</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12163,7 +12154,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12182,45 +12172,54 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129738190</v>
+        <v>129738249</v>
       </c>
       <c r="B114" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>407412</v>
+        <v>407512</v>
       </c>
       <c r="R114" t="n">
-        <v>6838831</v>
+        <v>6839241</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12261,6 +12260,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129738192</v>
+        <v>129738280</v>
       </c>
       <c r="B115" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,34 +12290,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407464</v>
+        <v>407623</v>
       </c>
       <c r="R115" t="n">
-        <v>6839157</v>
+        <v>6838894</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12352,12 +12355,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12376,7 +12385,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129738280</v>
+        <v>129739290</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -12414,10 +12423,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407623</v>
+        <v>407657</v>
       </c>
       <c r="R116" t="n">
-        <v>6838894</v>
+        <v>6839033</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12454,7 +12463,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12470,19 +12479,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129739290</v>
+        <v>129738282</v>
       </c>
       <c r="B117" t="n">
         <v>79081</v>
@@ -12511,19 +12520,16 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407657</v>
+        <v>407588</v>
       </c>
       <c r="R117" t="n">
-        <v>6839033</v>
+        <v>6838831</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12560,7 +12566,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12569,29 +12575,28 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129738282</v>
+        <v>129738145</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12599,21 +12604,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12623,10 +12628,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407588</v>
+        <v>407194</v>
       </c>
       <c r="R118" t="n">
-        <v>6838831</v>
+        <v>6838873</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12659,11 +12664,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12690,7 +12690,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129738145</v>
+        <v>129739243</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407194</v>
+        <v>407451</v>
       </c>
       <c r="R119" t="n">
-        <v>6838873</v>
+        <v>6838866</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12775,19 +12775,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129739243</v>
+        <v>129739224</v>
       </c>
       <c r="B120" t="n">
         <v>79700</v>
@@ -12822,10 +12822,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407451</v>
+        <v>407121</v>
       </c>
       <c r="R120" t="n">
-        <v>6838866</v>
+        <v>6838895</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12884,10 +12884,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129739224</v>
+        <v>129738192</v>
       </c>
       <c r="B121" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12895,21 +12895,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12919,10 +12919,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407121</v>
+        <v>407464</v>
       </c>
       <c r="R121" t="n">
-        <v>6838895</v>
+        <v>6839157</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12969,22 +12969,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739241</v>
+        <v>129739286</v>
       </c>
       <c r="B122" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407524</v>
+        <v>407570</v>
       </c>
       <c r="R122" t="n">
-        <v>6838914</v>
+        <v>6839041</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13078,7 +13078,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129738146</v>
+        <v>129739241</v>
       </c>
       <c r="B123" t="n">
         <v>79700</v>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407163</v>
+        <v>407524</v>
       </c>
       <c r="R123" t="n">
-        <v>6838891</v>
+        <v>6838914</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13163,22 +13163,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129739286</v>
+        <v>129738146</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13186,21 +13186,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407570</v>
+        <v>407163</v>
       </c>
       <c r="R124" t="n">
-        <v>6839041</v>
+        <v>6838891</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13260,22 +13260,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738279</v>
+        <v>129739249</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407617</v>
+        <v>407437</v>
       </c>
       <c r="R125" t="n">
-        <v>6838855</v>
+        <v>6839060</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13357,19 +13357,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129738288</v>
+        <v>129738279</v>
       </c>
       <c r="B126" t="n">
         <v>79081</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407592</v>
+        <v>407617</v>
       </c>
       <c r="R126" t="n">
-        <v>6838822</v>
+        <v>6838855</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13466,10 +13466,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739249</v>
+        <v>129738288</v>
       </c>
       <c r="B127" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407437</v>
+        <v>407592</v>
       </c>
       <c r="R127" t="n">
-        <v>6839060</v>
+        <v>6838822</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13551,66 +13551,57 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129738256</v>
+        <v>129739287</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407616</v>
+        <v>407622</v>
       </c>
       <c r="R128" t="n">
-        <v>6838794</v>
+        <v>6839045</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13651,73 +13642,63 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738248</v>
+        <v>129738281</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407481</v>
+        <v>407587</v>
       </c>
       <c r="R129" t="n">
-        <v>6839152</v>
+        <v>6838872</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13758,7 +13739,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13777,10 +13757,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129738242</v>
+        <v>129739230</v>
       </c>
       <c r="B130" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13788,21 +13768,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13812,10 +13792,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407719</v>
+        <v>407404</v>
       </c>
       <c r="R130" t="n">
-        <v>6839222</v>
+        <v>6839005</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13862,22 +13842,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129739254</v>
+        <v>129738151</v>
       </c>
       <c r="B131" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13885,21 +13865,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13909,10 +13889,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407418</v>
+        <v>407378</v>
       </c>
       <c r="R131" t="n">
-        <v>6838867</v>
+        <v>6839143</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13959,22 +13939,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129739268</v>
+        <v>129738156</v>
       </c>
       <c r="B132" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13982,37 +13962,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407573</v>
+        <v>407477</v>
       </c>
       <c r="R132" t="n">
-        <v>6838884</v>
+        <v>6839132</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14053,26 +14030,25 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738151</v>
+        <v>129738157</v>
       </c>
       <c r="B133" t="n">
         <v>79700</v>
@@ -14107,10 +14083,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407378</v>
+        <v>407535</v>
       </c>
       <c r="R133" t="n">
-        <v>6839143</v>
+        <v>6839193</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14169,7 +14145,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738156</v>
+        <v>129739231</v>
       </c>
       <c r="B134" t="n">
         <v>79700</v>
@@ -14204,10 +14180,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407477</v>
+        <v>407422</v>
       </c>
       <c r="R134" t="n">
-        <v>6839132</v>
+        <v>6839006</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14254,19 +14230,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129738177</v>
+        <v>129739235</v>
       </c>
       <c r="B135" t="n">
         <v>79700</v>
@@ -14301,10 +14277,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407476</v>
+        <v>407604</v>
       </c>
       <c r="R135" t="n">
-        <v>6838854</v>
+        <v>6839024</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14351,22 +14327,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129738281</v>
+        <v>129738177</v>
       </c>
       <c r="B136" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14374,21 +14350,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14398,10 +14374,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407587</v>
+        <v>407476</v>
       </c>
       <c r="R136" t="n">
-        <v>6838872</v>
+        <v>6838854</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14460,45 +14436,54 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129739235</v>
+        <v>129738248</v>
       </c>
       <c r="B137" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407604</v>
+        <v>407481</v>
       </c>
       <c r="R137" t="n">
-        <v>6839024</v>
+        <v>6839152</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14539,63 +14524,73 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129739287</v>
+        <v>129738256</v>
       </c>
       <c r="B138" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407622</v>
+        <v>407616</v>
       </c>
       <c r="R138" t="n">
-        <v>6839045</v>
+        <v>6838794</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14636,28 +14631,29 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129739230</v>
+        <v>129738242</v>
       </c>
       <c r="B139" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14665,21 +14661,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14689,10 +14685,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407404</v>
+        <v>407719</v>
       </c>
       <c r="R139" t="n">
-        <v>6839005</v>
+        <v>6839222</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14739,22 +14735,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129738157</v>
+        <v>129739254</v>
       </c>
       <c r="B140" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14762,21 +14758,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14786,10 +14782,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407535</v>
+        <v>407418</v>
       </c>
       <c r="R140" t="n">
-        <v>6839193</v>
+        <v>6838867</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14836,22 +14832,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129739231</v>
+        <v>129739268</v>
       </c>
       <c r="B141" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14859,34 +14855,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407422</v>
+        <v>407573</v>
       </c>
       <c r="R141" t="n">
-        <v>6839006</v>
+        <v>6838884</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14927,6 +14926,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14945,10 +14945,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738150</v>
+        <v>129738284</v>
       </c>
       <c r="B142" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,21 +14956,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407203</v>
+        <v>407595</v>
       </c>
       <c r="R142" t="n">
-        <v>6839015</v>
+        <v>6838836</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15042,10 +15042,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738286</v>
+        <v>129738201</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15053,34 +15053,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407586</v>
+        <v>407530</v>
       </c>
       <c r="R143" t="n">
-        <v>6838820</v>
+        <v>6839196</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15139,7 +15147,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738284</v>
+        <v>129738286</v>
       </c>
       <c r="B144" t="n">
         <v>79081</v>
@@ -15174,10 +15182,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407595</v>
+        <v>407586</v>
       </c>
       <c r="R144" t="n">
-        <v>6838836</v>
+        <v>6838820</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15236,10 +15244,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738201</v>
+        <v>129738150</v>
       </c>
       <c r="B145" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15247,42 +15255,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407530</v>
+        <v>407203</v>
       </c>
       <c r="R145" t="n">
-        <v>6839196</v>
+        <v>6839015</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738164</v>
+        <v>129738274</v>
       </c>
       <c r="B148" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15550,21 +15550,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407666</v>
+        <v>407522</v>
       </c>
       <c r="R148" t="n">
-        <v>6839269</v>
+        <v>6839200</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129738153</v>
+        <v>129739288</v>
       </c>
       <c r="B149" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407474</v>
+        <v>407625</v>
       </c>
       <c r="R149" t="n">
-        <v>6839108</v>
+        <v>6839051</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15721,19 +15721,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129738166</v>
+        <v>129738164</v>
       </c>
       <c r="B150" t="n">
         <v>79700</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407704</v>
+        <v>407666</v>
       </c>
       <c r="R150" t="n">
-        <v>6839251</v>
+        <v>6839269</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738274</v>
+        <v>129738153</v>
       </c>
       <c r="B151" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407522</v>
+        <v>407474</v>
       </c>
       <c r="R151" t="n">
-        <v>6839200</v>
+        <v>6839108</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15927,10 +15927,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129739288</v>
+        <v>129738166</v>
       </c>
       <c r="B152" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15938,21 +15938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407625</v>
+        <v>407704</v>
       </c>
       <c r="R152" t="n">
-        <v>6839051</v>
+        <v>6839251</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16012,12 +16012,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129738278</v>
+        <v>129739257</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,34 +2490,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407601</v>
+        <v>407574</v>
       </c>
       <c r="R16" t="n">
-        <v>6838838</v>
+        <v>6839050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,22 +2572,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129738159</v>
+        <v>129738266</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,34 +2595,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407516</v>
+        <v>407598</v>
       </c>
       <c r="R17" t="n">
-        <v>6839209</v>
+        <v>6838839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2673,10 +2689,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129739237</v>
+        <v>129738278</v>
       </c>
       <c r="B18" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,21 +2700,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,10 +2724,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407617</v>
+        <v>407601</v>
       </c>
       <c r="R18" t="n">
-        <v>6839035</v>
+        <v>6838838</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2758,19 +2774,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738187</v>
+        <v>129739237</v>
       </c>
       <c r="B19" t="n">
         <v>79700</v>
@@ -2805,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407437</v>
+        <v>407617</v>
       </c>
       <c r="R19" t="n">
-        <v>6838840</v>
+        <v>6839035</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2855,19 +2871,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738167</v>
+        <v>129738187</v>
       </c>
       <c r="B20" t="n">
         <v>79700</v>
@@ -2902,10 +2918,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407714</v>
+        <v>407437</v>
       </c>
       <c r="R20" t="n">
-        <v>6839244</v>
+        <v>6838840</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2964,10 +2980,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738266</v>
+        <v>129738167</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,42 +2991,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407598</v>
+        <v>407714</v>
       </c>
       <c r="R21" t="n">
-        <v>6838839</v>
+        <v>6839244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3069,10 +3077,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129739265</v>
+        <v>129738159</v>
       </c>
       <c r="B22" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,21 +3088,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3104,10 +3112,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407615</v>
+        <v>407516</v>
       </c>
       <c r="R22" t="n">
-        <v>6839034</v>
+        <v>6839209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3154,19 +3162,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739257</v>
+        <v>129739256</v>
       </c>
       <c r="B23" t="n">
         <v>57736</v>
@@ -3199,7 +3207,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3209,10 +3217,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407574</v>
+        <v>407082</v>
       </c>
       <c r="R23" t="n">
-        <v>6839050</v>
+        <v>6838747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3271,40 +3279,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129739256</v>
+        <v>129738245</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3314,10 +3323,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407082</v>
+        <v>407233</v>
       </c>
       <c r="R24" t="n">
-        <v>6838747</v>
+        <v>6838838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3358,72 +3367,64 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129738245</v>
+        <v>129739265</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407233</v>
+        <v>407615</v>
       </c>
       <c r="R25" t="n">
-        <v>6838838</v>
+        <v>6839034</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3464,29 +3465,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129739266</v>
+        <v>129739291</v>
       </c>
       <c r="B26" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,21 +3494,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407649</v>
+        <v>407656</v>
       </c>
       <c r="R26" t="n">
-        <v>6838875</v>
+        <v>6839031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3580,10 +3580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129739291</v>
+        <v>129739272</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,21 +3591,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407656</v>
+        <v>407597</v>
       </c>
       <c r="R27" t="n">
-        <v>6839031</v>
+        <v>6838888</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129739233</v>
+        <v>129738154</v>
       </c>
       <c r="B28" t="n">
         <v>79700</v>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407429</v>
+        <v>407536</v>
       </c>
       <c r="R28" t="n">
-        <v>6839067</v>
+        <v>6839138</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3762,19 +3762,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129738154</v>
+        <v>129739233</v>
       </c>
       <c r="B29" t="n">
         <v>79700</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407536</v>
+        <v>407429</v>
       </c>
       <c r="R29" t="n">
-        <v>6839138</v>
+        <v>6839067</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,22 +3859,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129739272</v>
+        <v>129739266</v>
       </c>
       <c r="B30" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407597</v>
+        <v>407649</v>
       </c>
       <c r="R30" t="n">
-        <v>6838888</v>
+        <v>6838875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4453,45 +4453,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738287</v>
+        <v>129738246</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407591</v>
+        <v>407154</v>
       </c>
       <c r="R36" t="n">
-        <v>6838814</v>
+        <v>6838842</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4532,6 +4541,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4550,37 +4560,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129738283</v>
+        <v>129739270</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4588,10 +4604,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407598</v>
+        <v>407283</v>
       </c>
       <c r="R37" t="n">
-        <v>6838839</v>
+        <v>6839055</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,11 +4642,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4644,22 +4655,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129738158</v>
+        <v>129738283</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,34 +4678,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407519</v>
+        <v>407598</v>
       </c>
       <c r="R38" t="n">
-        <v>6839207</v>
+        <v>6838839</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4729,12 +4743,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4850,10 +4870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738149</v>
+        <v>129738287</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,21 +4881,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4885,10 +4905,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407199</v>
+        <v>407591</v>
       </c>
       <c r="R40" t="n">
-        <v>6838976</v>
+        <v>6838814</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5044,54 +5064,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129738246</v>
+        <v>129738149</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407154</v>
+        <v>407199</v>
       </c>
       <c r="R42" t="n">
-        <v>6838842</v>
+        <v>6838976</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5132,7 +5143,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5151,54 +5161,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129739270</v>
+        <v>129738158</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407283</v>
+        <v>407519</v>
       </c>
       <c r="R43" t="n">
-        <v>6839055</v>
+        <v>6839207</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,19 +5240,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5452,45 +5452,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738186</v>
+        <v>129738247</v>
       </c>
       <c r="B46" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407479</v>
+        <v>407158</v>
       </c>
       <c r="R46" t="n">
-        <v>6838810</v>
+        <v>6838902</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5531,6 +5540,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5549,10 +5559,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129739240</v>
+        <v>129739250</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,34 +5570,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407581</v>
+        <v>407493</v>
       </c>
       <c r="R47" t="n">
-        <v>6838885</v>
+        <v>6839112</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5628,6 +5641,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5751,54 +5765,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129738247</v>
+        <v>129739240</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407158</v>
+        <v>407581</v>
       </c>
       <c r="R49" t="n">
-        <v>6838902</v>
+        <v>6838885</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5839,29 +5844,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129739250</v>
+        <v>129738186</v>
       </c>
       <c r="B50" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5869,37 +5873,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407493</v>
+        <v>407479</v>
       </c>
       <c r="R50" t="n">
-        <v>6839112</v>
+        <v>6838810</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5940,26 +5941,25 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129739234</v>
+        <v>129738152</v>
       </c>
       <c r="B51" t="n">
         <v>79700</v>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407466</v>
+        <v>407440</v>
       </c>
       <c r="R51" t="n">
-        <v>6839082</v>
+        <v>6839113</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6044,19 +6044,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129738152</v>
+        <v>129739234</v>
       </c>
       <c r="B52" t="n">
         <v>79700</v>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407440</v>
+        <v>407466</v>
       </c>
       <c r="R52" t="n">
-        <v>6839113</v>
+        <v>6839082</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6141,12 +6141,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6250,54 +6250,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738255</v>
+        <v>129738291</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407645</v>
+        <v>407574</v>
       </c>
       <c r="R54" t="n">
-        <v>6838797</v>
+        <v>6838848</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6338,7 +6329,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6357,10 +6347,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738198</v>
+        <v>129738160</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6368,42 +6358,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407575</v>
+        <v>407512</v>
       </c>
       <c r="R55" t="n">
-        <v>6838839</v>
+        <v>6839214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6462,10 +6444,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738291</v>
+        <v>129738168</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6473,21 +6455,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6497,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407574</v>
+        <v>407717</v>
       </c>
       <c r="R56" t="n">
-        <v>6838848</v>
+        <v>6839236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6559,7 +6541,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738160</v>
+        <v>129739229</v>
       </c>
       <c r="B57" t="n">
         <v>79700</v>
@@ -6594,10 +6576,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407512</v>
+        <v>407296</v>
       </c>
       <c r="R57" t="n">
-        <v>6839214</v>
+        <v>6838974</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6644,57 +6626,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738168</v>
+        <v>129738255</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407717</v>
+        <v>407645</v>
       </c>
       <c r="R58" t="n">
-        <v>6839236</v>
+        <v>6838797</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6735,6 +6726,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6753,10 +6745,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129739229</v>
+        <v>129738198</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6764,34 +6756,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407296</v>
+        <v>407575</v>
       </c>
       <c r="R59" t="n">
-        <v>6838974</v>
+        <v>6838839</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6838,12 +6838,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129738189</v>
+        <v>129739232</v>
       </c>
       <c r="B62" t="n">
         <v>79700</v>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407407</v>
+        <v>407441</v>
       </c>
       <c r="R62" t="n">
-        <v>6838839</v>
+        <v>6839017</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7129,19 +7129,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129739232</v>
+        <v>129739244</v>
       </c>
       <c r="B63" t="n">
         <v>79700</v>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407441</v>
+        <v>407448</v>
       </c>
       <c r="R63" t="n">
-        <v>6839017</v>
+        <v>6838869</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129739244</v>
+        <v>129739228</v>
       </c>
       <c r="B64" t="n">
         <v>79700</v>
@@ -7273,10 +7273,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407448</v>
+        <v>407244</v>
       </c>
       <c r="R64" t="n">
-        <v>6838869</v>
+        <v>6839107</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129739228</v>
+        <v>129738189</v>
       </c>
       <c r="B65" t="n">
         <v>79700</v>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407244</v>
+        <v>407407</v>
       </c>
       <c r="R65" t="n">
-        <v>6839107</v>
+        <v>6838839</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7420,12 +7420,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129739245</v>
+        <v>129738169</v>
       </c>
       <c r="B68" t="n">
         <v>79700</v>
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407443</v>
+        <v>407672</v>
       </c>
       <c r="R68" t="n">
-        <v>6838872</v>
+        <v>6838825</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7725,19 +7725,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739225</v>
+        <v>129739245</v>
       </c>
       <c r="B69" t="n">
         <v>79700</v>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407184</v>
+        <v>407443</v>
       </c>
       <c r="R69" t="n">
-        <v>6839011</v>
+        <v>6838872</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7834,7 +7834,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129738169</v>
+        <v>129739225</v>
       </c>
       <c r="B70" t="n">
         <v>79700</v>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407672</v>
+        <v>407184</v>
       </c>
       <c r="R70" t="n">
-        <v>6838825</v>
+        <v>6839011</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7919,12 +7919,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738181</v>
+        <v>129738275</v>
       </c>
       <c r="B75" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407467</v>
+        <v>407608</v>
       </c>
       <c r="R75" t="n">
-        <v>6838834</v>
+        <v>6839252</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738171</v>
+        <v>129738147</v>
       </c>
       <c r="B76" t="n">
         <v>79700</v>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407620</v>
+        <v>407190</v>
       </c>
       <c r="R76" t="n">
-        <v>6838898</v>
+        <v>6838950</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738147</v>
+        <v>129738171</v>
       </c>
       <c r="B78" t="n">
         <v>79700</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407190</v>
+        <v>407620</v>
       </c>
       <c r="R78" t="n">
-        <v>6838950</v>
+        <v>6838898</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,54 +8723,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738244</v>
+        <v>129738181</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407231</v>
+        <v>407467</v>
       </c>
       <c r="R79" t="n">
-        <v>6838827</v>
+        <v>6838834</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8811,7 +8802,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8830,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738275</v>
+        <v>129738194</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8841,21 +8831,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8865,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407608</v>
+        <v>407549</v>
       </c>
       <c r="R80" t="n">
-        <v>6839252</v>
+        <v>6838809</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9024,45 +9014,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B82" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R82" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,6 +9102,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9218,7 +9218,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738148</v>
+        <v>129738143</v>
       </c>
       <c r="B84" t="n">
         <v>79700</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407233</v>
+        <v>407137</v>
       </c>
       <c r="R84" t="n">
-        <v>6838964</v>
+        <v>6838823</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9412,7 +9412,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129738143</v>
+        <v>129739238</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407137</v>
+        <v>407627</v>
       </c>
       <c r="R86" t="n">
-        <v>6838823</v>
+        <v>6839039</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,19 +9497,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129739238</v>
+        <v>129738148</v>
       </c>
       <c r="B87" t="n">
         <v>79700</v>
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407627</v>
+        <v>407233</v>
       </c>
       <c r="R87" t="n">
-        <v>6839039</v>
+        <v>6838964</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9594,22 +9594,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129739259</v>
+        <v>129739267</v>
       </c>
       <c r="B88" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,42 +9617,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407549</v>
+        <v>407597</v>
       </c>
       <c r="R88" t="n">
-        <v>6839053</v>
+        <v>6838888</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9711,10 +9703,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129739267</v>
+        <v>129739259</v>
       </c>
       <c r="B89" t="n">
-        <v>78839</v>
+        <v>57896</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9722,34 +9714,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407597</v>
+        <v>407549</v>
       </c>
       <c r="R89" t="n">
-        <v>6838888</v>
+        <v>6839053</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129738188</v>
+        <v>129739255</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9819,21 +9819,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407408</v>
+        <v>407411</v>
       </c>
       <c r="R90" t="n">
-        <v>6838841</v>
+        <v>6838819</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9893,22 +9893,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739246</v>
+        <v>129739258</v>
       </c>
       <c r="B91" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9916,34 +9916,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407427</v>
+        <v>407616</v>
       </c>
       <c r="R91" t="n">
-        <v>6838886</v>
+        <v>6838890</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10002,7 +10010,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129738170</v>
+        <v>129739246</v>
       </c>
       <c r="B92" t="n">
         <v>79700</v>
@@ -10037,10 +10045,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407660</v>
+        <v>407427</v>
       </c>
       <c r="R92" t="n">
-        <v>6838791</v>
+        <v>6838886</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10087,12 +10095,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10196,10 +10204,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129739258</v>
+        <v>129738170</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10207,42 +10215,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407616</v>
+        <v>407660</v>
       </c>
       <c r="R94" t="n">
-        <v>6838890</v>
+        <v>6838791</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10289,66 +10289,57 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129738227</v>
+        <v>129738188</v>
       </c>
       <c r="B95" t="n">
-        <v>5480</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407545</v>
+        <v>407408</v>
       </c>
       <c r="R95" t="n">
-        <v>6839241</v>
+        <v>6838841</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10389,7 +10380,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10408,45 +10398,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129739255</v>
+        <v>129738227</v>
       </c>
       <c r="B96" t="n">
-        <v>79671</v>
+        <v>5480</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>101920</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407411</v>
+        <v>407545</v>
       </c>
       <c r="R96" t="n">
-        <v>6838819</v>
+        <v>6839241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10487,28 +10486,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129738144</v>
+        <v>129739289</v>
       </c>
       <c r="B97" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10516,21 +10516,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407223</v>
+        <v>407649</v>
       </c>
       <c r="R97" t="n">
-        <v>6838821</v>
+        <v>6839041</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10590,22 +10590,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129739289</v>
+        <v>129738144</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10613,21 +10613,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407649</v>
+        <v>407223</v>
       </c>
       <c r="R98" t="n">
-        <v>6839041</v>
+        <v>6838821</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10687,12 +10687,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129739242</v>
+        <v>129738172</v>
       </c>
       <c r="B100" t="n">
         <v>79700</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407515</v>
+        <v>407585</v>
       </c>
       <c r="R100" t="n">
-        <v>6838875</v>
+        <v>6838872</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10881,19 +10881,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129738172</v>
+        <v>129739242</v>
       </c>
       <c r="B101" t="n">
         <v>79700</v>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407585</v>
+        <v>407515</v>
       </c>
       <c r="R101" t="n">
-        <v>6838872</v>
+        <v>6838875</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10978,12 +10978,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11194,7 +11194,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129738191</v>
+        <v>129739251</v>
       </c>
       <c r="B104" t="n">
         <v>79671</v>
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407474</v>
+        <v>407563</v>
       </c>
       <c r="R104" t="n">
-        <v>6839108</v>
+        <v>6839056</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11279,19 +11279,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129739251</v>
+        <v>129738191</v>
       </c>
       <c r="B105" t="n">
         <v>79671</v>
@@ -11326,10 +11326,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407563</v>
+        <v>407474</v>
       </c>
       <c r="R105" t="n">
-        <v>6839056</v>
+        <v>6839108</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11376,22 +11376,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129738182</v>
+        <v>129739273</v>
       </c>
       <c r="B106" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11399,21 +11399,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>407447</v>
+        <v>407582</v>
       </c>
       <c r="R106" t="n">
-        <v>6838843</v>
+        <v>6838890</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11473,12 +11473,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129739273</v>
+        <v>129738182</v>
       </c>
       <c r="B108" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11593,21 +11593,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>407582</v>
+        <v>407447</v>
       </c>
       <c r="R108" t="n">
-        <v>6838890</v>
+        <v>6838843</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11667,12 +11667,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11873,7 +11873,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129738175</v>
+        <v>129738190</v>
       </c>
       <c r="B111" t="n">
         <v>79700</v>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>407547</v>
+        <v>407412</v>
       </c>
       <c r="R111" t="n">
-        <v>6838816</v>
+        <v>6838831</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,7 +11970,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129738190</v>
+        <v>129738175</v>
       </c>
       <c r="B112" t="n">
         <v>79700</v>
@@ -12005,10 +12005,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>407412</v>
+        <v>407547</v>
       </c>
       <c r="R112" t="n">
-        <v>6838831</v>
+        <v>6838816</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12593,7 +12593,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129738145</v>
+        <v>129739243</v>
       </c>
       <c r="B118" t="n">
         <v>79700</v>
@@ -12628,10 +12628,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407194</v>
+        <v>407451</v>
       </c>
       <c r="R118" t="n">
-        <v>6838873</v>
+        <v>6838866</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12678,19 +12678,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129739243</v>
+        <v>129739224</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407451</v>
+        <v>407121</v>
       </c>
       <c r="R119" t="n">
-        <v>6838866</v>
+        <v>6838895</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12787,7 +12787,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129739224</v>
+        <v>129738145</v>
       </c>
       <c r="B120" t="n">
         <v>79700</v>
@@ -12822,10 +12822,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407121</v>
+        <v>407194</v>
       </c>
       <c r="R120" t="n">
-        <v>6838895</v>
+        <v>6838873</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12872,12 +12872,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12981,10 +12981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739286</v>
+        <v>129739249</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407570</v>
+        <v>407437</v>
       </c>
       <c r="R122" t="n">
-        <v>6839041</v>
+        <v>6839060</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13078,10 +13078,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129739241</v>
+        <v>129738288</v>
       </c>
       <c r="B123" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13089,21 +13089,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407524</v>
+        <v>407592</v>
       </c>
       <c r="R123" t="n">
-        <v>6838914</v>
+        <v>6838822</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13163,22 +13163,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129738146</v>
+        <v>129739286</v>
       </c>
       <c r="B124" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13186,21 +13186,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407163</v>
+        <v>407570</v>
       </c>
       <c r="R124" t="n">
-        <v>6838891</v>
+        <v>6839041</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13260,22 +13260,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129739249</v>
+        <v>129738279</v>
       </c>
       <c r="B125" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407437</v>
+        <v>407617</v>
       </c>
       <c r="R125" t="n">
-        <v>6839060</v>
+        <v>6838855</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13357,22 +13357,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129738279</v>
+        <v>129738146</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13380,21 +13380,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407617</v>
+        <v>407163</v>
       </c>
       <c r="R126" t="n">
-        <v>6838855</v>
+        <v>6838891</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13466,10 +13466,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129738288</v>
+        <v>129739241</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407592</v>
+        <v>407524</v>
       </c>
       <c r="R127" t="n">
-        <v>6838822</v>
+        <v>6838914</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13551,57 +13551,66 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129739287</v>
+        <v>129738248</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407622</v>
+        <v>407481</v>
       </c>
       <c r="R128" t="n">
-        <v>6839045</v>
+        <v>6839152</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13642,63 +13651,73 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738281</v>
+        <v>129738256</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407587</v>
+        <v>407616</v>
       </c>
       <c r="R129" t="n">
-        <v>6838872</v>
+        <v>6838794</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13739,6 +13758,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13757,7 +13777,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129739230</v>
+        <v>129738157</v>
       </c>
       <c r="B130" t="n">
         <v>79700</v>
@@ -13792,10 +13812,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407404</v>
+        <v>407535</v>
       </c>
       <c r="R130" t="n">
-        <v>6839005</v>
+        <v>6839193</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13842,19 +13862,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738151</v>
+        <v>129738177</v>
       </c>
       <c r="B131" t="n">
         <v>79700</v>
@@ -13889,10 +13909,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407378</v>
+        <v>407476</v>
       </c>
       <c r="R131" t="n">
-        <v>6839143</v>
+        <v>6838854</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14048,7 +14068,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738157</v>
+        <v>129739230</v>
       </c>
       <c r="B133" t="n">
         <v>79700</v>
@@ -14083,10 +14103,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407535</v>
+        <v>407404</v>
       </c>
       <c r="R133" t="n">
-        <v>6839193</v>
+        <v>6839005</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14133,19 +14153,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129739231</v>
+        <v>129738151</v>
       </c>
       <c r="B134" t="n">
         <v>79700</v>
@@ -14180,10 +14200,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407422</v>
+        <v>407378</v>
       </c>
       <c r="R134" t="n">
-        <v>6839006</v>
+        <v>6839143</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14230,12 +14250,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14339,7 +14359,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129738177</v>
+        <v>129739231</v>
       </c>
       <c r="B136" t="n">
         <v>79700</v>
@@ -14374,10 +14394,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407476</v>
+        <v>407422</v>
       </c>
       <c r="R136" t="n">
-        <v>6838854</v>
+        <v>6839006</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14424,66 +14444,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129738248</v>
+        <v>129739287</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407481</v>
+        <v>407622</v>
       </c>
       <c r="R137" t="n">
-        <v>6839152</v>
+        <v>6839045</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14524,73 +14535,63 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129738256</v>
+        <v>129738281</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407616</v>
+        <v>407587</v>
       </c>
       <c r="R138" t="n">
-        <v>6838794</v>
+        <v>6838872</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14631,7 +14632,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14650,7 +14650,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129738242</v>
+        <v>129739268</v>
       </c>
       <c r="B139" t="n">
         <v>78839</v>
@@ -14679,16 +14679,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407719</v>
+        <v>407573</v>
       </c>
       <c r="R139" t="n">
-        <v>6839222</v>
+        <v>6838884</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14729,28 +14732,29 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129739254</v>
+        <v>129738242</v>
       </c>
       <c r="B140" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14758,21 +14762,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14782,10 +14786,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407418</v>
+        <v>407719</v>
       </c>
       <c r="R140" t="n">
-        <v>6838867</v>
+        <v>6839222</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14832,22 +14836,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129739268</v>
+        <v>129739254</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14855,37 +14859,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407573</v>
+        <v>407418</v>
       </c>
       <c r="R141" t="n">
-        <v>6838884</v>
+        <v>6838867</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14926,7 +14927,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14945,7 +14945,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738284</v>
+        <v>129738286</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407595</v>
+        <v>407586</v>
       </c>
       <c r="R142" t="n">
-        <v>6838836</v>
+        <v>6838820</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15042,10 +15042,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738201</v>
+        <v>129738150</v>
       </c>
       <c r="B143" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15053,42 +15053,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407530</v>
+        <v>407203</v>
       </c>
       <c r="R143" t="n">
-        <v>6839196</v>
+        <v>6839015</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15147,10 +15139,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738286</v>
+        <v>129739253</v>
       </c>
       <c r="B144" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15158,34 +15150,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407586</v>
+        <v>407589</v>
       </c>
       <c r="R144" t="n">
-        <v>6838820</v>
+        <v>6838889</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15226,28 +15221,29 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738150</v>
+        <v>129738195</v>
       </c>
       <c r="B145" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15255,21 +15251,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15279,10 +15275,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407203</v>
+        <v>407479</v>
       </c>
       <c r="R145" t="n">
-        <v>6839015</v>
+        <v>6838852</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15341,10 +15337,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129739253</v>
+        <v>129738284</v>
       </c>
       <c r="B146" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15352,37 +15348,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407589</v>
+        <v>407595</v>
       </c>
       <c r="R146" t="n">
-        <v>6838889</v>
+        <v>6838836</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15423,29 +15416,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738195</v>
+        <v>129738201</v>
       </c>
       <c r="B147" t="n">
-        <v>79671</v>
+        <v>57896</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15453,34 +15445,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407479</v>
+        <v>407530</v>
       </c>
       <c r="R147" t="n">
-        <v>6838852</v>
+        <v>6839196</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129739257</v>
+        <v>129738278</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,42 +2490,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407574</v>
+        <v>407601</v>
       </c>
       <c r="R16" t="n">
-        <v>6839050</v>
+        <v>6838838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2572,22 +2564,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129738266</v>
+        <v>129738187</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,42 +2587,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407598</v>
+        <v>407437</v>
       </c>
       <c r="R17" t="n">
-        <v>6838839</v>
+        <v>6838840</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2689,10 +2673,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738278</v>
+        <v>129738167</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,21 +2684,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2724,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407601</v>
+        <v>407714</v>
       </c>
       <c r="R18" t="n">
-        <v>6838838</v>
+        <v>6839244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2786,7 +2770,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129739237</v>
+        <v>129738159</v>
       </c>
       <c r="B19" t="n">
         <v>79700</v>
@@ -2821,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407617</v>
+        <v>407516</v>
       </c>
       <c r="R19" t="n">
-        <v>6839035</v>
+        <v>6839209</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2871,19 +2855,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738187</v>
+        <v>129739237</v>
       </c>
       <c r="B20" t="n">
         <v>79700</v>
@@ -2918,10 +2902,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407437</v>
+        <v>407617</v>
       </c>
       <c r="R20" t="n">
-        <v>6838840</v>
+        <v>6839035</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2968,57 +2952,66 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738167</v>
+        <v>129738245</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407714</v>
+        <v>407233</v>
       </c>
       <c r="R21" t="n">
-        <v>6839244</v>
+        <v>6838838</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3059,6 +3052,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3077,10 +3071,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738159</v>
+        <v>129739257</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,34 +3082,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407516</v>
+        <v>407574</v>
       </c>
       <c r="R22" t="n">
-        <v>6839209</v>
+        <v>6839050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3162,19 +3164,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739256</v>
+        <v>129738266</v>
       </c>
       <c r="B23" t="n">
         <v>57736</v>
@@ -3207,7 +3209,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3217,10 +3219,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407082</v>
+        <v>407598</v>
       </c>
       <c r="R23" t="n">
-        <v>6838747</v>
+        <v>6838839</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,53 +3269,52 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738245</v>
+        <v>129739256</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3323,10 +3324,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407233</v>
+        <v>407082</v>
       </c>
       <c r="R24" t="n">
-        <v>6838838</v>
+        <v>6838747</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3367,19 +3368,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129739291</v>
+        <v>129738154</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,21 +3494,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407656</v>
+        <v>407536</v>
       </c>
       <c r="R26" t="n">
-        <v>6839031</v>
+        <v>6839138</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3568,22 +3568,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129739272</v>
+        <v>129739291</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,21 +3591,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407597</v>
+        <v>407656</v>
       </c>
       <c r="R27" t="n">
-        <v>6838888</v>
+        <v>6839031</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129738154</v>
+        <v>129739233</v>
       </c>
       <c r="B28" t="n">
         <v>79700</v>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407536</v>
+        <v>407429</v>
       </c>
       <c r="R28" t="n">
-        <v>6839138</v>
+        <v>6839067</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3762,22 +3762,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129739233</v>
+        <v>129739272</v>
       </c>
       <c r="B29" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,21 +3785,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407429</v>
+        <v>407597</v>
       </c>
       <c r="R29" t="n">
-        <v>6839067</v>
+        <v>6838888</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4453,54 +4453,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738246</v>
+        <v>129739271</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>78838</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407154</v>
+        <v>407647</v>
       </c>
       <c r="R36" t="n">
-        <v>6838842</v>
+        <v>6838874</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4541,26 +4532,25 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129739270</v>
+        <v>129738246</v>
       </c>
       <c r="B37" t="n">
         <v>8450</v>
@@ -4604,10 +4594,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407283</v>
+        <v>407154</v>
       </c>
       <c r="R37" t="n">
-        <v>6839055</v>
+        <v>6838842</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4655,49 +4645,55 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129738283</v>
+        <v>129739270</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4705,10 +4701,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407598</v>
+        <v>407283</v>
       </c>
       <c r="R38" t="n">
-        <v>6838839</v>
+        <v>6839055</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4743,11 +4739,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4761,22 +4752,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129739271</v>
+        <v>129738184</v>
       </c>
       <c r="B39" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4784,21 +4775,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4808,10 +4799,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407647</v>
+        <v>407445</v>
       </c>
       <c r="R39" t="n">
-        <v>6838874</v>
+        <v>6838844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4858,22 +4849,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738287</v>
+        <v>129738158</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,21 +4872,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4905,10 +4896,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407591</v>
+        <v>407519</v>
       </c>
       <c r="R40" t="n">
-        <v>6838814</v>
+        <v>6839207</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4967,10 +4958,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738184</v>
+        <v>129738287</v>
       </c>
       <c r="B41" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4978,21 +4969,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5002,10 +4993,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407445</v>
+        <v>407591</v>
       </c>
       <c r="R41" t="n">
-        <v>6838844</v>
+        <v>6838814</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5064,10 +5055,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129738149</v>
+        <v>129738283</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,34 +5066,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407199</v>
+        <v>407598</v>
       </c>
       <c r="R42" t="n">
-        <v>6838976</v>
+        <v>6838839</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5137,12 +5131,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129738158</v>
+        <v>129738149</v>
       </c>
       <c r="B43" t="n">
         <v>79700</v>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407519</v>
+        <v>407199</v>
       </c>
       <c r="R43" t="n">
-        <v>6839207</v>
+        <v>6838976</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5452,54 +5452,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738247</v>
+        <v>129739240</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407158</v>
+        <v>407581</v>
       </c>
       <c r="R46" t="n">
-        <v>6838902</v>
+        <v>6838885</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5540,29 +5531,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129739250</v>
+        <v>129738186</v>
       </c>
       <c r="B47" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,37 +5560,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407493</v>
+        <v>407479</v>
       </c>
       <c r="R47" t="n">
-        <v>6839112</v>
+        <v>6838810</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5641,19 +5628,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5765,45 +5751,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129739240</v>
+        <v>129738247</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407581</v>
+        <v>407158</v>
       </c>
       <c r="R49" t="n">
-        <v>6838885</v>
+        <v>6838902</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5844,28 +5839,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129738186</v>
+        <v>129739250</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,34 +5869,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407479</v>
+        <v>407493</v>
       </c>
       <c r="R50" t="n">
-        <v>6838810</v>
+        <v>6839112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,18 +5940,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738291</v>
+        <v>129738198</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,34 +6261,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407574</v>
+        <v>407575</v>
       </c>
       <c r="R54" t="n">
-        <v>6838848</v>
+        <v>6838839</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,45 +6355,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738160</v>
+        <v>129738255</v>
       </c>
       <c r="B55" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407512</v>
+        <v>407645</v>
       </c>
       <c r="R55" t="n">
-        <v>6839214</v>
+        <v>6838797</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6426,6 +6443,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6444,7 +6462,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738168</v>
+        <v>129738160</v>
       </c>
       <c r="B56" t="n">
         <v>79700</v>
@@ -6479,10 +6497,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407717</v>
+        <v>407512</v>
       </c>
       <c r="R56" t="n">
-        <v>6839236</v>
+        <v>6839214</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6541,10 +6559,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129739229</v>
+        <v>129738291</v>
       </c>
       <c r="B57" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,21 +6570,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6576,10 +6594,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407296</v>
+        <v>407574</v>
       </c>
       <c r="R57" t="n">
-        <v>6838974</v>
+        <v>6838848</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,66 +6644,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738255</v>
+        <v>129738168</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407645</v>
+        <v>407717</v>
       </c>
       <c r="R58" t="n">
-        <v>6838797</v>
+        <v>6839236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6735,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6745,10 +6753,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738198</v>
+        <v>129739229</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6756,42 +6764,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407575</v>
+        <v>407296</v>
       </c>
       <c r="R59" t="n">
-        <v>6838839</v>
+        <v>6838974</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6838,12 +6838,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738169</v>
+        <v>129739264</v>
       </c>
       <c r="B68" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7651,21 +7651,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407672</v>
+        <v>407129</v>
       </c>
       <c r="R68" t="n">
-        <v>6838825</v>
+        <v>6838913</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7725,22 +7725,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739245</v>
+        <v>129738193</v>
       </c>
       <c r="B69" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7748,21 +7748,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407443</v>
+        <v>407714</v>
       </c>
       <c r="R69" t="n">
-        <v>6838872</v>
+        <v>6839244</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7822,12 +7822,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7931,10 +7931,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129738199</v>
+        <v>129738169</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7942,42 +7942,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407576</v>
+        <v>407672</v>
       </c>
       <c r="R71" t="n">
-        <v>6838847</v>
+        <v>6838825</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8036,53 +8028,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129738257</v>
+        <v>129739245</v>
       </c>
       <c r="B72" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407464</v>
+        <v>407443</v>
       </c>
       <c r="R72" t="n">
-        <v>6839159</v>
+        <v>6838872</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8129,22 +8113,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129739264</v>
+        <v>129738199</v>
       </c>
       <c r="B73" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8152,34 +8136,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407129</v>
+        <v>407576</v>
       </c>
       <c r="R73" t="n">
-        <v>6838913</v>
+        <v>6838847</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8226,57 +8218,65 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129738193</v>
+        <v>129738257</v>
       </c>
       <c r="B74" t="n">
-        <v>79671</v>
+        <v>58106</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407714</v>
+        <v>407464</v>
       </c>
       <c r="R74" t="n">
-        <v>6839244</v>
+        <v>6839159</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738147</v>
+        <v>129738285</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8443,21 +8443,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407190</v>
+        <v>407587</v>
       </c>
       <c r="R76" t="n">
-        <v>6838950</v>
+        <v>6838806</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738176</v>
+        <v>129738147</v>
       </c>
       <c r="B77" t="n">
         <v>79700</v>
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407519</v>
+        <v>407190</v>
       </c>
       <c r="R77" t="n">
-        <v>6838831</v>
+        <v>6838950</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738171</v>
+        <v>129738176</v>
       </c>
       <c r="B78" t="n">
         <v>79700</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407620</v>
+        <v>407519</v>
       </c>
       <c r="R78" t="n">
-        <v>6838898</v>
+        <v>6838831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,7 +8723,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738181</v>
+        <v>129738171</v>
       </c>
       <c r="B79" t="n">
         <v>79700</v>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407467</v>
+        <v>407620</v>
       </c>
       <c r="R79" t="n">
-        <v>6838834</v>
+        <v>6838898</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738194</v>
+        <v>129738181</v>
       </c>
       <c r="B80" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8831,21 +8831,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407549</v>
+        <v>407467</v>
       </c>
       <c r="R80" t="n">
-        <v>6838809</v>
+        <v>6838834</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,45 +8917,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738285</v>
+        <v>129738244</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407587</v>
+        <v>407231</v>
       </c>
       <c r="R81" t="n">
-        <v>6838806</v>
+        <v>6838827</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8996,6 +9005,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9014,54 +9024,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738244</v>
+        <v>129738194</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407231</v>
+        <v>407549</v>
       </c>
       <c r="R82" t="n">
-        <v>6838827</v>
+        <v>6838809</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9102,7 +9103,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9606,10 +9606,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129739267</v>
+        <v>129739259</v>
       </c>
       <c r="B88" t="n">
-        <v>78839</v>
+        <v>57896</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,34 +9617,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407597</v>
+        <v>407549</v>
       </c>
       <c r="R88" t="n">
-        <v>6838888</v>
+        <v>6839053</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9703,10 +9711,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129739259</v>
+        <v>129739267</v>
       </c>
       <c r="B89" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9714,42 +9722,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407549</v>
+        <v>407597</v>
       </c>
       <c r="R89" t="n">
-        <v>6839053</v>
+        <v>6838888</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129739255</v>
+        <v>129739239</v>
       </c>
       <c r="B90" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9819,21 +9819,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407411</v>
+        <v>407614</v>
       </c>
       <c r="R90" t="n">
-        <v>6838819</v>
+        <v>6838900</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9905,40 +9905,41 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739258</v>
+        <v>129738227</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>5480</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>101920</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -9948,10 +9949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407616</v>
+        <v>407545</v>
       </c>
       <c r="R91" t="n">
-        <v>6838890</v>
+        <v>6839241</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9992,28 +9993,29 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129739246</v>
+        <v>129739258</v>
       </c>
       <c r="B92" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,34 +10023,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407427</v>
+        <v>407616</v>
       </c>
       <c r="R92" t="n">
-        <v>6838886</v>
+        <v>6838890</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10107,7 +10117,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129739239</v>
+        <v>129739246</v>
       </c>
       <c r="B93" t="n">
         <v>79700</v>
@@ -10142,10 +10152,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407614</v>
+        <v>407427</v>
       </c>
       <c r="R93" t="n">
-        <v>6838900</v>
+        <v>6838886</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10398,54 +10408,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129738227</v>
+        <v>129739255</v>
       </c>
       <c r="B96" t="n">
-        <v>5480</v>
+        <v>79671</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>101920</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407545</v>
+        <v>407411</v>
       </c>
       <c r="R96" t="n">
-        <v>6839241</v>
+        <v>6838819</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10486,29 +10487,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129739289</v>
+        <v>129738185</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10516,21 +10516,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407649</v>
+        <v>407439</v>
       </c>
       <c r="R97" t="n">
-        <v>6839041</v>
+        <v>6838837</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10590,22 +10590,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129738144</v>
+        <v>129739289</v>
       </c>
       <c r="B98" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10613,21 +10613,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407223</v>
+        <v>407649</v>
       </c>
       <c r="R98" t="n">
-        <v>6838821</v>
+        <v>6839041</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10687,19 +10687,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129738185</v>
+        <v>129738144</v>
       </c>
       <c r="B99" t="n">
         <v>79700</v>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407439</v>
+        <v>407223</v>
       </c>
       <c r="R99" t="n">
-        <v>6838837</v>
+        <v>6838821</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11194,7 +11194,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129739251</v>
+        <v>129738191</v>
       </c>
       <c r="B104" t="n">
         <v>79671</v>
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407563</v>
+        <v>407474</v>
       </c>
       <c r="R104" t="n">
-        <v>6839056</v>
+        <v>6839108</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11279,19 +11279,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129738191</v>
+        <v>129739251</v>
       </c>
       <c r="B105" t="n">
         <v>79671</v>
@@ -11326,10 +11326,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407474</v>
+        <v>407563</v>
       </c>
       <c r="R105" t="n">
-        <v>6839108</v>
+        <v>6839056</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11376,12 +11376,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12279,7 +12279,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129738280</v>
+        <v>129739290</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407623</v>
+        <v>407657</v>
       </c>
       <c r="R115" t="n">
-        <v>6838894</v>
+        <v>6839033</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12373,22 +12373,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129739290</v>
+        <v>129738145</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12396,37 +12396,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407657</v>
+        <v>407194</v>
       </c>
       <c r="R116" t="n">
-        <v>6839033</v>
+        <v>6838873</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12461,40 +12458,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129738282</v>
+        <v>129739243</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12502,21 +12493,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12526,10 +12517,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407588</v>
+        <v>407451</v>
       </c>
       <c r="R117" t="n">
-        <v>6838831</v>
+        <v>6838866</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12564,11 +12555,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12581,22 +12567,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129739243</v>
+        <v>129738280</v>
       </c>
       <c r="B118" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12604,34 +12590,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407451</v>
+        <v>407623</v>
       </c>
       <c r="R118" t="n">
-        <v>6838866</v>
+        <v>6838894</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12666,24 +12655,30 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12787,10 +12782,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738145</v>
+        <v>129738282</v>
       </c>
       <c r="B120" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12798,21 +12793,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12822,10 +12817,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407194</v>
+        <v>407588</v>
       </c>
       <c r="R120" t="n">
-        <v>6838873</v>
+        <v>6838831</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12858,6 +12853,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12981,10 +12981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739249</v>
+        <v>129739286</v>
       </c>
       <c r="B122" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407437</v>
+        <v>407570</v>
       </c>
       <c r="R122" t="n">
-        <v>6839060</v>
+        <v>6839041</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13175,7 +13175,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129739286</v>
+        <v>129738279</v>
       </c>
       <c r="B124" t="n">
         <v>79081</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407570</v>
+        <v>407617</v>
       </c>
       <c r="R124" t="n">
-        <v>6839041</v>
+        <v>6838855</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13260,22 +13260,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738279</v>
+        <v>129738146</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407617</v>
+        <v>407163</v>
       </c>
       <c r="R125" t="n">
-        <v>6838855</v>
+        <v>6838891</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,7 +13369,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129738146</v>
+        <v>129739241</v>
       </c>
       <c r="B126" t="n">
         <v>79700</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407163</v>
+        <v>407524</v>
       </c>
       <c r="R126" t="n">
-        <v>6838891</v>
+        <v>6838914</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13454,22 +13454,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739241</v>
+        <v>129739249</v>
       </c>
       <c r="B127" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407524</v>
+        <v>407437</v>
       </c>
       <c r="R127" t="n">
-        <v>6838914</v>
+        <v>6839060</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13563,54 +13563,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129738248</v>
+        <v>129739287</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407481</v>
+        <v>407622</v>
       </c>
       <c r="R128" t="n">
-        <v>6839152</v>
+        <v>6839045</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13651,73 +13642,63 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738256</v>
+        <v>129738281</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407616</v>
+        <v>407587</v>
       </c>
       <c r="R129" t="n">
-        <v>6838794</v>
+        <v>6838872</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13758,7 +13739,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13777,7 +13757,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129738157</v>
+        <v>129739230</v>
       </c>
       <c r="B130" t="n">
         <v>79700</v>
@@ -13812,10 +13792,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407535</v>
+        <v>407404</v>
       </c>
       <c r="R130" t="n">
-        <v>6839193</v>
+        <v>6839005</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13862,19 +13842,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738177</v>
+        <v>129738157</v>
       </c>
       <c r="B131" t="n">
         <v>79700</v>
@@ -13909,10 +13889,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407476</v>
+        <v>407535</v>
       </c>
       <c r="R131" t="n">
-        <v>6838854</v>
+        <v>6839193</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13971,7 +13951,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738156</v>
+        <v>129738177</v>
       </c>
       <c r="B132" t="n">
         <v>79700</v>
@@ -14006,10 +13986,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407477</v>
+        <v>407476</v>
       </c>
       <c r="R132" t="n">
-        <v>6839132</v>
+        <v>6838854</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14068,7 +14048,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129739230</v>
+        <v>129738156</v>
       </c>
       <c r="B133" t="n">
         <v>79700</v>
@@ -14103,10 +14083,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407404</v>
+        <v>407477</v>
       </c>
       <c r="R133" t="n">
-        <v>6839005</v>
+        <v>6839132</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14153,12 +14133,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14456,45 +14436,54 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129739287</v>
+        <v>129738248</v>
       </c>
       <c r="B137" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407622</v>
+        <v>407481</v>
       </c>
       <c r="R137" t="n">
-        <v>6839045</v>
+        <v>6839152</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14535,63 +14524,73 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129738281</v>
+        <v>129738256</v>
       </c>
       <c r="B138" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407587</v>
+        <v>407616</v>
       </c>
       <c r="R138" t="n">
-        <v>6838872</v>
+        <v>6838794</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14632,6 +14631,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14650,7 +14650,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129739268</v>
+        <v>129738242</v>
       </c>
       <c r="B139" t="n">
         <v>78839</v>
@@ -14679,19 +14679,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407573</v>
+        <v>407719</v>
       </c>
       <c r="R139" t="n">
-        <v>6838884</v>
+        <v>6839222</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14732,29 +14729,28 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129738242</v>
+        <v>129739254</v>
       </c>
       <c r="B140" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14762,21 +14758,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14786,10 +14782,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407719</v>
+        <v>407418</v>
       </c>
       <c r="R140" t="n">
-        <v>6839222</v>
+        <v>6838867</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14836,22 +14832,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129739254</v>
+        <v>129739268</v>
       </c>
       <c r="B141" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14859,34 +14855,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407418</v>
+        <v>407573</v>
       </c>
       <c r="R141" t="n">
-        <v>6838867</v>
+        <v>6838884</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14927,6 +14926,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14945,7 +14945,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738286</v>
+        <v>129738284</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407586</v>
+        <v>407595</v>
       </c>
       <c r="R142" t="n">
-        <v>6838820</v>
+        <v>6838836</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15042,10 +15042,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738150</v>
+        <v>129738286</v>
       </c>
       <c r="B143" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15053,21 +15053,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15077,10 +15077,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407203</v>
+        <v>407586</v>
       </c>
       <c r="R143" t="n">
-        <v>6839015</v>
+        <v>6838820</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15139,10 +15139,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129739253</v>
+        <v>129738150</v>
       </c>
       <c r="B144" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15150,37 +15150,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407589</v>
+        <v>407203</v>
       </c>
       <c r="R144" t="n">
-        <v>6838889</v>
+        <v>6839015</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15221,29 +15218,28 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738195</v>
+        <v>129738201</v>
       </c>
       <c r="B145" t="n">
-        <v>79671</v>
+        <v>57896</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15251,34 +15247,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407479</v>
+        <v>407530</v>
       </c>
       <c r="R145" t="n">
-        <v>6838852</v>
+        <v>6839196</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15337,10 +15341,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129738284</v>
+        <v>129739253</v>
       </c>
       <c r="B146" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15348,34 +15352,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407595</v>
+        <v>407589</v>
       </c>
       <c r="R146" t="n">
-        <v>6838836</v>
+        <v>6838889</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15416,28 +15423,29 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738201</v>
+        <v>129738195</v>
       </c>
       <c r="B147" t="n">
-        <v>57896</v>
+        <v>79671</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15445,42 +15453,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407530</v>
+        <v>407479</v>
       </c>
       <c r="R147" t="n">
-        <v>6839196</v>
+        <v>6838852</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738274</v>
+        <v>129738166</v>
       </c>
       <c r="B148" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15550,21 +15550,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407522</v>
+        <v>407704</v>
       </c>
       <c r="R148" t="n">
-        <v>6839200</v>
+        <v>6839251</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129739288</v>
+        <v>129739247</v>
       </c>
       <c r="B149" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407625</v>
+        <v>407319</v>
       </c>
       <c r="R149" t="n">
-        <v>6839051</v>
+        <v>6838979</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15927,10 +15927,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129738166</v>
+        <v>129738274</v>
       </c>
       <c r="B152" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15938,21 +15938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407704</v>
+        <v>407522</v>
       </c>
       <c r="R152" t="n">
-        <v>6839251</v>
+        <v>6839200</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16024,10 +16024,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129739247</v>
+        <v>129739288</v>
       </c>
       <c r="B153" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>407319</v>
+        <v>407625</v>
       </c>
       <c r="R153" t="n">
-        <v>6838979</v>
+        <v>6839051</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129738278</v>
+        <v>129739257</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,34 +2490,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407601</v>
+        <v>407574</v>
       </c>
       <c r="R16" t="n">
-        <v>6838838</v>
+        <v>6839050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,22 +2572,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129738187</v>
+        <v>129738266</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,34 +2595,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407437</v>
+        <v>407598</v>
       </c>
       <c r="R17" t="n">
-        <v>6838840</v>
+        <v>6838839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2673,10 +2689,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738167</v>
+        <v>129739256</v>
       </c>
       <c r="B18" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,34 +2700,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407714</v>
+        <v>407082</v>
       </c>
       <c r="R18" t="n">
-        <v>6839244</v>
+        <v>6838747</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2758,22 +2782,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738159</v>
+        <v>129738278</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,21 +2805,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,10 +2829,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407516</v>
+        <v>407601</v>
       </c>
       <c r="R19" t="n">
-        <v>6839209</v>
+        <v>6838838</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2867,7 +2891,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129739237</v>
+        <v>129738187</v>
       </c>
       <c r="B20" t="n">
         <v>79700</v>
@@ -2902,10 +2926,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407617</v>
+        <v>407437</v>
       </c>
       <c r="R20" t="n">
-        <v>6839035</v>
+        <v>6838840</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2952,66 +2976,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738245</v>
+        <v>129738167</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407233</v>
+        <v>407714</v>
       </c>
       <c r="R21" t="n">
-        <v>6838838</v>
+        <v>6839244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3052,7 +3067,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3071,10 +3085,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129739257</v>
+        <v>129738159</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3082,42 +3096,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407574</v>
+        <v>407516</v>
       </c>
       <c r="R22" t="n">
-        <v>6839050</v>
+        <v>6839209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3164,22 +3170,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129738266</v>
+        <v>129739237</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3187,42 +3193,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407598</v>
+        <v>407617</v>
       </c>
       <c r="R23" t="n">
-        <v>6838839</v>
+        <v>6839035</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3269,22 +3267,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129739256</v>
+        <v>129739265</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3292,42 +3290,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407082</v>
+        <v>407615</v>
       </c>
       <c r="R24" t="n">
-        <v>6838747</v>
+        <v>6839034</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3386,45 +3376,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129739265</v>
+        <v>129738245</v>
       </c>
       <c r="B25" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407615</v>
+        <v>407233</v>
       </c>
       <c r="R25" t="n">
-        <v>6839034</v>
+        <v>6838838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3465,18 +3464,19 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129738197</v>
+        <v>129738179</v>
       </c>
       <c r="B31" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407408</v>
+        <v>407483</v>
       </c>
       <c r="R31" t="n">
-        <v>6838841</v>
+        <v>6838820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129739248</v>
+        <v>129739227</v>
       </c>
       <c r="B32" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407440</v>
+        <v>407211</v>
       </c>
       <c r="R32" t="n">
         <v>6839027</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129739227</v>
+        <v>129738155</v>
       </c>
       <c r="B33" t="n">
         <v>79700</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407211</v>
+        <v>407503</v>
       </c>
       <c r="R33" t="n">
-        <v>6839027</v>
+        <v>6839131</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,22 +4247,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129738155</v>
+        <v>129738197</v>
       </c>
       <c r="B34" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407503</v>
+        <v>407408</v>
       </c>
       <c r="R34" t="n">
-        <v>6839131</v>
+        <v>6838841</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129738179</v>
+        <v>129739248</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,21 +4367,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407483</v>
+        <v>407440</v>
       </c>
       <c r="R35" t="n">
-        <v>6838820</v>
+        <v>6839027</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,22 +4441,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129739271</v>
+        <v>129738184</v>
       </c>
       <c r="B36" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4464,21 +4464,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407647</v>
+        <v>407445</v>
       </c>
       <c r="R36" t="n">
-        <v>6838874</v>
+        <v>6838844</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4538,66 +4538,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129738246</v>
+        <v>129738158</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407154</v>
+        <v>407519</v>
       </c>
       <c r="R37" t="n">
-        <v>6838842</v>
+        <v>6839207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4638,7 +4629,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4657,54 +4647,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129739270</v>
+        <v>129738287</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407283</v>
+        <v>407591</v>
       </c>
       <c r="R38" t="n">
-        <v>6839055</v>
+        <v>6838814</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4745,29 +4726,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738184</v>
+        <v>129738283</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4775,34 +4755,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407445</v>
+        <v>407598</v>
       </c>
       <c r="R39" t="n">
-        <v>6838844</v>
+        <v>6838839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4837,12 +4820,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4861,10 +4850,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738158</v>
+        <v>129739271</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4872,21 +4861,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4896,10 +4885,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407519</v>
+        <v>407647</v>
       </c>
       <c r="R40" t="n">
-        <v>6839207</v>
+        <v>6838874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4946,57 +4935,66 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738287</v>
+        <v>129738246</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407591</v>
+        <v>407154</v>
       </c>
       <c r="R41" t="n">
-        <v>6838814</v>
+        <v>6838842</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5037,6 +5035,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5055,37 +5054,43 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129738283</v>
+        <v>129739270</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5093,10 +5098,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407598</v>
+        <v>407283</v>
       </c>
       <c r="R42" t="n">
-        <v>6838839</v>
+        <v>6839055</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5131,11 +5136,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5149,12 +5149,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738292</v>
+        <v>129738290</v>
       </c>
       <c r="B44" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407528</v>
+        <v>407575</v>
       </c>
       <c r="R44" t="n">
-        <v>6839142</v>
+        <v>6838839</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738290</v>
+        <v>129738204</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,34 +5366,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407575</v>
+        <v>407170</v>
       </c>
       <c r="R45" t="n">
-        <v>6838839</v>
+        <v>6838942</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5452,10 +5460,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129739240</v>
+        <v>129738292</v>
       </c>
       <c r="B46" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5463,21 +5471,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5487,10 +5495,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407581</v>
+        <v>407528</v>
       </c>
       <c r="R46" t="n">
-        <v>6838885</v>
+        <v>6839142</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,19 +5545,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738186</v>
+        <v>129739240</v>
       </c>
       <c r="B47" t="n">
         <v>79700</v>
@@ -5584,10 +5592,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407479</v>
+        <v>407581</v>
       </c>
       <c r="R47" t="n">
-        <v>6838810</v>
+        <v>6838885</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5634,22 +5642,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738204</v>
+        <v>129738186</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5657,42 +5665,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407170</v>
+        <v>407479</v>
       </c>
       <c r="R48" t="n">
-        <v>6838942</v>
+        <v>6838810</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738198</v>
+        <v>129738160</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,42 +6261,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407575</v>
+        <v>407512</v>
       </c>
       <c r="R54" t="n">
-        <v>6838839</v>
+        <v>6839214</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6355,54 +6347,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738255</v>
+        <v>129738291</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407645</v>
+        <v>407574</v>
       </c>
       <c r="R55" t="n">
-        <v>6838797</v>
+        <v>6838848</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6443,7 +6426,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6462,7 +6444,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738160</v>
+        <v>129738168</v>
       </c>
       <c r="B56" t="n">
         <v>79700</v>
@@ -6497,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407512</v>
+        <v>407717</v>
       </c>
       <c r="R56" t="n">
-        <v>6839214</v>
+        <v>6839236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6559,10 +6541,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738291</v>
+        <v>129739229</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6570,21 +6552,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6594,10 +6576,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407574</v>
+        <v>407296</v>
       </c>
       <c r="R57" t="n">
-        <v>6838848</v>
+        <v>6838974</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6644,22 +6626,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738168</v>
+        <v>129738198</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6667,34 +6649,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407717</v>
+        <v>407575</v>
       </c>
       <c r="R58" t="n">
-        <v>6839236</v>
+        <v>6838839</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6753,45 +6743,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129739229</v>
+        <v>129738255</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407296</v>
+        <v>407645</v>
       </c>
       <c r="R59" t="n">
-        <v>6838974</v>
+        <v>6838797</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6832,18 +6831,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129739292</v>
+        <v>129739264</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7550,37 +7550,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407632</v>
+        <v>407129</v>
       </c>
       <c r="R67" t="n">
-        <v>6838901</v>
+        <v>6838913</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7621,7 +7618,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7640,10 +7636,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129739264</v>
+        <v>129738193</v>
       </c>
       <c r="B68" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7651,21 +7647,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7675,10 +7671,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407129</v>
+        <v>407714</v>
       </c>
       <c r="R68" t="n">
-        <v>6838913</v>
+        <v>6839244</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7725,22 +7721,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129738193</v>
+        <v>129739292</v>
       </c>
       <c r="B69" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7748,34 +7744,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407714</v>
+        <v>407632</v>
       </c>
       <c r="R69" t="n">
-        <v>6839244</v>
+        <v>6838901</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7816,18 +7815,19 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738275</v>
+        <v>129738147</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407608</v>
+        <v>407190</v>
       </c>
       <c r="R75" t="n">
-        <v>6839252</v>
+        <v>6838950</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738285</v>
+        <v>129738176</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8443,21 +8443,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407587</v>
+        <v>407519</v>
       </c>
       <c r="R76" t="n">
-        <v>6838806</v>
+        <v>6838831</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738147</v>
+        <v>129738171</v>
       </c>
       <c r="B77" t="n">
         <v>79700</v>
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407190</v>
+        <v>407620</v>
       </c>
       <c r="R77" t="n">
-        <v>6838950</v>
+        <v>6838898</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738176</v>
+        <v>129738181</v>
       </c>
       <c r="B78" t="n">
         <v>79700</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407519</v>
+        <v>407467</v>
       </c>
       <c r="R78" t="n">
-        <v>6838831</v>
+        <v>6838834</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738171</v>
+        <v>129738275</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8734,21 +8734,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407620</v>
+        <v>407608</v>
       </c>
       <c r="R79" t="n">
-        <v>6838898</v>
+        <v>6839252</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738181</v>
+        <v>129738285</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8831,21 +8831,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407467</v>
+        <v>407587</v>
       </c>
       <c r="R80" t="n">
-        <v>6838834</v>
+        <v>6838806</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9121,7 +9121,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129738174</v>
+        <v>129738143</v>
       </c>
       <c r="B83" t="n">
         <v>79700</v>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407572</v>
+        <v>407137</v>
       </c>
       <c r="R83" t="n">
-        <v>6838852</v>
+        <v>6838823</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9218,7 +9218,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738143</v>
+        <v>129738165</v>
       </c>
       <c r="B84" t="n">
         <v>79700</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407137</v>
+        <v>407691</v>
       </c>
       <c r="R84" t="n">
-        <v>6838823</v>
+        <v>6839279</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9315,7 +9315,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738165</v>
+        <v>129739238</v>
       </c>
       <c r="B85" t="n">
         <v>79700</v>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407691</v>
+        <v>407627</v>
       </c>
       <c r="R85" t="n">
-        <v>6839279</v>
+        <v>6839039</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9400,19 +9400,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129739238</v>
+        <v>129738148</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407627</v>
+        <v>407233</v>
       </c>
       <c r="R86" t="n">
-        <v>6839039</v>
+        <v>6838964</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,22 +9497,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129738148</v>
+        <v>129739267</v>
       </c>
       <c r="B87" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9520,21 +9520,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407233</v>
+        <v>407597</v>
       </c>
       <c r="R87" t="n">
-        <v>6838964</v>
+        <v>6838888</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9594,22 +9594,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129739259</v>
+        <v>129738174</v>
       </c>
       <c r="B88" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,42 +9617,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407549</v>
+        <v>407572</v>
       </c>
       <c r="R88" t="n">
-        <v>6839053</v>
+        <v>6838852</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,22 +9691,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129739267</v>
+        <v>129739259</v>
       </c>
       <c r="B89" t="n">
-        <v>78839</v>
+        <v>57896</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9722,34 +9714,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407597</v>
+        <v>407549</v>
       </c>
       <c r="R89" t="n">
-        <v>6838888</v>
+        <v>6839053</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12279,7 +12279,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129739290</v>
+        <v>129738280</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407657</v>
+        <v>407623</v>
       </c>
       <c r="R115" t="n">
-        <v>6839033</v>
+        <v>6838894</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12373,19 +12373,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129738145</v>
+        <v>129739224</v>
       </c>
       <c r="B116" t="n">
         <v>79700</v>
@@ -12420,10 +12420,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407194</v>
+        <v>407121</v>
       </c>
       <c r="R116" t="n">
-        <v>6838873</v>
+        <v>6838895</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12470,22 +12470,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129739243</v>
+        <v>129738282</v>
       </c>
       <c r="B117" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12493,21 +12493,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12517,10 +12517,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407451</v>
+        <v>407588</v>
       </c>
       <c r="R117" t="n">
-        <v>6838866</v>
+        <v>6838831</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12555,6 +12555,11 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12567,22 +12572,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129738280</v>
+        <v>129738192</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12590,37 +12595,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407623</v>
+        <v>407464</v>
       </c>
       <c r="R118" t="n">
-        <v>6838894</v>
+        <v>6839157</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12655,18 +12657,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12685,10 +12681,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129739224</v>
+        <v>129739290</v>
       </c>
       <c r="B119" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12696,34 +12692,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407121</v>
+        <v>407657</v>
       </c>
       <c r="R119" t="n">
-        <v>6838895</v>
+        <v>6839033</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12758,12 +12757,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12782,10 +12787,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738282</v>
+        <v>129738145</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12793,21 +12798,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12817,10 +12822,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407588</v>
+        <v>407194</v>
       </c>
       <c r="R120" t="n">
-        <v>6838831</v>
+        <v>6838873</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12853,11 +12858,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12884,10 +12884,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129738192</v>
+        <v>129739243</v>
       </c>
       <c r="B121" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12895,21 +12895,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12919,10 +12919,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407464</v>
+        <v>407451</v>
       </c>
       <c r="R121" t="n">
-        <v>6839157</v>
+        <v>6838866</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12969,12 +12969,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -15042,10 +15042,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738286</v>
+        <v>129738150</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15053,21 +15053,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15077,10 +15077,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407586</v>
+        <v>407203</v>
       </c>
       <c r="R143" t="n">
-        <v>6838820</v>
+        <v>6839015</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15139,10 +15139,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738150</v>
+        <v>129738286</v>
       </c>
       <c r="B144" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15150,21 +15150,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15174,10 +15174,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407203</v>
+        <v>407586</v>
       </c>
       <c r="R144" t="n">
-        <v>6839015</v>
+        <v>6838820</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -3968,10 +3968,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129738179</v>
+        <v>129738197</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407483</v>
+        <v>407408</v>
       </c>
       <c r="R31" t="n">
-        <v>6838820</v>
+        <v>6838841</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129739227</v>
+        <v>129739248</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407211</v>
+        <v>407440</v>
       </c>
       <c r="R32" t="n">
         <v>6839027</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129738155</v>
+        <v>129739227</v>
       </c>
       <c r="B33" t="n">
         <v>79700</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407503</v>
+        <v>407211</v>
       </c>
       <c r="R33" t="n">
-        <v>6839131</v>
+        <v>6839027</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,22 +4247,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129738197</v>
+        <v>129738155</v>
       </c>
       <c r="B34" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407408</v>
+        <v>407503</v>
       </c>
       <c r="R34" t="n">
-        <v>6838841</v>
+        <v>6839131</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129739248</v>
+        <v>129738179</v>
       </c>
       <c r="B35" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,21 +4367,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407440</v>
+        <v>407483</v>
       </c>
       <c r="R35" t="n">
-        <v>6839027</v>
+        <v>6838820</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,12 +4441,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738160</v>
+        <v>129738198</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,34 +6261,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407512</v>
+        <v>407575</v>
       </c>
       <c r="R54" t="n">
-        <v>6839214</v>
+        <v>6838839</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,45 +6355,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738291</v>
+        <v>129738255</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407574</v>
+        <v>407645</v>
       </c>
       <c r="R55" t="n">
-        <v>6838848</v>
+        <v>6838797</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6426,6 +6443,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6444,7 +6462,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738168</v>
+        <v>129738160</v>
       </c>
       <c r="B56" t="n">
         <v>79700</v>
@@ -6479,10 +6497,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407717</v>
+        <v>407512</v>
       </c>
       <c r="R56" t="n">
-        <v>6839236</v>
+        <v>6839214</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6541,10 +6559,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129739229</v>
+        <v>129738291</v>
       </c>
       <c r="B57" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,21 +6570,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6576,10 +6594,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407296</v>
+        <v>407574</v>
       </c>
       <c r="R57" t="n">
-        <v>6838974</v>
+        <v>6838848</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,22 +6644,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738198</v>
+        <v>129738168</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6649,42 +6667,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407575</v>
+        <v>407717</v>
       </c>
       <c r="R58" t="n">
-        <v>6838839</v>
+        <v>6839236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6743,54 +6753,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738255</v>
+        <v>129739229</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407645</v>
+        <v>407296</v>
       </c>
       <c r="R59" t="n">
-        <v>6838797</v>
+        <v>6838974</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6831,29 +6832,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129738289</v>
+        <v>129739232</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6861,21 +6861,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407581</v>
+        <v>407441</v>
       </c>
       <c r="R60" t="n">
-        <v>6838815</v>
+        <v>6839017</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6935,22 +6935,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129738277</v>
+        <v>129739244</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6958,21 +6958,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407593</v>
+        <v>407448</v>
       </c>
       <c r="R61" t="n">
-        <v>6838795</v>
+        <v>6838869</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7032,19 +7032,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129739232</v>
+        <v>129739228</v>
       </c>
       <c r="B62" t="n">
         <v>79700</v>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407441</v>
+        <v>407244</v>
       </c>
       <c r="R62" t="n">
-        <v>6839017</v>
+        <v>6839107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7141,7 +7141,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129739244</v>
+        <v>129738189</v>
       </c>
       <c r="B63" t="n">
         <v>79700</v>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407448</v>
+        <v>407407</v>
       </c>
       <c r="R63" t="n">
-        <v>6838869</v>
+        <v>6838839</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7226,57 +7226,66 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129739228</v>
+        <v>129738243</v>
       </c>
       <c r="B64" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407244</v>
+        <v>407117</v>
       </c>
       <c r="R64" t="n">
-        <v>6839107</v>
+        <v>6838831</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7317,28 +7326,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129738189</v>
+        <v>129738289</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7346,21 +7356,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7370,10 +7380,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407407</v>
+        <v>407581</v>
       </c>
       <c r="R65" t="n">
-        <v>6838839</v>
+        <v>6838815</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7432,54 +7442,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129738243</v>
+        <v>129738277</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>407117</v>
+        <v>407593</v>
       </c>
       <c r="R66" t="n">
-        <v>6838831</v>
+        <v>6838795</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7520,7 +7521,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -9121,7 +9121,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129738143</v>
+        <v>129738174</v>
       </c>
       <c r="B83" t="n">
         <v>79700</v>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407137</v>
+        <v>407572</v>
       </c>
       <c r="R83" t="n">
-        <v>6838823</v>
+        <v>6838852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9218,7 +9218,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738165</v>
+        <v>129738143</v>
       </c>
       <c r="B84" t="n">
         <v>79700</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407691</v>
+        <v>407137</v>
       </c>
       <c r="R84" t="n">
-        <v>6839279</v>
+        <v>6838823</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9315,7 +9315,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129739238</v>
+        <v>129738165</v>
       </c>
       <c r="B85" t="n">
         <v>79700</v>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407627</v>
+        <v>407691</v>
       </c>
       <c r="R85" t="n">
-        <v>6839039</v>
+        <v>6839279</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9400,19 +9400,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129738148</v>
+        <v>129739238</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407233</v>
+        <v>407627</v>
       </c>
       <c r="R86" t="n">
-        <v>6838964</v>
+        <v>6839039</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,22 +9497,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129739267</v>
+        <v>129738148</v>
       </c>
       <c r="B87" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9520,21 +9520,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407597</v>
+        <v>407233</v>
       </c>
       <c r="R87" t="n">
-        <v>6838888</v>
+        <v>6838964</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9594,22 +9594,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129738174</v>
+        <v>129739259</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,34 +9617,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407572</v>
+        <v>407549</v>
       </c>
       <c r="R88" t="n">
-        <v>6838852</v>
+        <v>6839053</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9691,22 +9699,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129739259</v>
+        <v>129739267</v>
       </c>
       <c r="B89" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9714,42 +9722,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407549</v>
+        <v>407597</v>
       </c>
       <c r="R89" t="n">
-        <v>6839053</v>
+        <v>6838888</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -13563,45 +13563,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129739287</v>
+        <v>129738248</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407622</v>
+        <v>407481</v>
       </c>
       <c r="R128" t="n">
-        <v>6839045</v>
+        <v>6839152</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13642,63 +13651,73 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738281</v>
+        <v>129738256</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407587</v>
+        <v>407616</v>
       </c>
       <c r="R129" t="n">
-        <v>6838872</v>
+        <v>6838794</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13739,6 +13758,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13757,10 +13777,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129739230</v>
+        <v>129738242</v>
       </c>
       <c r="B130" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,21 +13788,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13792,10 +13812,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407404</v>
+        <v>407719</v>
       </c>
       <c r="R130" t="n">
-        <v>6839005</v>
+        <v>6839222</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13842,22 +13862,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738157</v>
+        <v>129739254</v>
       </c>
       <c r="B131" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,21 +13885,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13889,10 +13909,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407535</v>
+        <v>407418</v>
       </c>
       <c r="R131" t="n">
-        <v>6839193</v>
+        <v>6838867</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13939,22 +13959,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738177</v>
+        <v>129739268</v>
       </c>
       <c r="B132" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13962,34 +13982,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407476</v>
+        <v>407573</v>
       </c>
       <c r="R132" t="n">
-        <v>6838854</v>
+        <v>6838884</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14030,28 +14053,29 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738156</v>
+        <v>129739287</v>
       </c>
       <c r="B133" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14059,21 +14083,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14083,10 +14107,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407477</v>
+        <v>407622</v>
       </c>
       <c r="R133" t="n">
-        <v>6839132</v>
+        <v>6839045</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14133,22 +14157,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738151</v>
+        <v>129738281</v>
       </c>
       <c r="B134" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14156,21 +14180,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14180,10 +14204,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407378</v>
+        <v>407587</v>
       </c>
       <c r="R134" t="n">
-        <v>6839143</v>
+        <v>6838872</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14242,7 +14266,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739235</v>
+        <v>129739230</v>
       </c>
       <c r="B135" t="n">
         <v>79700</v>
@@ -14277,10 +14301,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407604</v>
+        <v>407404</v>
       </c>
       <c r="R135" t="n">
-        <v>6839024</v>
+        <v>6839005</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14339,7 +14363,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129739231</v>
+        <v>129738157</v>
       </c>
       <c r="B136" t="n">
         <v>79700</v>
@@ -14374,10 +14398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407422</v>
+        <v>407535</v>
       </c>
       <c r="R136" t="n">
-        <v>6839006</v>
+        <v>6839193</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14424,66 +14448,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129738248</v>
+        <v>129738177</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407481</v>
+        <v>407476</v>
       </c>
       <c r="R137" t="n">
-        <v>6839152</v>
+        <v>6838854</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14524,7 +14539,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14543,54 +14557,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129738256</v>
+        <v>129738156</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407616</v>
+        <v>407477</v>
       </c>
       <c r="R138" t="n">
-        <v>6838794</v>
+        <v>6839132</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14631,7 +14636,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14650,10 +14654,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129738242</v>
+        <v>129738151</v>
       </c>
       <c r="B139" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14661,21 +14665,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14685,10 +14689,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407719</v>
+        <v>407378</v>
       </c>
       <c r="R139" t="n">
-        <v>6839222</v>
+        <v>6839143</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14747,10 +14751,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129739254</v>
+        <v>129739235</v>
       </c>
       <c r="B140" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14758,21 +14762,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14782,10 +14786,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407418</v>
+        <v>407604</v>
       </c>
       <c r="R140" t="n">
-        <v>6838867</v>
+        <v>6839024</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14844,10 +14848,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129739268</v>
+        <v>129739231</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14855,37 +14859,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407573</v>
+        <v>407422</v>
       </c>
       <c r="R141" t="n">
-        <v>6838884</v>
+        <v>6839006</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14926,7 +14927,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15539,7 +15539,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738166</v>
+        <v>129738164</v>
       </c>
       <c r="B148" t="n">
         <v>79700</v>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407704</v>
+        <v>407666</v>
       </c>
       <c r="R148" t="n">
-        <v>6839251</v>
+        <v>6839269</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129739247</v>
+        <v>129738153</v>
       </c>
       <c r="B149" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407319</v>
+        <v>407474</v>
       </c>
       <c r="R149" t="n">
-        <v>6838979</v>
+        <v>6839108</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15721,22 +15721,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129738164</v>
+        <v>129738274</v>
       </c>
       <c r="B150" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15744,21 +15744,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407666</v>
+        <v>407522</v>
       </c>
       <c r="R150" t="n">
-        <v>6839269</v>
+        <v>6839200</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738153</v>
+        <v>129739288</v>
       </c>
       <c r="B151" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407474</v>
+        <v>407625</v>
       </c>
       <c r="R151" t="n">
-        <v>6839108</v>
+        <v>6839051</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15915,22 +15915,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129738274</v>
+        <v>129738166</v>
       </c>
       <c r="B152" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15938,21 +15938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407522</v>
+        <v>407704</v>
       </c>
       <c r="R152" t="n">
-        <v>6839200</v>
+        <v>6839251</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16024,10 +16024,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129739288</v>
+        <v>129739247</v>
       </c>
       <c r="B153" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>407625</v>
+        <v>407319</v>
       </c>
       <c r="R153" t="n">
-        <v>6839051</v>
+        <v>6838979</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -15539,7 +15539,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738164</v>
+        <v>129738166</v>
       </c>
       <c r="B148" t="n">
         <v>79700</v>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407666</v>
+        <v>407704</v>
       </c>
       <c r="R148" t="n">
-        <v>6839269</v>
+        <v>6839251</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129738153</v>
+        <v>129739247</v>
       </c>
       <c r="B149" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407474</v>
+        <v>407319</v>
       </c>
       <c r="R149" t="n">
-        <v>6839108</v>
+        <v>6838979</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15721,22 +15721,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129738274</v>
+        <v>129738164</v>
       </c>
       <c r="B150" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15744,21 +15744,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407522</v>
+        <v>407666</v>
       </c>
       <c r="R150" t="n">
-        <v>6839200</v>
+        <v>6839269</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129739288</v>
+        <v>129738153</v>
       </c>
       <c r="B151" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407625</v>
+        <v>407474</v>
       </c>
       <c r="R151" t="n">
-        <v>6839051</v>
+        <v>6839108</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15915,22 +15915,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129738166</v>
+        <v>129738274</v>
       </c>
       <c r="B152" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15938,21 +15938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407704</v>
+        <v>407522</v>
       </c>
       <c r="R152" t="n">
-        <v>6839251</v>
+        <v>6839200</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16024,10 +16024,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129739247</v>
+        <v>129739288</v>
       </c>
       <c r="B153" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>407319</v>
+        <v>407625</v>
       </c>
       <c r="R153" t="n">
-        <v>6838979</v>
+        <v>6839051</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129739257</v>
+        <v>129738278</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,42 +2490,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407574</v>
+        <v>407601</v>
       </c>
       <c r="R16" t="n">
-        <v>6839050</v>
+        <v>6838838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2572,22 +2564,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129738266</v>
+        <v>129739237</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,42 +2587,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407598</v>
+        <v>407617</v>
       </c>
       <c r="R17" t="n">
-        <v>6838839</v>
+        <v>6839035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2677,22 +2661,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129739256</v>
+        <v>129738187</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,42 +2684,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407082</v>
+        <v>407437</v>
       </c>
       <c r="R18" t="n">
-        <v>6838747</v>
+        <v>6838840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2782,22 +2758,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738278</v>
+        <v>129738167</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,21 +2781,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2829,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407601</v>
+        <v>407714</v>
       </c>
       <c r="R19" t="n">
-        <v>6838838</v>
+        <v>6839244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2891,7 +2867,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738187</v>
+        <v>129738159</v>
       </c>
       <c r="B20" t="n">
         <v>79700</v>
@@ -2926,10 +2902,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407437</v>
+        <v>407516</v>
       </c>
       <c r="R20" t="n">
-        <v>6838840</v>
+        <v>6839209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2988,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738167</v>
+        <v>129739257</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,34 +2975,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407714</v>
+        <v>407574</v>
       </c>
       <c r="R21" t="n">
-        <v>6839244</v>
+        <v>6839050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3073,22 +3057,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738159</v>
+        <v>129738266</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,34 +3080,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407516</v>
+        <v>407598</v>
       </c>
       <c r="R22" t="n">
-        <v>6839209</v>
+        <v>6838839</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3182,10 +3174,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739237</v>
+        <v>129739256</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3193,34 +3185,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407617</v>
+        <v>407082</v>
       </c>
       <c r="R23" t="n">
-        <v>6839035</v>
+        <v>6838747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,45 +3279,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129739265</v>
+        <v>129738245</v>
       </c>
       <c r="B24" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407615</v>
+        <v>407233</v>
       </c>
       <c r="R24" t="n">
-        <v>6839034</v>
+        <v>6838838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3358,72 +3367,64 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129738245</v>
+        <v>129739265</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407233</v>
+        <v>407615</v>
       </c>
       <c r="R25" t="n">
-        <v>6838838</v>
+        <v>6839034</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3464,29 +3465,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129738154</v>
+        <v>129739291</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,21 +3494,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407536</v>
+        <v>407656</v>
       </c>
       <c r="R26" t="n">
-        <v>6839138</v>
+        <v>6839031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3568,22 +3568,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129739291</v>
+        <v>129738154</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,21 +3591,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407656</v>
+        <v>407536</v>
       </c>
       <c r="R27" t="n">
-        <v>6839031</v>
+        <v>6839138</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,12 +3665,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4453,45 +4453,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738184</v>
+        <v>129738246</v>
       </c>
       <c r="B36" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407445</v>
+        <v>407154</v>
       </c>
       <c r="R36" t="n">
-        <v>6838844</v>
+        <v>6838842</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4532,6 +4541,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4550,45 +4560,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129738158</v>
+        <v>129739270</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407519</v>
+        <v>407283</v>
       </c>
       <c r="R37" t="n">
-        <v>6839207</v>
+        <v>6839055</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4629,28 +4648,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129738287</v>
+        <v>129738184</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,21 +4678,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4682,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407591</v>
+        <v>407445</v>
       </c>
       <c r="R38" t="n">
-        <v>6838814</v>
+        <v>6838844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4744,7 +4764,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738283</v>
+        <v>129738287</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4773,19 +4793,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407598</v>
+        <v>407591</v>
       </c>
       <c r="R39" t="n">
-        <v>6838839</v>
+        <v>6838814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4820,18 +4837,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4850,10 +4861,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129739271</v>
+        <v>129738283</v>
       </c>
       <c r="B40" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,34 +4872,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407647</v>
+        <v>407598</v>
       </c>
       <c r="R40" t="n">
-        <v>6838874</v>
+        <v>6838839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4923,78 +4937,75 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738246</v>
+        <v>129739271</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>78838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407154</v>
+        <v>407647</v>
       </c>
       <c r="R41" t="n">
-        <v>6838842</v>
+        <v>6838874</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5035,73 +5046,63 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129739270</v>
+        <v>129738149</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407283</v>
+        <v>407199</v>
       </c>
       <c r="R42" t="n">
-        <v>6839055</v>
+        <v>6838976</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5142,26 +5143,25 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129738149</v>
+        <v>129738158</v>
       </c>
       <c r="B43" t="n">
         <v>79700</v>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407199</v>
+        <v>407519</v>
       </c>
       <c r="R43" t="n">
-        <v>6838976</v>
+        <v>6839207</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738290</v>
+        <v>129739240</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407575</v>
+        <v>407581</v>
       </c>
       <c r="R44" t="n">
-        <v>6838839</v>
+        <v>6838885</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5343,22 +5343,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738204</v>
+        <v>129738186</v>
       </c>
       <c r="B45" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,42 +5366,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407170</v>
+        <v>407479</v>
       </c>
       <c r="R45" t="n">
-        <v>6838942</v>
+        <v>6838810</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5460,10 +5452,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738292</v>
+        <v>129738290</v>
       </c>
       <c r="B46" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5471,21 +5463,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5495,10 +5487,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407528</v>
+        <v>407575</v>
       </c>
       <c r="R46" t="n">
-        <v>6839142</v>
+        <v>6838839</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5557,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129739240</v>
+        <v>129738292</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5568,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5592,10 +5584,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407581</v>
+        <v>407528</v>
       </c>
       <c r="R47" t="n">
-        <v>6838885</v>
+        <v>6839142</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,22 +5634,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738186</v>
+        <v>129738204</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5665,34 +5657,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407479</v>
+        <v>407170</v>
       </c>
       <c r="R48" t="n">
-        <v>6838810</v>
+        <v>6838942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6355,54 +6355,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738255</v>
+        <v>129738160</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407645</v>
+        <v>407512</v>
       </c>
       <c r="R55" t="n">
-        <v>6838797</v>
+        <v>6839214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6443,7 +6434,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6462,10 +6452,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738160</v>
+        <v>129738291</v>
       </c>
       <c r="B56" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6473,21 +6463,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6497,10 +6487,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407512</v>
+        <v>407574</v>
       </c>
       <c r="R56" t="n">
-        <v>6839214</v>
+        <v>6838848</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6559,10 +6549,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738291</v>
+        <v>129738168</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6570,21 +6560,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6594,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407574</v>
+        <v>407717</v>
       </c>
       <c r="R57" t="n">
-        <v>6838848</v>
+        <v>6839236</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6656,7 +6646,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738168</v>
+        <v>129739229</v>
       </c>
       <c r="B58" t="n">
         <v>79700</v>
@@ -6691,10 +6681,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407717</v>
+        <v>407296</v>
       </c>
       <c r="R58" t="n">
-        <v>6839236</v>
+        <v>6838974</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6741,57 +6731,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129739229</v>
+        <v>129738255</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407296</v>
+        <v>407645</v>
       </c>
       <c r="R59" t="n">
-        <v>6838974</v>
+        <v>6838797</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6832,18 +6831,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129739228</v>
+        <v>129738289</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407244</v>
+        <v>407581</v>
       </c>
       <c r="R62" t="n">
-        <v>6839107</v>
+        <v>6838815</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7129,22 +7129,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129738189</v>
+        <v>129738277</v>
       </c>
       <c r="B63" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407407</v>
+        <v>407593</v>
       </c>
       <c r="R63" t="n">
-        <v>6838839</v>
+        <v>6838795</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7238,54 +7238,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129738243</v>
+        <v>129739228</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407117</v>
+        <v>407244</v>
       </c>
       <c r="R64" t="n">
-        <v>6838831</v>
+        <v>6839107</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,29 +7317,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129738289</v>
+        <v>129738189</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7356,21 +7346,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7380,10 +7370,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407581</v>
+        <v>407407</v>
       </c>
       <c r="R65" t="n">
-        <v>6838815</v>
+        <v>6838839</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7442,45 +7432,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129738277</v>
+        <v>129738243</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>407593</v>
+        <v>407117</v>
       </c>
       <c r="R66" t="n">
-        <v>6838795</v>
+        <v>6838831</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7521,6 +7520,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7834,7 +7834,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129739225</v>
+        <v>129738169</v>
       </c>
       <c r="B70" t="n">
         <v>79700</v>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407184</v>
+        <v>407672</v>
       </c>
       <c r="R70" t="n">
-        <v>6839011</v>
+        <v>6838825</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7919,19 +7919,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129738169</v>
+        <v>129739245</v>
       </c>
       <c r="B71" t="n">
         <v>79700</v>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407672</v>
+        <v>407443</v>
       </c>
       <c r="R71" t="n">
-        <v>6838825</v>
+        <v>6838872</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8016,19 +8016,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129739245</v>
+        <v>129739225</v>
       </c>
       <c r="B72" t="n">
         <v>79700</v>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407443</v>
+        <v>407184</v>
       </c>
       <c r="R72" t="n">
-        <v>6838872</v>
+        <v>6839011</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8335,10 +8335,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738147</v>
+        <v>129738275</v>
       </c>
       <c r="B75" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407190</v>
+        <v>407608</v>
       </c>
       <c r="R75" t="n">
-        <v>6838950</v>
+        <v>6839252</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738176</v>
+        <v>129738285</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8443,21 +8443,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407519</v>
+        <v>407587</v>
       </c>
       <c r="R76" t="n">
-        <v>6838831</v>
+        <v>6838806</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738171</v>
+        <v>129738147</v>
       </c>
       <c r="B77" t="n">
         <v>79700</v>
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407620</v>
+        <v>407190</v>
       </c>
       <c r="R77" t="n">
-        <v>6838898</v>
+        <v>6838950</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738181</v>
+        <v>129738176</v>
       </c>
       <c r="B78" t="n">
         <v>79700</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407467</v>
+        <v>407519</v>
       </c>
       <c r="R78" t="n">
-        <v>6838834</v>
+        <v>6838831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738275</v>
+        <v>129738171</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8734,21 +8734,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407608</v>
+        <v>407620</v>
       </c>
       <c r="R79" t="n">
-        <v>6839252</v>
+        <v>6838898</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738285</v>
+        <v>129738181</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8831,21 +8831,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407587</v>
+        <v>407467</v>
       </c>
       <c r="R80" t="n">
-        <v>6838806</v>
+        <v>6838834</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,54 +8917,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738244</v>
+        <v>129738194</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407231</v>
+        <v>407549</v>
       </c>
       <c r="R81" t="n">
-        <v>6838827</v>
+        <v>6838809</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9005,7 +8996,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9024,45 +9014,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B82" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R82" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,6 +9102,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129738174</v>
+        <v>129739259</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9132,34 +9132,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407572</v>
+        <v>407549</v>
       </c>
       <c r="R83" t="n">
-        <v>6838852</v>
+        <v>6839053</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9206,19 +9214,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738143</v>
+        <v>129738174</v>
       </c>
       <c r="B84" t="n">
         <v>79700</v>
@@ -9253,10 +9261,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407137</v>
+        <v>407572</v>
       </c>
       <c r="R84" t="n">
-        <v>6838823</v>
+        <v>6838852</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9315,7 +9323,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738165</v>
+        <v>129738143</v>
       </c>
       <c r="B85" t="n">
         <v>79700</v>
@@ -9350,10 +9358,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407691</v>
+        <v>407137</v>
       </c>
       <c r="R85" t="n">
-        <v>6839279</v>
+        <v>6838823</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9412,7 +9420,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129739238</v>
+        <v>129738165</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9447,10 +9455,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407627</v>
+        <v>407691</v>
       </c>
       <c r="R86" t="n">
-        <v>6839039</v>
+        <v>6839279</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,19 +9505,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129738148</v>
+        <v>129739238</v>
       </c>
       <c r="B87" t="n">
         <v>79700</v>
@@ -9544,10 +9552,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407233</v>
+        <v>407627</v>
       </c>
       <c r="R87" t="n">
-        <v>6838964</v>
+        <v>6839039</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9594,22 +9602,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129739259</v>
+        <v>129738148</v>
       </c>
       <c r="B88" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,42 +9625,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407549</v>
+        <v>407233</v>
       </c>
       <c r="R88" t="n">
-        <v>6839053</v>
+        <v>6838964</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,12 +9699,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9808,7 +9808,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129739239</v>
+        <v>129739246</v>
       </c>
       <c r="B90" t="n">
         <v>79700</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407614</v>
+        <v>407427</v>
       </c>
       <c r="R90" t="n">
-        <v>6838900</v>
+        <v>6838886</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9905,54 +9905,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129738227</v>
+        <v>129739239</v>
       </c>
       <c r="B91" t="n">
-        <v>5480</v>
+        <v>79700</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407545</v>
+        <v>407614</v>
       </c>
       <c r="R91" t="n">
-        <v>6839241</v>
+        <v>6838900</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9993,29 +9984,28 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129739258</v>
+        <v>129738170</v>
       </c>
       <c r="B92" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10023,42 +10013,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407616</v>
+        <v>407660</v>
       </c>
       <c r="R92" t="n">
-        <v>6838890</v>
+        <v>6838791</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10105,19 +10087,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129739246</v>
+        <v>129738188</v>
       </c>
       <c r="B93" t="n">
         <v>79700</v>
@@ -10152,10 +10134,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407427</v>
+        <v>407408</v>
       </c>
       <c r="R93" t="n">
-        <v>6838886</v>
+        <v>6838841</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10202,22 +10184,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129738170</v>
+        <v>129739258</v>
       </c>
       <c r="B94" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10225,34 +10207,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407660</v>
+        <v>407616</v>
       </c>
       <c r="R94" t="n">
-        <v>6838791</v>
+        <v>6838890</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10299,57 +10289,66 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129738188</v>
+        <v>129738227</v>
       </c>
       <c r="B95" t="n">
-        <v>79700</v>
+        <v>5480</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407408</v>
+        <v>407545</v>
       </c>
       <c r="R95" t="n">
-        <v>6838841</v>
+        <v>6839241</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10390,6 +10389,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10505,7 +10505,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129738185</v>
+        <v>129738144</v>
       </c>
       <c r="B97" t="n">
         <v>79700</v>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407439</v>
+        <v>407223</v>
       </c>
       <c r="R97" t="n">
-        <v>6838837</v>
+        <v>6838821</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10602,10 +10602,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129739289</v>
+        <v>129738185</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10613,21 +10613,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407649</v>
+        <v>407439</v>
       </c>
       <c r="R98" t="n">
-        <v>6839041</v>
+        <v>6838837</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10687,22 +10687,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129738144</v>
+        <v>129739289</v>
       </c>
       <c r="B99" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407223</v>
+        <v>407649</v>
       </c>
       <c r="R99" t="n">
-        <v>6838821</v>
+        <v>6839041</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10784,12 +10784,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -11679,10 +11679,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738276</v>
+        <v>129738180</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11690,21 +11690,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407607</v>
+        <v>407480</v>
       </c>
       <c r="R109" t="n">
-        <v>6838798</v>
+        <v>6838840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11776,10 +11776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738180</v>
+        <v>129738276</v>
       </c>
       <c r="B110" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407480</v>
+        <v>407607</v>
       </c>
       <c r="R110" t="n">
-        <v>6838840</v>
+        <v>6838798</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129738280</v>
+        <v>129739243</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,37 +12290,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407623</v>
+        <v>407451</v>
       </c>
       <c r="R115" t="n">
-        <v>6838894</v>
+        <v>6838866</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12355,40 +12352,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129739224</v>
+        <v>129738280</v>
       </c>
       <c r="B116" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12396,34 +12387,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407121</v>
+        <v>407623</v>
       </c>
       <c r="R116" t="n">
-        <v>6838895</v>
+        <v>6838894</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12458,31 +12452,37 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129738282</v>
+        <v>129739290</v>
       </c>
       <c r="B117" t="n">
         <v>79081</v>
@@ -12511,16 +12511,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407588</v>
+        <v>407657</v>
       </c>
       <c r="R117" t="n">
-        <v>6838831</v>
+        <v>6839033</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12557,7 +12560,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12566,28 +12569,29 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129738192</v>
+        <v>129738282</v>
       </c>
       <c r="B118" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12595,21 +12599,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12619,10 +12623,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407464</v>
+        <v>407588</v>
       </c>
       <c r="R118" t="n">
-        <v>6839157</v>
+        <v>6838831</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12655,6 +12659,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12681,10 +12690,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129739290</v>
+        <v>129738145</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12692,37 +12701,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407657</v>
+        <v>407194</v>
       </c>
       <c r="R119" t="n">
-        <v>6839033</v>
+        <v>6838873</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12757,40 +12763,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738145</v>
+        <v>129738192</v>
       </c>
       <c r="B120" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12822,10 +12822,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407194</v>
+        <v>407464</v>
       </c>
       <c r="R120" t="n">
-        <v>6838873</v>
+        <v>6839157</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12884,7 +12884,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129739243</v>
+        <v>129739224</v>
       </c>
       <c r="B121" t="n">
         <v>79700</v>
@@ -12919,10 +12919,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407451</v>
+        <v>407121</v>
       </c>
       <c r="R121" t="n">
-        <v>6838866</v>
+        <v>6838895</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13078,7 +13078,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129738288</v>
+        <v>129738279</v>
       </c>
       <c r="B123" t="n">
         <v>79081</v>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407592</v>
+        <v>407617</v>
       </c>
       <c r="R123" t="n">
-        <v>6838822</v>
+        <v>6838855</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13175,7 +13175,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129738279</v>
+        <v>129738288</v>
       </c>
       <c r="B124" t="n">
         <v>79081</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407617</v>
+        <v>407592</v>
       </c>
       <c r="R124" t="n">
-        <v>6838855</v>
+        <v>6838822</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13563,54 +13563,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129738248</v>
+        <v>129738157</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407481</v>
+        <v>407535</v>
       </c>
       <c r="R128" t="n">
-        <v>6839152</v>
+        <v>6839193</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13651,7 +13642,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13670,54 +13660,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738256</v>
+        <v>129739287</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407616</v>
+        <v>407622</v>
       </c>
       <c r="R129" t="n">
-        <v>6838794</v>
+        <v>6839045</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13758,29 +13739,28 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129738242</v>
+        <v>129738281</v>
       </c>
       <c r="B130" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13788,21 +13768,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13812,10 +13792,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407719</v>
+        <v>407587</v>
       </c>
       <c r="R130" t="n">
-        <v>6839222</v>
+        <v>6838872</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13874,10 +13854,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129739254</v>
+        <v>129738177</v>
       </c>
       <c r="B131" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13885,21 +13865,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13909,10 +13889,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407418</v>
+        <v>407476</v>
       </c>
       <c r="R131" t="n">
-        <v>6838867</v>
+        <v>6838854</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13959,22 +13939,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129739268</v>
+        <v>129738156</v>
       </c>
       <c r="B132" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13982,37 +13962,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407573</v>
+        <v>407477</v>
       </c>
       <c r="R132" t="n">
-        <v>6838884</v>
+        <v>6839132</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14053,29 +14030,28 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129739287</v>
+        <v>129739230</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14083,21 +14059,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14107,10 +14083,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407622</v>
+        <v>407404</v>
       </c>
       <c r="R133" t="n">
-        <v>6839045</v>
+        <v>6839005</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14169,10 +14145,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738281</v>
+        <v>129738151</v>
       </c>
       <c r="B134" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14180,21 +14156,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14204,10 +14180,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407587</v>
+        <v>407378</v>
       </c>
       <c r="R134" t="n">
-        <v>6838872</v>
+        <v>6839143</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14266,7 +14242,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739230</v>
+        <v>129739235</v>
       </c>
       <c r="B135" t="n">
         <v>79700</v>
@@ -14301,10 +14277,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407404</v>
+        <v>407604</v>
       </c>
       <c r="R135" t="n">
-        <v>6839005</v>
+        <v>6839024</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14363,7 +14339,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129738157</v>
+        <v>129739231</v>
       </c>
       <c r="B136" t="n">
         <v>79700</v>
@@ -14398,10 +14374,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407535</v>
+        <v>407422</v>
       </c>
       <c r="R136" t="n">
-        <v>6839193</v>
+        <v>6839006</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14448,57 +14424,66 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129738177</v>
+        <v>129738248</v>
       </c>
       <c r="B137" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407476</v>
+        <v>407481</v>
       </c>
       <c r="R137" t="n">
-        <v>6838854</v>
+        <v>6839152</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14539,6 +14524,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14557,45 +14543,54 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129738156</v>
+        <v>129738256</v>
       </c>
       <c r="B138" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407477</v>
+        <v>407616</v>
       </c>
       <c r="R138" t="n">
-        <v>6839132</v>
+        <v>6838794</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14636,6 +14631,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14654,10 +14650,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129738151</v>
+        <v>129738242</v>
       </c>
       <c r="B139" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14665,21 +14661,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14689,10 +14685,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407378</v>
+        <v>407719</v>
       </c>
       <c r="R139" t="n">
-        <v>6839143</v>
+        <v>6839222</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14751,10 +14747,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129739235</v>
+        <v>129739254</v>
       </c>
       <c r="B140" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14762,21 +14758,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14786,10 +14782,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407604</v>
+        <v>407418</v>
       </c>
       <c r="R140" t="n">
-        <v>6839024</v>
+        <v>6838867</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14848,10 +14844,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129739231</v>
+        <v>129739268</v>
       </c>
       <c r="B141" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14859,34 +14855,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407422</v>
+        <v>407573</v>
       </c>
       <c r="R141" t="n">
-        <v>6839006</v>
+        <v>6838884</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14927,6 +14926,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14945,10 +14945,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738284</v>
+        <v>129738150</v>
       </c>
       <c r="B142" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,21 +14956,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407595</v>
+        <v>407203</v>
       </c>
       <c r="R142" t="n">
-        <v>6838836</v>
+        <v>6839015</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15042,10 +15042,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738150</v>
+        <v>129738286</v>
       </c>
       <c r="B143" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15053,21 +15053,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15077,10 +15077,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407203</v>
+        <v>407586</v>
       </c>
       <c r="R143" t="n">
-        <v>6839015</v>
+        <v>6838820</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15139,7 +15139,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738286</v>
+        <v>129738284</v>
       </c>
       <c r="B144" t="n">
         <v>79081</v>
@@ -15174,10 +15174,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407586</v>
+        <v>407595</v>
       </c>
       <c r="R144" t="n">
-        <v>6838820</v>
+        <v>6838836</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15236,10 +15236,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738201</v>
+        <v>129739253</v>
       </c>
       <c r="B145" t="n">
-        <v>57896</v>
+        <v>79671</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15247,31 +15247,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15279,10 +15274,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407530</v>
+        <v>407589</v>
       </c>
       <c r="R145" t="n">
-        <v>6839196</v>
+        <v>6838889</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15323,25 +15318,26 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129739253</v>
+        <v>129738195</v>
       </c>
       <c r="B146" t="n">
         <v>79671</v>
@@ -15370,19 +15366,16 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407589</v>
+        <v>407479</v>
       </c>
       <c r="R146" t="n">
-        <v>6838889</v>
+        <v>6838852</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15423,29 +15416,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738195</v>
+        <v>129738201</v>
       </c>
       <c r="B147" t="n">
-        <v>79671</v>
+        <v>57896</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15453,34 +15445,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407479</v>
+        <v>407530</v>
       </c>
       <c r="R147" t="n">
-        <v>6838852</v>
+        <v>6839196</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15539,7 +15539,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738166</v>
+        <v>129738164</v>
       </c>
       <c r="B148" t="n">
         <v>79700</v>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407704</v>
+        <v>407666</v>
       </c>
       <c r="R148" t="n">
-        <v>6839251</v>
+        <v>6839269</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129739247</v>
+        <v>129738153</v>
       </c>
       <c r="B149" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407319</v>
+        <v>407474</v>
       </c>
       <c r="R149" t="n">
-        <v>6838979</v>
+        <v>6839108</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15721,19 +15721,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129738164</v>
+        <v>129738166</v>
       </c>
       <c r="B150" t="n">
         <v>79700</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407666</v>
+        <v>407704</v>
       </c>
       <c r="R150" t="n">
-        <v>6839269</v>
+        <v>6839251</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738153</v>
+        <v>129738274</v>
       </c>
       <c r="B151" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407474</v>
+        <v>407522</v>
       </c>
       <c r="R151" t="n">
-        <v>6839108</v>
+        <v>6839200</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15927,7 +15927,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129738274</v>
+        <v>129739288</v>
       </c>
       <c r="B152" t="n">
         <v>79081</v>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407522</v>
+        <v>407625</v>
       </c>
       <c r="R152" t="n">
-        <v>6839200</v>
+        <v>6839051</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16012,22 +16012,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129739288</v>
+        <v>129739247</v>
       </c>
       <c r="B153" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>407625</v>
+        <v>407319</v>
       </c>
       <c r="R153" t="n">
-        <v>6839051</v>
+        <v>6838979</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129738278</v>
+        <v>129739257</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,34 +2490,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407601</v>
+        <v>407574</v>
       </c>
       <c r="R16" t="n">
-        <v>6838838</v>
+        <v>6839050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,22 +2572,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129739237</v>
+        <v>129738266</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,34 +2595,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407617</v>
+        <v>407598</v>
       </c>
       <c r="R17" t="n">
-        <v>6839035</v>
+        <v>6838839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2661,22 +2677,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738187</v>
+        <v>129739256</v>
       </c>
       <c r="B18" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,34 +2700,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407437</v>
+        <v>407082</v>
       </c>
       <c r="R18" t="n">
-        <v>6838840</v>
+        <v>6838747</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2758,22 +2782,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738167</v>
+        <v>129738278</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,21 +2805,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,10 +2829,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407714</v>
+        <v>407601</v>
       </c>
       <c r="R19" t="n">
-        <v>6839244</v>
+        <v>6838838</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2867,7 +2891,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738159</v>
+        <v>129739237</v>
       </c>
       <c r="B20" t="n">
         <v>79700</v>
@@ -2902,10 +2926,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407516</v>
+        <v>407617</v>
       </c>
       <c r="R20" t="n">
-        <v>6839209</v>
+        <v>6839035</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2952,22 +2976,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129739257</v>
+        <v>129738187</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,42 +2999,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407574</v>
+        <v>407437</v>
       </c>
       <c r="R21" t="n">
-        <v>6839050</v>
+        <v>6838840</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3057,22 +3073,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738266</v>
+        <v>129738167</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,42 +3096,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407598</v>
+        <v>407714</v>
       </c>
       <c r="R22" t="n">
-        <v>6838839</v>
+        <v>6839244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3174,10 +3182,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739256</v>
+        <v>129738159</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,42 +3193,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407082</v>
+        <v>407516</v>
       </c>
       <c r="R23" t="n">
-        <v>6838747</v>
+        <v>6839209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,66 +3267,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738245</v>
+        <v>129739265</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407233</v>
+        <v>407615</v>
       </c>
       <c r="R24" t="n">
-        <v>6838838</v>
+        <v>6839034</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3367,64 +3358,72 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129739265</v>
+        <v>129738245</v>
       </c>
       <c r="B25" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407615</v>
+        <v>407233</v>
       </c>
       <c r="R25" t="n">
-        <v>6839034</v>
+        <v>6838838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3465,18 +3464,19 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129738197</v>
+        <v>129739227</v>
       </c>
       <c r="B31" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407408</v>
+        <v>407211</v>
       </c>
       <c r="R31" t="n">
-        <v>6838841</v>
+        <v>6839027</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,22 +4053,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129739248</v>
+        <v>129738155</v>
       </c>
       <c r="B32" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407440</v>
+        <v>407503</v>
       </c>
       <c r="R32" t="n">
-        <v>6839027</v>
+        <v>6839131</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,19 +4150,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129739227</v>
+        <v>129738179</v>
       </c>
       <c r="B33" t="n">
         <v>79700</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407211</v>
+        <v>407483</v>
       </c>
       <c r="R33" t="n">
-        <v>6839027</v>
+        <v>6838820</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,22 +4247,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129738155</v>
+        <v>129738197</v>
       </c>
       <c r="B34" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407503</v>
+        <v>407408</v>
       </c>
       <c r="R34" t="n">
-        <v>6839131</v>
+        <v>6838841</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129738179</v>
+        <v>129739248</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,21 +4367,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407483</v>
+        <v>407440</v>
       </c>
       <c r="R35" t="n">
-        <v>6838820</v>
+        <v>6839027</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,12 +4441,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129738184</v>
+        <v>129738158</v>
       </c>
       <c r="B38" t="n">
         <v>79700</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407445</v>
+        <v>407519</v>
       </c>
       <c r="R38" t="n">
-        <v>6838844</v>
+        <v>6839207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738287</v>
+        <v>129738283</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4793,16 +4793,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407591</v>
+        <v>407598</v>
       </c>
       <c r="R39" t="n">
-        <v>6838814</v>
+        <v>6838839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4837,12 +4840,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4861,10 +4870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738283</v>
+        <v>129739271</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4872,37 +4881,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407598</v>
+        <v>407647</v>
       </c>
       <c r="R40" t="n">
-        <v>6838839</v>
+        <v>6838874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4937,40 +4943,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129739271</v>
+        <v>129738184</v>
       </c>
       <c r="B41" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4978,21 +4978,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407647</v>
+        <v>407445</v>
       </c>
       <c r="R41" t="n">
-        <v>6838874</v>
+        <v>6838844</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5052,12 +5052,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129738158</v>
+        <v>129738287</v>
       </c>
       <c r="B43" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5172,21 +5172,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407519</v>
+        <v>407591</v>
       </c>
       <c r="R43" t="n">
-        <v>6839207</v>
+        <v>6838814</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738292</v>
+        <v>129738204</v>
       </c>
       <c r="B47" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,34 +5560,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407528</v>
+        <v>407170</v>
       </c>
       <c r="R47" t="n">
-        <v>6839142</v>
+        <v>6838942</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5646,40 +5654,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738204</v>
+        <v>129738247</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5689,10 +5698,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407170</v>
+        <v>407158</v>
       </c>
       <c r="R48" t="n">
-        <v>6838942</v>
+        <v>6838902</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5733,6 +5742,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5751,43 +5761,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129738247</v>
+        <v>129739250</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5795,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407158</v>
+        <v>407493</v>
       </c>
       <c r="R49" t="n">
-        <v>6838902</v>
+        <v>6839112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5846,22 +5850,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129739250</v>
+        <v>129738292</v>
       </c>
       <c r="B50" t="n">
-        <v>79671</v>
+        <v>78747</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5869,37 +5873,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407493</v>
+        <v>407528</v>
       </c>
       <c r="R50" t="n">
-        <v>6839112</v>
+        <v>6839142</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5940,29 +5941,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129738152</v>
+        <v>129738196</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5970,21 +5970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407440</v>
+        <v>407436</v>
       </c>
       <c r="R51" t="n">
-        <v>6839113</v>
+        <v>6838838</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129739234</v>
+        <v>129738152</v>
       </c>
       <c r="B52" t="n">
         <v>79700</v>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407466</v>
+        <v>407440</v>
       </c>
       <c r="R52" t="n">
-        <v>6839082</v>
+        <v>6839113</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6141,22 +6141,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129738196</v>
+        <v>129739234</v>
       </c>
       <c r="B53" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407436</v>
+        <v>407466</v>
       </c>
       <c r="R53" t="n">
-        <v>6838838</v>
+        <v>6839082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6238,12 +6238,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129739264</v>
+        <v>129738199</v>
       </c>
       <c r="B67" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7550,34 +7550,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407129</v>
+        <v>407576</v>
       </c>
       <c r="R67" t="n">
-        <v>6838913</v>
+        <v>6838847</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7624,57 +7632,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738193</v>
+        <v>129738257</v>
       </c>
       <c r="B68" t="n">
-        <v>79671</v>
+        <v>58106</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407714</v>
+        <v>407464</v>
       </c>
       <c r="R68" t="n">
-        <v>6839244</v>
+        <v>6839159</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7733,10 +7749,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739292</v>
+        <v>129739264</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7744,37 +7760,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407632</v>
+        <v>407129</v>
       </c>
       <c r="R69" t="n">
-        <v>6838901</v>
+        <v>6838913</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7815,7 +7828,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7834,10 +7846,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129738169</v>
+        <v>129738193</v>
       </c>
       <c r="B70" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7845,21 +7857,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7869,10 +7881,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407672</v>
+        <v>407714</v>
       </c>
       <c r="R70" t="n">
-        <v>6838825</v>
+        <v>6839244</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7931,10 +7943,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129739245</v>
+        <v>129739292</v>
       </c>
       <c r="B71" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7942,34 +7954,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407443</v>
+        <v>407632</v>
       </c>
       <c r="R71" t="n">
-        <v>6838872</v>
+        <v>6838901</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8010,6 +8025,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8028,7 +8044,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129739225</v>
+        <v>129738169</v>
       </c>
       <c r="B72" t="n">
         <v>79700</v>
@@ -8063,10 +8079,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407184</v>
+        <v>407672</v>
       </c>
       <c r="R72" t="n">
-        <v>6839011</v>
+        <v>6838825</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8113,22 +8129,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129738199</v>
+        <v>129739245</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8136,42 +8152,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407576</v>
+        <v>407443</v>
       </c>
       <c r="R73" t="n">
-        <v>6838847</v>
+        <v>6838872</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8218,65 +8226,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129738257</v>
+        <v>129739225</v>
       </c>
       <c r="B74" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407464</v>
+        <v>407184</v>
       </c>
       <c r="R74" t="n">
-        <v>6839159</v>
+        <v>6839011</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8323,12 +8323,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8917,45 +8917,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B81" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R81" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8996,6 +9005,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9014,54 +9024,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738244</v>
+        <v>129738194</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407231</v>
+        <v>407549</v>
       </c>
       <c r="R82" t="n">
-        <v>6838827</v>
+        <v>6838809</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9102,7 +9103,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129739258</v>
+        <v>129739255</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>79671</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10207,42 +10207,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407616</v>
+        <v>407411</v>
       </c>
       <c r="R94" t="n">
-        <v>6838890</v>
+        <v>6838819</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10301,41 +10293,40 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129738227</v>
+        <v>129739258</v>
       </c>
       <c r="B95" t="n">
-        <v>5480</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>101920</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10345,10 +10336,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407545</v>
+        <v>407616</v>
       </c>
       <c r="R95" t="n">
-        <v>6839241</v>
+        <v>6838890</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10389,64 +10380,72 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129739255</v>
+        <v>129738227</v>
       </c>
       <c r="B96" t="n">
-        <v>79671</v>
+        <v>5480</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>101920</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407411</v>
+        <v>407545</v>
       </c>
       <c r="R96" t="n">
-        <v>6838819</v>
+        <v>6839241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10487,18 +10486,19 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129739289</v>
+        <v>129738172</v>
       </c>
       <c r="B99" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407649</v>
+        <v>407585</v>
       </c>
       <c r="R99" t="n">
-        <v>6839041</v>
+        <v>6838872</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10784,19 +10784,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129738172</v>
+        <v>129739242</v>
       </c>
       <c r="B100" t="n">
         <v>79700</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407585</v>
+        <v>407515</v>
       </c>
       <c r="R100" t="n">
-        <v>6838872</v>
+        <v>6838875</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10881,22 +10881,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129739242</v>
+        <v>129739289</v>
       </c>
       <c r="B101" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10904,21 +10904,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407515</v>
+        <v>407649</v>
       </c>
       <c r="R101" t="n">
-        <v>6838875</v>
+        <v>6839041</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10990,54 +10990,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129738250</v>
+        <v>129739252</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407525</v>
+        <v>407615</v>
       </c>
       <c r="R102" t="n">
-        <v>6839244</v>
+        <v>6839041</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11078,26 +11069,25 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129739252</v>
+        <v>129738191</v>
       </c>
       <c r="B103" t="n">
         <v>79671</v>
@@ -11132,10 +11122,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407615</v>
+        <v>407474</v>
       </c>
       <c r="R103" t="n">
-        <v>6839041</v>
+        <v>6839108</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11182,19 +11172,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129738191</v>
+        <v>129739251</v>
       </c>
       <c r="B104" t="n">
         <v>79671</v>
@@ -11229,10 +11219,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407474</v>
+        <v>407563</v>
       </c>
       <c r="R104" t="n">
-        <v>6839108</v>
+        <v>6839056</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11279,57 +11269,66 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129739251</v>
+        <v>129738250</v>
       </c>
       <c r="B105" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407563</v>
+        <v>407525</v>
       </c>
       <c r="R105" t="n">
-        <v>6839056</v>
+        <v>6839244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11370,18 +11369,19 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129738280</v>
+        <v>129738145</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12387,37 +12387,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407623</v>
+        <v>407194</v>
       </c>
       <c r="R116" t="n">
-        <v>6838894</v>
+        <v>6838873</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12452,18 +12449,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12482,7 +12473,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129739290</v>
+        <v>129738280</v>
       </c>
       <c r="B117" t="n">
         <v>79081</v>
@@ -12520,10 +12511,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407657</v>
+        <v>407623</v>
       </c>
       <c r="R117" t="n">
-        <v>6839033</v>
+        <v>6838894</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12560,7 +12551,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12576,22 +12567,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129738282</v>
+        <v>129739224</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12599,21 +12590,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12623,10 +12614,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407588</v>
+        <v>407121</v>
       </c>
       <c r="R118" t="n">
-        <v>6838831</v>
+        <v>6838895</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12661,11 +12652,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12678,22 +12664,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129738145</v>
+        <v>129739290</v>
       </c>
       <c r="B119" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12701,34 +12687,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407194</v>
+        <v>407657</v>
       </c>
       <c r="R119" t="n">
-        <v>6838873</v>
+        <v>6839033</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12763,34 +12752,40 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738192</v>
+        <v>129738282</v>
       </c>
       <c r="B120" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12798,21 +12793,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12822,10 +12817,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407464</v>
+        <v>407588</v>
       </c>
       <c r="R120" t="n">
-        <v>6839157</v>
+        <v>6838831</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12858,6 +12853,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12884,10 +12884,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129739224</v>
+        <v>129738192</v>
       </c>
       <c r="B121" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12895,21 +12895,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12919,10 +12919,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407121</v>
+        <v>407464</v>
       </c>
       <c r="R121" t="n">
-        <v>6838895</v>
+        <v>6839157</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12969,22 +12969,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739286</v>
+        <v>129739249</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407570</v>
+        <v>407437</v>
       </c>
       <c r="R122" t="n">
-        <v>6839041</v>
+        <v>6839060</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13078,7 +13078,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129738279</v>
+        <v>129739286</v>
       </c>
       <c r="B123" t="n">
         <v>79081</v>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407617</v>
+        <v>407570</v>
       </c>
       <c r="R123" t="n">
-        <v>6838855</v>
+        <v>6839041</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13163,19 +13163,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129738288</v>
+        <v>129738279</v>
       </c>
       <c r="B124" t="n">
         <v>79081</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407592</v>
+        <v>407617</v>
       </c>
       <c r="R124" t="n">
-        <v>6838822</v>
+        <v>6838855</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13272,10 +13272,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738146</v>
+        <v>129738288</v>
       </c>
       <c r="B125" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407163</v>
+        <v>407592</v>
       </c>
       <c r="R125" t="n">
-        <v>6838891</v>
+        <v>6838822</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,7 +13369,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129739241</v>
+        <v>129738146</v>
       </c>
       <c r="B126" t="n">
         <v>79700</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407524</v>
+        <v>407163</v>
       </c>
       <c r="R126" t="n">
-        <v>6838914</v>
+        <v>6838891</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13454,22 +13454,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739249</v>
+        <v>129739241</v>
       </c>
       <c r="B127" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407437</v>
+        <v>407524</v>
       </c>
       <c r="R127" t="n">
-        <v>6839060</v>
+        <v>6838914</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13563,45 +13563,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129738157</v>
+        <v>129738248</v>
       </c>
       <c r="B128" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407535</v>
+        <v>407481</v>
       </c>
       <c r="R128" t="n">
-        <v>6839193</v>
+        <v>6839152</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13642,6 +13651,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13660,45 +13670,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129739287</v>
+        <v>129738256</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407622</v>
+        <v>407616</v>
       </c>
       <c r="R129" t="n">
-        <v>6839045</v>
+        <v>6838794</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13739,28 +13758,29 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129738281</v>
+        <v>129738157</v>
       </c>
       <c r="B130" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,21 +13788,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13792,10 +13812,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407587</v>
+        <v>407535</v>
       </c>
       <c r="R130" t="n">
-        <v>6838872</v>
+        <v>6839193</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13854,10 +13874,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738177</v>
+        <v>129739287</v>
       </c>
       <c r="B131" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,21 +13885,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13889,10 +13909,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407476</v>
+        <v>407622</v>
       </c>
       <c r="R131" t="n">
-        <v>6838854</v>
+        <v>6839045</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13939,22 +13959,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738156</v>
+        <v>129738281</v>
       </c>
       <c r="B132" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13962,21 +13982,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13986,10 +14006,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407477</v>
+        <v>407587</v>
       </c>
       <c r="R132" t="n">
-        <v>6839132</v>
+        <v>6838872</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14048,7 +14068,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129739230</v>
+        <v>129738177</v>
       </c>
       <c r="B133" t="n">
         <v>79700</v>
@@ -14083,10 +14103,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407404</v>
+        <v>407476</v>
       </c>
       <c r="R133" t="n">
-        <v>6839005</v>
+        <v>6838854</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14133,19 +14153,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738151</v>
+        <v>129738156</v>
       </c>
       <c r="B134" t="n">
         <v>79700</v>
@@ -14180,10 +14200,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407378</v>
+        <v>407477</v>
       </c>
       <c r="R134" t="n">
-        <v>6839143</v>
+        <v>6839132</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14242,7 +14262,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739235</v>
+        <v>129739230</v>
       </c>
       <c r="B135" t="n">
         <v>79700</v>
@@ -14277,10 +14297,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407604</v>
+        <v>407404</v>
       </c>
       <c r="R135" t="n">
-        <v>6839024</v>
+        <v>6839005</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14339,7 +14359,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129739231</v>
+        <v>129738151</v>
       </c>
       <c r="B136" t="n">
         <v>79700</v>
@@ -14374,10 +14394,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407422</v>
+        <v>407378</v>
       </c>
       <c r="R136" t="n">
-        <v>6839006</v>
+        <v>6839143</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14424,66 +14444,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129738248</v>
+        <v>129739235</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407481</v>
+        <v>407604</v>
       </c>
       <c r="R137" t="n">
-        <v>6839152</v>
+        <v>6839024</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14524,73 +14535,63 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129738256</v>
+        <v>129739231</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407616</v>
+        <v>407422</v>
       </c>
       <c r="R138" t="n">
-        <v>6838794</v>
+        <v>6839006</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14631,19 +14632,18 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129739257</v>
+        <v>129738278</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,42 +2490,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407574</v>
+        <v>407601</v>
       </c>
       <c r="R16" t="n">
-        <v>6839050</v>
+        <v>6838838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2572,22 +2564,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129738266</v>
+        <v>129739237</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79703</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,42 +2587,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407598</v>
+        <v>407617</v>
       </c>
       <c r="R17" t="n">
-        <v>6838839</v>
+        <v>6839035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2677,22 +2661,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129739256</v>
+        <v>129738187</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79703</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,42 +2684,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407082</v>
+        <v>407437</v>
       </c>
       <c r="R18" t="n">
-        <v>6838747</v>
+        <v>6838840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2782,22 +2758,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738278</v>
+        <v>129738167</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,21 +2781,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2829,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407601</v>
+        <v>407714</v>
       </c>
       <c r="R19" t="n">
-        <v>6838838</v>
+        <v>6839244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2891,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129739237</v>
+        <v>129738159</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,10 +2902,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407617</v>
+        <v>407516</v>
       </c>
       <c r="R20" t="n">
-        <v>6839035</v>
+        <v>6839209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2976,22 +2952,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738187</v>
+        <v>129739265</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>78842</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,21 +2975,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3023,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407437</v>
+        <v>407615</v>
       </c>
       <c r="R21" t="n">
-        <v>6838840</v>
+        <v>6839034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3073,22 +3049,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738167</v>
+        <v>129739257</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,34 +3072,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407714</v>
+        <v>407574</v>
       </c>
       <c r="R22" t="n">
-        <v>6839244</v>
+        <v>6839050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3170,22 +3154,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129738159</v>
+        <v>129739256</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3193,34 +3177,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407516</v>
+        <v>407082</v>
       </c>
       <c r="R23" t="n">
-        <v>6839209</v>
+        <v>6838747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,22 +3259,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129739265</v>
+        <v>129738266</v>
       </c>
       <c r="B24" t="n">
-        <v>78839</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,34 +3282,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407615</v>
+        <v>407598</v>
       </c>
       <c r="R24" t="n">
-        <v>6839034</v>
+        <v>6838839</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3364,12 +3364,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3486,7 +3486,7 @@
         <v>129739291</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>129738154</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>129739233</v>
       </c>
       <c r="B28" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>129739272</v>
       </c>
       <c r="B29" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>129739266</v>
       </c>
       <c r="B30" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,10 +3968,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129739227</v>
+        <v>129738197</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407211</v>
+        <v>407408</v>
       </c>
       <c r="R31" t="n">
-        <v>6839027</v>
+        <v>6838841</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,22 +4053,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129738155</v>
+        <v>129739248</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407503</v>
+        <v>407440</v>
       </c>
       <c r="R32" t="n">
-        <v>6839131</v>
+        <v>6839027</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,22 +4150,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129738179</v>
+        <v>129739227</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407483</v>
+        <v>407211</v>
       </c>
       <c r="R33" t="n">
-        <v>6838820</v>
+        <v>6839027</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,22 +4247,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129738197</v>
+        <v>129738155</v>
       </c>
       <c r="B34" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407408</v>
+        <v>407503</v>
       </c>
       <c r="R34" t="n">
-        <v>6838841</v>
+        <v>6839131</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129739248</v>
+        <v>129738179</v>
       </c>
       <c r="B35" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,21 +4367,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407440</v>
+        <v>407483</v>
       </c>
       <c r="R35" t="n">
-        <v>6839027</v>
+        <v>6838820</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,66 +4441,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738246</v>
+        <v>129738184</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407154</v>
+        <v>407445</v>
       </c>
       <c r="R36" t="n">
-        <v>6838842</v>
+        <v>6838844</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4541,7 +4532,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4560,54 +4550,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129739270</v>
+        <v>129738149</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407283</v>
+        <v>407199</v>
       </c>
       <c r="R37" t="n">
-        <v>6839055</v>
+        <v>6838976</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4648,19 +4629,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4670,7 +4650,7 @@
         <v>129738158</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4764,10 +4744,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738283</v>
+        <v>129739271</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4775,37 +4755,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407598</v>
+        <v>407647</v>
       </c>
       <c r="R39" t="n">
-        <v>6838839</v>
+        <v>6838874</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4840,40 +4817,34 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129739271</v>
+        <v>129738287</v>
       </c>
       <c r="B40" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,21 +4852,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4905,10 +4876,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407647</v>
+        <v>407591</v>
       </c>
       <c r="R40" t="n">
-        <v>6838874</v>
+        <v>6838814</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4955,22 +4926,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738184</v>
+        <v>129738283</v>
       </c>
       <c r="B41" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4978,34 +4949,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407445</v>
+        <v>407598</v>
       </c>
       <c r="R41" t="n">
-        <v>6838844</v>
+        <v>6838839</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5040,12 +5014,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5064,45 +5044,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129738149</v>
+        <v>129738246</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>407199</v>
+        <v>407154</v>
       </c>
       <c r="R42" t="n">
-        <v>6838976</v>
+        <v>6838842</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5143,6 +5132,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5161,45 +5151,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129738287</v>
+        <v>129739270</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>407591</v>
+        <v>407283</v>
       </c>
       <c r="R43" t="n">
-        <v>6838814</v>
+        <v>6839055</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5240,63 +5239,73 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129739240</v>
+        <v>129738247</v>
       </c>
       <c r="B44" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407581</v>
+        <v>407158</v>
       </c>
       <c r="R44" t="n">
-        <v>6838885</v>
+        <v>6838902</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5337,28 +5346,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738186</v>
+        <v>129738292</v>
       </c>
       <c r="B45" t="n">
-        <v>79700</v>
+        <v>78750</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5376,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,10 +5400,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407479</v>
+        <v>407528</v>
       </c>
       <c r="R45" t="n">
-        <v>6838810</v>
+        <v>6839142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5452,10 +5462,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738290</v>
+        <v>129738204</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5463,34 +5473,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407575</v>
+        <v>407170</v>
       </c>
       <c r="R46" t="n">
-        <v>6838839</v>
+        <v>6838942</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5549,10 +5567,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738204</v>
+        <v>129739250</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>79674</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,31 +5578,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5592,10 +5605,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407170</v>
+        <v>407493</v>
       </c>
       <c r="R47" t="n">
-        <v>6838942</v>
+        <v>6839112</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5636,72 +5649,64 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738247</v>
+        <v>129738290</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407158</v>
+        <v>407575</v>
       </c>
       <c r="R48" t="n">
-        <v>6838902</v>
+        <v>6838839</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5742,7 +5747,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5761,10 +5765,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129739250</v>
+        <v>129739240</v>
       </c>
       <c r="B49" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,37 +5776,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407493</v>
+        <v>407581</v>
       </c>
       <c r="R49" t="n">
-        <v>6839112</v>
+        <v>6838885</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5843,7 +5844,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5862,10 +5862,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129738292</v>
+        <v>129738186</v>
       </c>
       <c r="B50" t="n">
-        <v>78747</v>
+        <v>79703</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,21 +5873,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5897,10 +5897,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407528</v>
+        <v>407479</v>
       </c>
       <c r="R50" t="n">
-        <v>6839142</v>
+        <v>6838810</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5959,10 +5959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129738196</v>
+        <v>129738152</v>
       </c>
       <c r="B51" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5970,21 +5970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407436</v>
+        <v>407440</v>
       </c>
       <c r="R51" t="n">
-        <v>6838838</v>
+        <v>6839113</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,10 +6056,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129738152</v>
+        <v>129739234</v>
       </c>
       <c r="B52" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407440</v>
+        <v>407466</v>
       </c>
       <c r="R52" t="n">
-        <v>6839113</v>
+        <v>6839082</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6141,22 +6141,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129739234</v>
+        <v>129738196</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407466</v>
+        <v>407436</v>
       </c>
       <c r="R53" t="n">
-        <v>6839082</v>
+        <v>6838838</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6238,22 +6238,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738198</v>
+        <v>129738160</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79703</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,42 +6261,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407575</v>
+        <v>407512</v>
       </c>
       <c r="R54" t="n">
-        <v>6838839</v>
+        <v>6839214</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6355,10 +6347,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738160</v>
+        <v>129738168</v>
       </c>
       <c r="B55" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6390,10 +6382,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407512</v>
+        <v>407717</v>
       </c>
       <c r="R55" t="n">
-        <v>6839214</v>
+        <v>6839236</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6452,10 +6444,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738291</v>
+        <v>129739229</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6463,21 +6455,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6487,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407574</v>
+        <v>407296</v>
       </c>
       <c r="R56" t="n">
-        <v>6838848</v>
+        <v>6838974</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6537,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738168</v>
+        <v>129738291</v>
       </c>
       <c r="B57" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6560,21 +6552,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6584,10 +6576,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407717</v>
+        <v>407574</v>
       </c>
       <c r="R57" t="n">
-        <v>6839236</v>
+        <v>6838848</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6646,10 +6638,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129739229</v>
+        <v>129738198</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6657,34 +6649,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407296</v>
+        <v>407575</v>
       </c>
       <c r="R58" t="n">
-        <v>6838974</v>
+        <v>6838839</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6731,12 +6731,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6850,45 +6850,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129739232</v>
+        <v>129738243</v>
       </c>
       <c r="B60" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407441</v>
+        <v>407117</v>
       </c>
       <c r="R60" t="n">
-        <v>6839017</v>
+        <v>6838831</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6929,28 +6938,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129739244</v>
+        <v>129738289</v>
       </c>
       <c r="B61" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6958,21 +6968,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6982,10 +6992,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407448</v>
+        <v>407581</v>
       </c>
       <c r="R61" t="n">
-        <v>6838869</v>
+        <v>6838815</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7032,22 +7042,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129738289</v>
+        <v>129738277</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7079,10 +7089,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407581</v>
+        <v>407593</v>
       </c>
       <c r="R62" t="n">
-        <v>6838815</v>
+        <v>6838795</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7141,10 +7151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129738277</v>
+        <v>129739232</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7152,21 +7162,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7176,10 +7186,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407593</v>
+        <v>407441</v>
       </c>
       <c r="R63" t="n">
-        <v>6838795</v>
+        <v>6839017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7226,22 +7236,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129739228</v>
+        <v>129739244</v>
       </c>
       <c r="B64" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7273,10 +7283,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407244</v>
+        <v>407448</v>
       </c>
       <c r="R64" t="n">
-        <v>6839107</v>
+        <v>6838869</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7335,10 +7345,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129738189</v>
+        <v>129739228</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7370,10 +7380,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407407</v>
+        <v>407244</v>
       </c>
       <c r="R65" t="n">
-        <v>6838839</v>
+        <v>6839107</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7420,66 +7430,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129738243</v>
+        <v>129738189</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>407117</v>
+        <v>407407</v>
       </c>
       <c r="R66" t="n">
-        <v>6838831</v>
+        <v>6838839</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7520,7 +7521,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>129738199</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7644,53 +7644,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738257</v>
+        <v>129738169</v>
       </c>
       <c r="B68" t="n">
-        <v>58106</v>
+        <v>79703</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407464</v>
+        <v>407672</v>
       </c>
       <c r="R68" t="n">
-        <v>6839159</v>
+        <v>6838825</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7749,10 +7741,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739264</v>
+        <v>129739245</v>
       </c>
       <c r="B69" t="n">
-        <v>78839</v>
+        <v>79703</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7760,21 +7752,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7784,10 +7776,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407129</v>
+        <v>407443</v>
       </c>
       <c r="R69" t="n">
-        <v>6838913</v>
+        <v>6838872</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7846,10 +7838,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129738193</v>
+        <v>129739225</v>
       </c>
       <c r="B70" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7857,21 +7849,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7881,10 +7873,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407714</v>
+        <v>407184</v>
       </c>
       <c r="R70" t="n">
-        <v>6839244</v>
+        <v>6839011</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7931,12 +7923,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7946,7 +7938,7 @@
         <v>129739292</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8044,45 +8036,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129738169</v>
+        <v>129738257</v>
       </c>
       <c r="B72" t="n">
-        <v>79700</v>
+        <v>58108</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407672</v>
+        <v>407464</v>
       </c>
       <c r="R72" t="n">
-        <v>6838825</v>
+        <v>6839159</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8141,10 +8141,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129739245</v>
+        <v>129739264</v>
       </c>
       <c r="B73" t="n">
-        <v>79700</v>
+        <v>78842</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8152,21 +8152,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407443</v>
+        <v>407129</v>
       </c>
       <c r="R73" t="n">
-        <v>6838872</v>
+        <v>6838913</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129739225</v>
+        <v>129738193</v>
       </c>
       <c r="B74" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8249,21 +8249,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407184</v>
+        <v>407714</v>
       </c>
       <c r="R74" t="n">
-        <v>6839011</v>
+        <v>6839244</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8323,12 +8323,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8338,7 +8338,7 @@
         <v>129738275</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>129738285</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>129738147</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>129738176</v>
       </c>
       <c r="B78" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>129738171</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>129738181</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,54 +8917,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738244</v>
+        <v>129738194</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407231</v>
+        <v>407549</v>
       </c>
       <c r="R81" t="n">
-        <v>6838827</v>
+        <v>6838809</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9005,7 +8996,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9024,45 +9014,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B82" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R82" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,6 +9102,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129739259</v>
+        <v>129738174</v>
       </c>
       <c r="B83" t="n">
-        <v>57896</v>
+        <v>79703</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9132,42 +9132,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407549</v>
+        <v>407572</v>
       </c>
       <c r="R83" t="n">
-        <v>6839053</v>
+        <v>6838852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9214,22 +9206,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738174</v>
+        <v>129738143</v>
       </c>
       <c r="B84" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9261,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407572</v>
+        <v>407137</v>
       </c>
       <c r="R84" t="n">
-        <v>6838852</v>
+        <v>6838823</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9323,10 +9315,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738143</v>
+        <v>129738165</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9358,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407137</v>
+        <v>407691</v>
       </c>
       <c r="R85" t="n">
-        <v>6838823</v>
+        <v>6839279</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9420,10 +9412,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129738165</v>
+        <v>129739238</v>
       </c>
       <c r="B86" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9455,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407691</v>
+        <v>407627</v>
       </c>
       <c r="R86" t="n">
-        <v>6839279</v>
+        <v>6839039</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9505,22 +9497,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129739238</v>
+        <v>129738148</v>
       </c>
       <c r="B87" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9552,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407627</v>
+        <v>407233</v>
       </c>
       <c r="R87" t="n">
-        <v>6839039</v>
+        <v>6838964</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9602,22 +9594,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129738148</v>
+        <v>129739259</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>57895</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9625,34 +9617,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407233</v>
+        <v>407549</v>
       </c>
       <c r="R88" t="n">
-        <v>6838964</v>
+        <v>6839053</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,12 +9699,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9714,7 +9714,7 @@
         <v>129739267</v>
       </c>
       <c r="B89" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9808,45 +9808,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129739246</v>
+        <v>129738227</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>5480</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407427</v>
+        <v>407545</v>
       </c>
       <c r="R90" t="n">
-        <v>6838886</v>
+        <v>6839241</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9887,28 +9896,29 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739239</v>
+        <v>129739255</v>
       </c>
       <c r="B91" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9916,21 +9926,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9940,10 +9950,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407614</v>
+        <v>407411</v>
       </c>
       <c r="R91" t="n">
-        <v>6838900</v>
+        <v>6838819</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10002,10 +10012,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129738170</v>
+        <v>129739258</v>
       </c>
       <c r="B92" t="n">
-        <v>79700</v>
+        <v>57737</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10013,34 +10023,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407660</v>
+        <v>407616</v>
       </c>
       <c r="R92" t="n">
-        <v>6838791</v>
+        <v>6838890</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10087,22 +10105,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129738188</v>
+        <v>129739246</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10134,10 +10152,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407408</v>
+        <v>407427</v>
       </c>
       <c r="R93" t="n">
-        <v>6838841</v>
+        <v>6838886</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10184,22 +10202,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129739255</v>
+        <v>129739239</v>
       </c>
       <c r="B94" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10207,21 +10225,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10231,10 +10249,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407411</v>
+        <v>407614</v>
       </c>
       <c r="R94" t="n">
-        <v>6838819</v>
+        <v>6838900</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10293,10 +10311,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129739258</v>
+        <v>129738170</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>79703</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10304,42 +10322,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407616</v>
+        <v>407660</v>
       </c>
       <c r="R95" t="n">
-        <v>6838890</v>
+        <v>6838791</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10386,66 +10396,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129738227</v>
+        <v>129738188</v>
       </c>
       <c r="B96" t="n">
-        <v>5480</v>
+        <v>79703</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407545</v>
+        <v>407408</v>
       </c>
       <c r="R96" t="n">
-        <v>6839241</v>
+        <v>6838841</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10486,7 +10487,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129738144</v>
+        <v>129739289</v>
       </c>
       <c r="B97" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10516,21 +10516,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407223</v>
+        <v>407649</v>
       </c>
       <c r="R97" t="n">
-        <v>6838821</v>
+        <v>6839041</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10590,22 +10590,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129738185</v>
+        <v>129738144</v>
       </c>
       <c r="B98" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407439</v>
+        <v>407223</v>
       </c>
       <c r="R98" t="n">
-        <v>6838837</v>
+        <v>6838821</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129738172</v>
+        <v>129738185</v>
       </c>
       <c r="B99" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407585</v>
+        <v>407439</v>
       </c>
       <c r="R99" t="n">
-        <v>6838872</v>
+        <v>6838837</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10796,10 +10796,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129739242</v>
+        <v>129738172</v>
       </c>
       <c r="B100" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407515</v>
+        <v>407585</v>
       </c>
       <c r="R100" t="n">
-        <v>6838875</v>
+        <v>6838872</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10881,22 +10881,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129739289</v>
+        <v>129739242</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10904,21 +10904,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407649</v>
+        <v>407515</v>
       </c>
       <c r="R101" t="n">
-        <v>6839041</v>
+        <v>6838875</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10993,7 +10993,7 @@
         <v>129739252</v>
       </c>
       <c r="B102" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>129738191</v>
       </c>
       <c r="B103" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>129739251</v>
       </c>
       <c r="B104" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>129739273</v>
       </c>
       <c r="B106" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>129738173</v>
       </c>
       <c r="B107" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>129738182</v>
       </c>
       <c r="B108" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11679,10 +11679,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738180</v>
+        <v>129738276</v>
       </c>
       <c r="B109" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11690,21 +11690,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407480</v>
+        <v>407607</v>
       </c>
       <c r="R109" t="n">
-        <v>6838840</v>
+        <v>6838798</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11776,10 +11776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738276</v>
+        <v>129738180</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407607</v>
+        <v>407480</v>
       </c>
       <c r="R110" t="n">
-        <v>6838798</v>
+        <v>6838840</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11876,7 +11876,7 @@
         <v>129738190</v>
       </c>
       <c r="B111" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>129738175</v>
       </c>
       <c r="B112" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>129738268</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129739243</v>
+        <v>129739290</v>
       </c>
       <c r="B115" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,34 +12290,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407451</v>
+        <v>407657</v>
       </c>
       <c r="R115" t="n">
-        <v>6838866</v>
+        <v>6839033</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12352,12 +12355,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12376,10 +12385,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129738145</v>
+        <v>129738280</v>
       </c>
       <c r="B116" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12387,34 +12396,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407194</v>
+        <v>407623</v>
       </c>
       <c r="R116" t="n">
-        <v>6838873</v>
+        <v>6838894</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12449,12 +12461,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12473,10 +12491,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129738280</v>
+        <v>129738282</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12502,19 +12520,16 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407623</v>
+        <v>407588</v>
       </c>
       <c r="R117" t="n">
-        <v>6838894</v>
+        <v>6838831</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12560,7 +12575,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12579,10 +12593,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129739224</v>
+        <v>129739243</v>
       </c>
       <c r="B118" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12614,10 +12628,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407121</v>
+        <v>407451</v>
       </c>
       <c r="R118" t="n">
-        <v>6838895</v>
+        <v>6838866</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12676,10 +12690,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129739290</v>
+        <v>129739224</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12687,37 +12701,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407657</v>
+        <v>407121</v>
       </c>
       <c r="R119" t="n">
-        <v>6839033</v>
+        <v>6838895</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12752,18 +12763,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12782,10 +12787,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738282</v>
+        <v>129738145</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12793,21 +12798,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12817,10 +12822,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407588</v>
+        <v>407194</v>
       </c>
       <c r="R120" t="n">
-        <v>6838831</v>
+        <v>6838873</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12853,11 +12858,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12887,7 +12887,7 @@
         <v>129738192</v>
       </c>
       <c r="B121" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12981,10 +12981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739249</v>
+        <v>129739286</v>
       </c>
       <c r="B122" t="n">
-        <v>79671</v>
+        <v>79084</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407437</v>
+        <v>407570</v>
       </c>
       <c r="R122" t="n">
-        <v>6839060</v>
+        <v>6839041</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13078,10 +13078,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129739286</v>
+        <v>129739249</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13089,21 +13089,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407570</v>
+        <v>407437</v>
       </c>
       <c r="R123" t="n">
-        <v>6839041</v>
+        <v>6839060</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13178,7 +13178,7 @@
         <v>129738279</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>129738288</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>129738146</v>
       </c>
       <c r="B126" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>129739241</v>
       </c>
       <c r="B127" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13563,54 +13563,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129738248</v>
+        <v>129739287</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407481</v>
+        <v>407622</v>
       </c>
       <c r="R128" t="n">
-        <v>6839152</v>
+        <v>6839045</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13651,73 +13642,63 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738256</v>
+        <v>129738281</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407616</v>
+        <v>407587</v>
       </c>
       <c r="R129" t="n">
-        <v>6838794</v>
+        <v>6838872</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13758,7 +13739,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13780,7 +13760,7 @@
         <v>129738157</v>
       </c>
       <c r="B130" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13874,10 +13854,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129739287</v>
+        <v>129738177</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13885,21 +13865,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13909,10 +13889,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407622</v>
+        <v>407476</v>
       </c>
       <c r="R131" t="n">
-        <v>6839045</v>
+        <v>6838854</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13959,22 +13939,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738281</v>
+        <v>129738156</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13982,21 +13962,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14006,10 +13986,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407587</v>
+        <v>407477</v>
       </c>
       <c r="R132" t="n">
-        <v>6838872</v>
+        <v>6839132</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14068,10 +14048,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738177</v>
+        <v>129739230</v>
       </c>
       <c r="B133" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14103,10 +14083,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407476</v>
+        <v>407404</v>
       </c>
       <c r="R133" t="n">
-        <v>6838854</v>
+        <v>6839005</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14153,22 +14133,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738156</v>
+        <v>129738151</v>
       </c>
       <c r="B134" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14200,10 +14180,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407477</v>
+        <v>407378</v>
       </c>
       <c r="R134" t="n">
-        <v>6839132</v>
+        <v>6839143</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14262,10 +14242,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739230</v>
+        <v>129739235</v>
       </c>
       <c r="B135" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14297,10 +14277,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407404</v>
+        <v>407604</v>
       </c>
       <c r="R135" t="n">
-        <v>6839005</v>
+        <v>6839024</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14359,10 +14339,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129738151</v>
+        <v>129739231</v>
       </c>
       <c r="B136" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14394,10 +14374,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407378</v>
+        <v>407422</v>
       </c>
       <c r="R136" t="n">
-        <v>6839143</v>
+        <v>6839006</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14444,22 +14424,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129739235</v>
+        <v>129739254</v>
       </c>
       <c r="B137" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14467,21 +14447,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14491,10 +14471,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407604</v>
+        <v>407418</v>
       </c>
       <c r="R137" t="n">
-        <v>6839024</v>
+        <v>6838867</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14553,10 +14533,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129739231</v>
+        <v>129738242</v>
       </c>
       <c r="B138" t="n">
-        <v>79700</v>
+        <v>78842</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14564,21 +14544,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14588,10 +14568,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407422</v>
+        <v>407719</v>
       </c>
       <c r="R138" t="n">
-        <v>6839006</v>
+        <v>6839222</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14638,22 +14618,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129738242</v>
+        <v>129739268</v>
       </c>
       <c r="B139" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14679,16 +14659,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407719</v>
+        <v>407573</v>
       </c>
       <c r="R139" t="n">
-        <v>6839222</v>
+        <v>6838884</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14729,63 +14712,73 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129739254</v>
+        <v>129738248</v>
       </c>
       <c r="B140" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407418</v>
+        <v>407481</v>
       </c>
       <c r="R140" t="n">
-        <v>6838867</v>
+        <v>6839152</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14826,55 +14819,62 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129739268</v>
+        <v>129738256</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -14882,10 +14882,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407573</v>
+        <v>407616</v>
       </c>
       <c r="R141" t="n">
-        <v>6838884</v>
+        <v>6838794</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14933,22 +14933,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738150</v>
+        <v>129738286</v>
       </c>
       <c r="B142" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,21 +14956,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407203</v>
+        <v>407586</v>
       </c>
       <c r="R142" t="n">
-        <v>6839015</v>
+        <v>6838820</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15042,10 +15042,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738286</v>
+        <v>129738284</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15077,10 +15077,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407586</v>
+        <v>407595</v>
       </c>
       <c r="R143" t="n">
-        <v>6838820</v>
+        <v>6838836</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15139,10 +15139,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738284</v>
+        <v>129738150</v>
       </c>
       <c r="B144" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15150,21 +15150,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15174,10 +15174,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407595</v>
+        <v>407203</v>
       </c>
       <c r="R144" t="n">
-        <v>6838836</v>
+        <v>6839015</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15236,10 +15236,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129739253</v>
+        <v>129738201</v>
       </c>
       <c r="B145" t="n">
-        <v>79671</v>
+        <v>57895</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15247,26 +15247,31 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15274,10 +15279,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407589</v>
+        <v>407530</v>
       </c>
       <c r="R145" t="n">
-        <v>6838889</v>
+        <v>6839196</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15318,29 +15323,28 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129738195</v>
+        <v>129739253</v>
       </c>
       <c r="B146" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15366,16 +15370,19 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407479</v>
+        <v>407589</v>
       </c>
       <c r="R146" t="n">
-        <v>6838852</v>
+        <v>6838889</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15416,28 +15423,29 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738201</v>
+        <v>129738195</v>
       </c>
       <c r="B147" t="n">
-        <v>57896</v>
+        <v>79674</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15445,42 +15453,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407530</v>
+        <v>407479</v>
       </c>
       <c r="R147" t="n">
-        <v>6839196</v>
+        <v>6838852</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15542,7 +15542,7 @@
         <v>129738164</v>
       </c>
       <c r="B148" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>129738153</v>
       </c>
       <c r="B149" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>129738166</v>
       </c>
       <c r="B150" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738274</v>
+        <v>129739288</v>
       </c>
       <c r="B151" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407522</v>
+        <v>407625</v>
       </c>
       <c r="R151" t="n">
-        <v>6839200</v>
+        <v>6839051</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15915,22 +15915,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129739288</v>
+        <v>129738274</v>
       </c>
       <c r="B152" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407625</v>
+        <v>407522</v>
       </c>
       <c r="R152" t="n">
-        <v>6839051</v>
+        <v>6839200</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16012,12 +16012,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
         <v>129739247</v>
       </c>
       <c r="B153" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2964,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129739265</v>
+        <v>129739257</v>
       </c>
       <c r="B21" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,34 +2975,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407615</v>
+        <v>407574</v>
       </c>
       <c r="R21" t="n">
-        <v>6839034</v>
+        <v>6839050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3061,7 +3069,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129739257</v>
+        <v>129739256</v>
       </c>
       <c r="B22" t="n">
         <v>57737</v>
@@ -3094,7 +3102,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3104,10 +3112,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407574</v>
+        <v>407082</v>
       </c>
       <c r="R22" t="n">
-        <v>6839050</v>
+        <v>6838747</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3166,7 +3174,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739256</v>
+        <v>129738266</v>
       </c>
       <c r="B23" t="n">
         <v>57737</v>
@@ -3199,7 +3207,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3209,10 +3217,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407082</v>
+        <v>407598</v>
       </c>
       <c r="R23" t="n">
-        <v>6838747</v>
+        <v>6838839</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3259,52 +3267,53 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738266</v>
+        <v>129738245</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3314,10 +3323,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407598</v>
+        <v>407233</v>
       </c>
       <c r="R24" t="n">
-        <v>6838839</v>
+        <v>6838838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3358,6 +3367,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3376,54 +3386,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129738245</v>
+        <v>129739265</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>78842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407233</v>
+        <v>407615</v>
       </c>
       <c r="R25" t="n">
-        <v>6838838</v>
+        <v>6839034</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3464,19 +3465,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129739271</v>
+        <v>129738287</v>
       </c>
       <c r="B39" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407647</v>
+        <v>407591</v>
       </c>
       <c r="R39" t="n">
-        <v>6838874</v>
+        <v>6838814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4829,19 +4829,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738287</v>
+        <v>129738283</v>
       </c>
       <c r="B40" t="n">
         <v>79084</v>
@@ -4870,16 +4870,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407591</v>
+        <v>407598</v>
       </c>
       <c r="R40" t="n">
-        <v>6838814</v>
+        <v>6838839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4914,12 +4917,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4938,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738283</v>
+        <v>129739271</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4949,37 +4958,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407598</v>
+        <v>407647</v>
       </c>
       <c r="R41" t="n">
-        <v>6838839</v>
+        <v>6838874</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5014,30 +5020,24 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738204</v>
+        <v>129739240</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5473,42 +5473,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407170</v>
+        <v>407581</v>
       </c>
       <c r="R46" t="n">
-        <v>6838942</v>
+        <v>6838885</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5555,22 +5547,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129739250</v>
+        <v>129738186</v>
       </c>
       <c r="B47" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5578,37 +5570,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407493</v>
+        <v>407479</v>
       </c>
       <c r="R47" t="n">
-        <v>6839112</v>
+        <v>6838810</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5649,19 +5638,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5765,10 +5753,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129739240</v>
+        <v>129738204</v>
       </c>
       <c r="B49" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5776,34 +5764,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407581</v>
+        <v>407170</v>
       </c>
       <c r="R49" t="n">
-        <v>6838885</v>
+        <v>6838942</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5850,22 +5846,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129738186</v>
+        <v>129739250</v>
       </c>
       <c r="B50" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,34 +5869,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407479</v>
+        <v>407493</v>
       </c>
       <c r="R50" t="n">
-        <v>6838810</v>
+        <v>6839112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,18 +5940,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6347,10 +6347,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738168</v>
+        <v>129738291</v>
       </c>
       <c r="B55" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6358,21 +6358,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407717</v>
+        <v>407574</v>
       </c>
       <c r="R55" t="n">
-        <v>6839236</v>
+        <v>6838848</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129739229</v>
+        <v>129738168</v>
       </c>
       <c r="B56" t="n">
         <v>79703</v>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407296</v>
+        <v>407717</v>
       </c>
       <c r="R56" t="n">
-        <v>6838974</v>
+        <v>6839236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6529,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738291</v>
+        <v>129739229</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,21 +6552,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407574</v>
+        <v>407296</v>
       </c>
       <c r="R57" t="n">
-        <v>6838848</v>
+        <v>6838974</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,52 +6626,53 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738198</v>
+        <v>129738255</v>
       </c>
       <c r="B58" t="n">
-        <v>57737</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6681,10 +6682,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407575</v>
+        <v>407645</v>
       </c>
       <c r="R58" t="n">
-        <v>6838839</v>
+        <v>6838797</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6725,6 +6726,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6743,41 +6745,40 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738255</v>
+        <v>129738198</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6787,10 +6788,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407645</v>
+        <v>407575</v>
       </c>
       <c r="R59" t="n">
-        <v>6838797</v>
+        <v>6838839</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6831,7 +6832,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6957,7 +6957,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129738289</v>
+        <v>129738277</v>
       </c>
       <c r="B61" t="n">
         <v>79084</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407581</v>
+        <v>407593</v>
       </c>
       <c r="R61" t="n">
-        <v>6838815</v>
+        <v>6838795</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7054,10 +7054,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129738277</v>
+        <v>129739232</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7065,21 +7065,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407593</v>
+        <v>407441</v>
       </c>
       <c r="R62" t="n">
-        <v>6838795</v>
+        <v>6839017</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7139,19 +7139,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129739232</v>
+        <v>129739244</v>
       </c>
       <c r="B63" t="n">
         <v>79703</v>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407441</v>
+        <v>407448</v>
       </c>
       <c r="R63" t="n">
-        <v>6839017</v>
+        <v>6838869</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7248,10 +7248,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129739244</v>
+        <v>129738289</v>
       </c>
       <c r="B64" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7259,21 +7259,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7283,10 +7283,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407448</v>
+        <v>407581</v>
       </c>
       <c r="R64" t="n">
-        <v>6838869</v>
+        <v>6838815</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7333,12 +7333,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7539,27 +7539,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129738199</v>
+        <v>129738257</v>
       </c>
       <c r="B67" t="n">
-        <v>57737</v>
+        <v>58108</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7572,7 +7572,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407576</v>
+        <v>407464</v>
       </c>
       <c r="R67" t="n">
-        <v>6838847</v>
+        <v>6839159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7644,10 +7644,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738169</v>
+        <v>129738193</v>
       </c>
       <c r="B68" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7655,21 +7655,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407672</v>
+        <v>407714</v>
       </c>
       <c r="R68" t="n">
-        <v>6838825</v>
+        <v>6839244</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7741,10 +7741,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739245</v>
+        <v>129739264</v>
       </c>
       <c r="B69" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,21 +7752,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407443</v>
+        <v>407129</v>
       </c>
       <c r="R69" t="n">
-        <v>6838872</v>
+        <v>6838913</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7838,10 +7838,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129739225</v>
+        <v>129739292</v>
       </c>
       <c r="B70" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,34 +7849,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407184</v>
+        <v>407632</v>
       </c>
       <c r="R70" t="n">
-        <v>6839011</v>
+        <v>6838901</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7917,6 +7920,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7935,10 +7939,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129739292</v>
+        <v>129738169</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,37 +7950,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407632</v>
+        <v>407672</v>
       </c>
       <c r="R71" t="n">
-        <v>6838901</v>
+        <v>6838825</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8017,72 +8018,63 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129738257</v>
+        <v>129739245</v>
       </c>
       <c r="B72" t="n">
-        <v>58108</v>
+        <v>79703</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407464</v>
+        <v>407443</v>
       </c>
       <c r="R72" t="n">
-        <v>6839159</v>
+        <v>6838872</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8129,22 +8121,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129739264</v>
+        <v>129739225</v>
       </c>
       <c r="B73" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8152,21 +8144,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8176,10 +8168,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407129</v>
+        <v>407184</v>
       </c>
       <c r="R73" t="n">
-        <v>6838913</v>
+        <v>6839011</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8238,10 +8230,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129738193</v>
+        <v>129738199</v>
       </c>
       <c r="B74" t="n">
-        <v>79674</v>
+        <v>57737</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8249,34 +8241,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407714</v>
+        <v>407576</v>
       </c>
       <c r="R74" t="n">
-        <v>6839244</v>
+        <v>6838847</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8335,45 +8335,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738275</v>
+        <v>129738244</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407608</v>
+        <v>407231</v>
       </c>
       <c r="R75" t="n">
-        <v>6839252</v>
+        <v>6838827</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8414,6 +8423,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8432,7 +8442,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738285</v>
+        <v>129738275</v>
       </c>
       <c r="B76" t="n">
         <v>79084</v>
@@ -8467,10 +8477,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407587</v>
+        <v>407608</v>
       </c>
       <c r="R76" t="n">
-        <v>6838806</v>
+        <v>6839252</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,10 +8539,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738147</v>
+        <v>129738285</v>
       </c>
       <c r="B77" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8540,21 +8550,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8564,10 +8574,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407190</v>
+        <v>407587</v>
       </c>
       <c r="R77" t="n">
-        <v>6838950</v>
+        <v>6838806</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,7 +8636,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738176</v>
+        <v>129738147</v>
       </c>
       <c r="B78" t="n">
         <v>79703</v>
@@ -8661,10 +8671,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407519</v>
+        <v>407190</v>
       </c>
       <c r="R78" t="n">
-        <v>6838831</v>
+        <v>6838950</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,7 +8733,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738171</v>
+        <v>129738176</v>
       </c>
       <c r="B79" t="n">
         <v>79703</v>
@@ -8758,10 +8768,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407620</v>
+        <v>407519</v>
       </c>
       <c r="R79" t="n">
-        <v>6838898</v>
+        <v>6838831</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,7 +8830,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738181</v>
+        <v>129738171</v>
       </c>
       <c r="B80" t="n">
         <v>79703</v>
@@ -8855,10 +8865,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407467</v>
+        <v>407620</v>
       </c>
       <c r="R80" t="n">
-        <v>6838834</v>
+        <v>6838898</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,10 +8927,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738194</v>
+        <v>129738181</v>
       </c>
       <c r="B81" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8928,21 +8938,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8952,10 +8962,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407549</v>
+        <v>407467</v>
       </c>
       <c r="R81" t="n">
-        <v>6838809</v>
+        <v>6838834</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9014,54 +9024,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738244</v>
+        <v>129738194</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407231</v>
+        <v>407549</v>
       </c>
       <c r="R82" t="n">
-        <v>6838827</v>
+        <v>6838809</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9102,7 +9103,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129738174</v>
+        <v>129739259</v>
       </c>
       <c r="B83" t="n">
-        <v>79703</v>
+        <v>57895</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9132,34 +9132,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407572</v>
+        <v>407549</v>
       </c>
       <c r="R83" t="n">
-        <v>6838852</v>
+        <v>6839053</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9206,19 +9214,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738143</v>
+        <v>129738174</v>
       </c>
       <c r="B84" t="n">
         <v>79703</v>
@@ -9253,10 +9261,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407137</v>
+        <v>407572</v>
       </c>
       <c r="R84" t="n">
-        <v>6838823</v>
+        <v>6838852</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9315,7 +9323,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738165</v>
+        <v>129738143</v>
       </c>
       <c r="B85" t="n">
         <v>79703</v>
@@ -9350,10 +9358,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407691</v>
+        <v>407137</v>
       </c>
       <c r="R85" t="n">
-        <v>6839279</v>
+        <v>6838823</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9412,7 +9420,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129739238</v>
+        <v>129738165</v>
       </c>
       <c r="B86" t="n">
         <v>79703</v>
@@ -9447,10 +9455,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407627</v>
+        <v>407691</v>
       </c>
       <c r="R86" t="n">
-        <v>6839039</v>
+        <v>6839279</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,19 +9505,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129738148</v>
+        <v>129739238</v>
       </c>
       <c r="B87" t="n">
         <v>79703</v>
@@ -9544,10 +9552,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407233</v>
+        <v>407627</v>
       </c>
       <c r="R87" t="n">
-        <v>6838964</v>
+        <v>6839039</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9594,22 +9602,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129739259</v>
+        <v>129738148</v>
       </c>
       <c r="B88" t="n">
-        <v>57895</v>
+        <v>79703</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,42 +9625,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407549</v>
+        <v>407233</v>
       </c>
       <c r="R88" t="n">
-        <v>6839053</v>
+        <v>6838964</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,12 +9699,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9808,54 +9808,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129738227</v>
+        <v>129739246</v>
       </c>
       <c r="B90" t="n">
-        <v>5480</v>
+        <v>79703</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407545</v>
+        <v>407427</v>
       </c>
       <c r="R90" t="n">
-        <v>6839241</v>
+        <v>6838886</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9896,29 +9887,28 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739255</v>
+        <v>129739239</v>
       </c>
       <c r="B91" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9926,21 +9916,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9950,10 +9940,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407411</v>
+        <v>407614</v>
       </c>
       <c r="R91" t="n">
-        <v>6838819</v>
+        <v>6838900</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10012,10 +10002,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129739258</v>
+        <v>129738170</v>
       </c>
       <c r="B92" t="n">
-        <v>57737</v>
+        <v>79703</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10023,42 +10013,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407616</v>
+        <v>407660</v>
       </c>
       <c r="R92" t="n">
-        <v>6838890</v>
+        <v>6838791</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10105,19 +10087,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129739246</v>
+        <v>129738188</v>
       </c>
       <c r="B93" t="n">
         <v>79703</v>
@@ -10152,10 +10134,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407427</v>
+        <v>407408</v>
       </c>
       <c r="R93" t="n">
-        <v>6838886</v>
+        <v>6838841</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10202,22 +10184,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129739239</v>
+        <v>129739255</v>
       </c>
       <c r="B94" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10225,21 +10207,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10249,10 +10231,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407614</v>
+        <v>407411</v>
       </c>
       <c r="R94" t="n">
-        <v>6838900</v>
+        <v>6838819</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10311,10 +10293,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129738170</v>
+        <v>129739258</v>
       </c>
       <c r="B95" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10322,34 +10304,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407660</v>
+        <v>407616</v>
       </c>
       <c r="R95" t="n">
-        <v>6838791</v>
+        <v>6838890</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10396,57 +10386,66 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129738188</v>
+        <v>129738227</v>
       </c>
       <c r="B96" t="n">
-        <v>79703</v>
+        <v>5480</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407408</v>
+        <v>407545</v>
       </c>
       <c r="R96" t="n">
-        <v>6838841</v>
+        <v>6839241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10487,6 +10486,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11087,7 +11087,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129738191</v>
+        <v>129739251</v>
       </c>
       <c r="B103" t="n">
         <v>79674</v>
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407474</v>
+        <v>407563</v>
       </c>
       <c r="R103" t="n">
-        <v>6839108</v>
+        <v>6839056</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11172,19 +11172,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129739251</v>
+        <v>129738191</v>
       </c>
       <c r="B104" t="n">
         <v>79674</v>
@@ -11219,10 +11219,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407563</v>
+        <v>407474</v>
       </c>
       <c r="R104" t="n">
-        <v>6839056</v>
+        <v>6839108</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11269,12 +11269,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11679,10 +11679,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738276</v>
+        <v>129738180</v>
       </c>
       <c r="B109" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11690,21 +11690,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407607</v>
+        <v>407480</v>
       </c>
       <c r="R109" t="n">
-        <v>6838798</v>
+        <v>6838840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11776,10 +11776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738180</v>
+        <v>129738276</v>
       </c>
       <c r="B110" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407480</v>
+        <v>407607</v>
       </c>
       <c r="R110" t="n">
-        <v>6838840</v>
+        <v>6838798</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129739290</v>
+        <v>129739243</v>
       </c>
       <c r="B115" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,37 +12290,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407657</v>
+        <v>407451</v>
       </c>
       <c r="R115" t="n">
-        <v>6839033</v>
+        <v>6838866</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12355,18 +12352,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12491,10 +12482,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129738282</v>
+        <v>129739224</v>
       </c>
       <c r="B117" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12502,21 +12493,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12526,10 +12517,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407588</v>
+        <v>407121</v>
       </c>
       <c r="R117" t="n">
-        <v>6838831</v>
+        <v>6838895</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12564,11 +12555,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12581,22 +12567,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129739243</v>
+        <v>129738282</v>
       </c>
       <c r="B118" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12604,21 +12590,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12628,10 +12614,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407451</v>
+        <v>407588</v>
       </c>
       <c r="R118" t="n">
-        <v>6838866</v>
+        <v>6838831</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12666,6 +12652,11 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12678,19 +12669,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129739224</v>
+        <v>129738145</v>
       </c>
       <c r="B119" t="n">
         <v>79703</v>
@@ -12725,10 +12716,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407121</v>
+        <v>407194</v>
       </c>
       <c r="R119" t="n">
-        <v>6838895</v>
+        <v>6838873</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12775,22 +12766,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738145</v>
+        <v>129739290</v>
       </c>
       <c r="B120" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12798,34 +12789,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407194</v>
+        <v>407657</v>
       </c>
       <c r="R120" t="n">
-        <v>6838873</v>
+        <v>6839033</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12860,24 +12854,30 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13078,10 +13078,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129739249</v>
+        <v>129738279</v>
       </c>
       <c r="B123" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13089,21 +13089,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407437</v>
+        <v>407617</v>
       </c>
       <c r="R123" t="n">
-        <v>6839060</v>
+        <v>6838855</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13163,19 +13163,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129738279</v>
+        <v>129738288</v>
       </c>
       <c r="B124" t="n">
         <v>79084</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407617</v>
+        <v>407592</v>
       </c>
       <c r="R124" t="n">
-        <v>6838855</v>
+        <v>6838822</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13272,10 +13272,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738288</v>
+        <v>129738146</v>
       </c>
       <c r="B125" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407592</v>
+        <v>407163</v>
       </c>
       <c r="R125" t="n">
-        <v>6838822</v>
+        <v>6838891</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,7 +13369,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129738146</v>
+        <v>129739241</v>
       </c>
       <c r="B126" t="n">
         <v>79703</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407163</v>
+        <v>407524</v>
       </c>
       <c r="R126" t="n">
-        <v>6838891</v>
+        <v>6838914</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13454,22 +13454,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739241</v>
+        <v>129739249</v>
       </c>
       <c r="B127" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407524</v>
+        <v>407437</v>
       </c>
       <c r="R127" t="n">
-        <v>6838914</v>
+        <v>6839060</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13563,10 +13563,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129739287</v>
+        <v>129738242</v>
       </c>
       <c r="B128" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13574,21 +13574,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13598,10 +13598,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407622</v>
+        <v>407719</v>
       </c>
       <c r="R128" t="n">
-        <v>6839045</v>
+        <v>6839222</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,22 +13648,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738281</v>
+        <v>129739254</v>
       </c>
       <c r="B129" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,21 +13671,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13695,10 +13695,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407587</v>
+        <v>407418</v>
       </c>
       <c r="R129" t="n">
-        <v>6838872</v>
+        <v>6838867</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13745,22 +13745,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129738157</v>
+        <v>129739268</v>
       </c>
       <c r="B130" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,34 +13768,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407535</v>
+        <v>407573</v>
       </c>
       <c r="R130" t="n">
-        <v>6839193</v>
+        <v>6838884</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13836,63 +13839,73 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738177</v>
+        <v>129738248</v>
       </c>
       <c r="B131" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407476</v>
+        <v>407481</v>
       </c>
       <c r="R131" t="n">
-        <v>6838854</v>
+        <v>6839152</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13933,6 +13946,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13951,45 +13965,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738156</v>
+        <v>129738256</v>
       </c>
       <c r="B132" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407477</v>
+        <v>407616</v>
       </c>
       <c r="R132" t="n">
-        <v>6839132</v>
+        <v>6838794</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14030,6 +14053,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14048,10 +14072,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129739230</v>
+        <v>129738281</v>
       </c>
       <c r="B133" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14059,21 +14083,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14083,10 +14107,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407404</v>
+        <v>407587</v>
       </c>
       <c r="R133" t="n">
-        <v>6839005</v>
+        <v>6838872</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14133,19 +14157,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738151</v>
+        <v>129738157</v>
       </c>
       <c r="B134" t="n">
         <v>79703</v>
@@ -14180,10 +14204,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407378</v>
+        <v>407535</v>
       </c>
       <c r="R134" t="n">
-        <v>6839143</v>
+        <v>6839193</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14242,10 +14266,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739235</v>
+        <v>129739287</v>
       </c>
       <c r="B135" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14253,21 +14277,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14277,10 +14301,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407604</v>
+        <v>407622</v>
       </c>
       <c r="R135" t="n">
-        <v>6839024</v>
+        <v>6839045</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14339,7 +14363,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129739231</v>
+        <v>129738177</v>
       </c>
       <c r="B136" t="n">
         <v>79703</v>
@@ -14374,10 +14398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407422</v>
+        <v>407476</v>
       </c>
       <c r="R136" t="n">
-        <v>6839006</v>
+        <v>6838854</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14424,22 +14448,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129739254</v>
+        <v>129738156</v>
       </c>
       <c r="B137" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14447,21 +14471,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14471,10 +14495,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407418</v>
+        <v>407477</v>
       </c>
       <c r="R137" t="n">
-        <v>6838867</v>
+        <v>6839132</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14521,22 +14545,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129738242</v>
+        <v>129739230</v>
       </c>
       <c r="B138" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14544,21 +14568,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14568,10 +14592,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407719</v>
+        <v>407404</v>
       </c>
       <c r="R138" t="n">
-        <v>6839222</v>
+        <v>6839005</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14618,22 +14642,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129739268</v>
+        <v>129738151</v>
       </c>
       <c r="B139" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14641,37 +14665,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407573</v>
+        <v>407378</v>
       </c>
       <c r="R139" t="n">
-        <v>6838884</v>
+        <v>6839143</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14712,73 +14733,63 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129738248</v>
+        <v>129739235</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407481</v>
+        <v>407604</v>
       </c>
       <c r="R140" t="n">
-        <v>6839152</v>
+        <v>6839024</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14819,73 +14830,63 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129738256</v>
+        <v>129739231</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407616</v>
+        <v>407422</v>
       </c>
       <c r="R141" t="n">
-        <v>6838794</v>
+        <v>6839006</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14926,29 +14927,28 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738286</v>
+        <v>129738201</v>
       </c>
       <c r="B142" t="n">
-        <v>79084</v>
+        <v>57895</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,34 +14956,42 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407586</v>
+        <v>407530</v>
       </c>
       <c r="R142" t="n">
-        <v>6838820</v>
+        <v>6839196</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15042,10 +15050,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738284</v>
+        <v>129738150</v>
       </c>
       <c r="B143" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15053,21 +15061,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15077,10 +15085,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407595</v>
+        <v>407203</v>
       </c>
       <c r="R143" t="n">
-        <v>6838836</v>
+        <v>6839015</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15139,10 +15147,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738150</v>
+        <v>129738286</v>
       </c>
       <c r="B144" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15150,21 +15158,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15174,10 +15182,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407203</v>
+        <v>407586</v>
       </c>
       <c r="R144" t="n">
-        <v>6839015</v>
+        <v>6838820</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15236,10 +15244,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738201</v>
+        <v>129738284</v>
       </c>
       <c r="B145" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15247,42 +15255,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407530</v>
+        <v>407595</v>
       </c>
       <c r="R145" t="n">
-        <v>6839196</v>
+        <v>6838836</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15830,7 +15830,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129739288</v>
+        <v>129738274</v>
       </c>
       <c r="B151" t="n">
         <v>79084</v>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407625</v>
+        <v>407522</v>
       </c>
       <c r="R151" t="n">
-        <v>6839051</v>
+        <v>6839200</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15915,19 +15915,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129738274</v>
+        <v>129739288</v>
       </c>
       <c r="B152" t="n">
         <v>79084</v>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407522</v>
+        <v>407625</v>
       </c>
       <c r="R152" t="n">
-        <v>6839200</v>
+        <v>6839051</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16012,12 +16012,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -3968,10 +3968,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129738197</v>
+        <v>129739227</v>
       </c>
       <c r="B31" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407408</v>
+        <v>407211</v>
       </c>
       <c r="R31" t="n">
-        <v>6838841</v>
+        <v>6839027</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,22 +4053,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129739248</v>
+        <v>129738155</v>
       </c>
       <c r="B32" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407440</v>
+        <v>407503</v>
       </c>
       <c r="R32" t="n">
-        <v>6839027</v>
+        <v>6839131</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,19 +4150,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129739227</v>
+        <v>129738179</v>
       </c>
       <c r="B33" t="n">
         <v>79703</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407211</v>
+        <v>407483</v>
       </c>
       <c r="R33" t="n">
-        <v>6839027</v>
+        <v>6838820</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,22 +4247,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129738155</v>
+        <v>129738197</v>
       </c>
       <c r="B34" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407503</v>
+        <v>407408</v>
       </c>
       <c r="R34" t="n">
-        <v>6839131</v>
+        <v>6838841</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129738179</v>
+        <v>129739248</v>
       </c>
       <c r="B35" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,21 +4367,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407483</v>
+        <v>407440</v>
       </c>
       <c r="R35" t="n">
-        <v>6838820</v>
+        <v>6839027</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,12 +4441,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -7539,27 +7539,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129738257</v>
+        <v>129738199</v>
       </c>
       <c r="B67" t="n">
-        <v>58108</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7572,7 +7572,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407464</v>
+        <v>407576</v>
       </c>
       <c r="R67" t="n">
-        <v>6839159</v>
+        <v>6838847</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7644,45 +7644,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738193</v>
+        <v>129738257</v>
       </c>
       <c r="B68" t="n">
-        <v>79674</v>
+        <v>58108</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407714</v>
+        <v>407464</v>
       </c>
       <c r="R68" t="n">
-        <v>6839244</v>
+        <v>6839159</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7741,10 +7749,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739264</v>
+        <v>129738193</v>
       </c>
       <c r="B69" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,21 +7760,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7776,10 +7784,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407129</v>
+        <v>407714</v>
       </c>
       <c r="R69" t="n">
-        <v>6838913</v>
+        <v>6839244</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7826,22 +7834,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129739292</v>
+        <v>129739264</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,37 +7857,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407632</v>
+        <v>407129</v>
       </c>
       <c r="R70" t="n">
-        <v>6838901</v>
+        <v>6838913</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7920,7 +7925,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7939,10 +7943,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129738169</v>
+        <v>129739292</v>
       </c>
       <c r="B71" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7950,34 +7954,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407672</v>
+        <v>407632</v>
       </c>
       <c r="R71" t="n">
-        <v>6838825</v>
+        <v>6838901</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8018,25 +8025,26 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129739245</v>
+        <v>129738169</v>
       </c>
       <c r="B72" t="n">
         <v>79703</v>
@@ -8071,10 +8079,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407443</v>
+        <v>407672</v>
       </c>
       <c r="R72" t="n">
-        <v>6838872</v>
+        <v>6838825</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8121,19 +8129,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129739225</v>
+        <v>129739245</v>
       </c>
       <c r="B73" t="n">
         <v>79703</v>
@@ -8168,10 +8176,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407184</v>
+        <v>407443</v>
       </c>
       <c r="R73" t="n">
-        <v>6839011</v>
+        <v>6838872</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8230,10 +8238,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129738199</v>
+        <v>129739225</v>
       </c>
       <c r="B74" t="n">
-        <v>57737</v>
+        <v>79703</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8241,42 +8249,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407576</v>
+        <v>407184</v>
       </c>
       <c r="R74" t="n">
-        <v>6838847</v>
+        <v>6839011</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8323,12 +8323,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129739259</v>
+        <v>129738174</v>
       </c>
       <c r="B83" t="n">
-        <v>57895</v>
+        <v>79703</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9132,42 +9132,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407549</v>
+        <v>407572</v>
       </c>
       <c r="R83" t="n">
-        <v>6839053</v>
+        <v>6838852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9214,19 +9206,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738174</v>
+        <v>129738143</v>
       </c>
       <c r="B84" t="n">
         <v>79703</v>
@@ -9261,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407572</v>
+        <v>407137</v>
       </c>
       <c r="R84" t="n">
-        <v>6838852</v>
+        <v>6838823</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9323,7 +9315,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738143</v>
+        <v>129738165</v>
       </c>
       <c r="B85" t="n">
         <v>79703</v>
@@ -9358,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407137</v>
+        <v>407691</v>
       </c>
       <c r="R85" t="n">
-        <v>6838823</v>
+        <v>6839279</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9420,7 +9412,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129738165</v>
+        <v>129739238</v>
       </c>
       <c r="B86" t="n">
         <v>79703</v>
@@ -9455,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407691</v>
+        <v>407627</v>
       </c>
       <c r="R86" t="n">
-        <v>6839279</v>
+        <v>6839039</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9505,19 +9497,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129739238</v>
+        <v>129738148</v>
       </c>
       <c r="B87" t="n">
         <v>79703</v>
@@ -9552,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407627</v>
+        <v>407233</v>
       </c>
       <c r="R87" t="n">
-        <v>6839039</v>
+        <v>6838964</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9602,22 +9594,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129738148</v>
+        <v>129739259</v>
       </c>
       <c r="B88" t="n">
-        <v>79703</v>
+        <v>57895</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9625,34 +9617,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407233</v>
+        <v>407549</v>
       </c>
       <c r="R88" t="n">
-        <v>6838964</v>
+        <v>6839053</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,12 +9699,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10196,45 +10196,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129739255</v>
+        <v>129738227</v>
       </c>
       <c r="B94" t="n">
-        <v>79674</v>
+        <v>5480</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>101920</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407411</v>
+        <v>407545</v>
       </c>
       <c r="R94" t="n">
-        <v>6838819</v>
+        <v>6839241</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10275,28 +10284,29 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129739258</v>
+        <v>129739255</v>
       </c>
       <c r="B95" t="n">
-        <v>57737</v>
+        <v>79674</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10304,42 +10314,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407616</v>
+        <v>407411</v>
       </c>
       <c r="R95" t="n">
-        <v>6838890</v>
+        <v>6838819</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10398,41 +10400,40 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129738227</v>
+        <v>129739258</v>
       </c>
       <c r="B96" t="n">
-        <v>5480</v>
+        <v>57737</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>101920</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10442,10 +10443,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407545</v>
+        <v>407616</v>
       </c>
       <c r="R96" t="n">
-        <v>6839241</v>
+        <v>6838890</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10486,19 +10487,18 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129738278</v>
+        <v>129738266</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,34 +2490,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407601</v>
+        <v>407598</v>
       </c>
       <c r="R16" t="n">
-        <v>6838838</v>
+        <v>6838839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2576,10 +2584,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129739237</v>
+        <v>129739257</v>
       </c>
       <c r="B17" t="n">
-        <v>79703</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,34 +2595,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407617</v>
+        <v>407574</v>
       </c>
       <c r="R17" t="n">
-        <v>6839035</v>
+        <v>6839050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2673,10 +2689,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738187</v>
+        <v>129738278</v>
       </c>
       <c r="B18" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,21 +2700,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2708,10 +2724,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407437</v>
+        <v>407601</v>
       </c>
       <c r="R18" t="n">
-        <v>6838840</v>
+        <v>6838838</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2770,10 +2786,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738167</v>
+        <v>129739237</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407714</v>
+        <v>407617</v>
       </c>
       <c r="R19" t="n">
-        <v>6839244</v>
+        <v>6839035</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2855,22 +2871,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738159</v>
+        <v>129738187</v>
       </c>
       <c r="B20" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,10 +2918,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407516</v>
+        <v>407437</v>
       </c>
       <c r="R20" t="n">
-        <v>6839209</v>
+        <v>6838840</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2964,10 +2980,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129739257</v>
+        <v>129738167</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,42 +2991,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407574</v>
+        <v>407714</v>
       </c>
       <c r="R21" t="n">
-        <v>6839050</v>
+        <v>6839244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3057,22 +3065,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129739256</v>
+        <v>129738159</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,42 +3088,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407082</v>
+        <v>407516</v>
       </c>
       <c r="R22" t="n">
-        <v>6838747</v>
+        <v>6839209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3162,22 +3162,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129738266</v>
+        <v>129739256</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407598</v>
+        <v>407082</v>
       </c>
       <c r="R23" t="n">
-        <v>6838839</v>
+        <v>6838747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,66 +3267,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129738245</v>
+        <v>129739265</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407233</v>
+        <v>407615</v>
       </c>
       <c r="R24" t="n">
-        <v>6838838</v>
+        <v>6839034</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3367,64 +3358,72 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129739265</v>
+        <v>129738245</v>
       </c>
       <c r="B25" t="n">
-        <v>78842</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407615</v>
+        <v>407233</v>
       </c>
       <c r="R25" t="n">
-        <v>6839034</v>
+        <v>6838838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3465,28 +3464,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129739291</v>
+        <v>129739266</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,21 +3494,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407656</v>
+        <v>407649</v>
       </c>
       <c r="R26" t="n">
-        <v>6839031</v>
+        <v>6838875</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3580,10 +3580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129738154</v>
+        <v>129739291</v>
       </c>
       <c r="B27" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,21 +3591,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407536</v>
+        <v>407656</v>
       </c>
       <c r="R27" t="n">
-        <v>6839138</v>
+        <v>6839031</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,22 +3665,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129739233</v>
+        <v>129739272</v>
       </c>
       <c r="B28" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407429</v>
+        <v>407597</v>
       </c>
       <c r="R28" t="n">
-        <v>6839067</v>
+        <v>6838888</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3774,10 +3774,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129739272</v>
+        <v>129738154</v>
       </c>
       <c r="B29" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,21 +3785,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407597</v>
+        <v>407536</v>
       </c>
       <c r="R29" t="n">
-        <v>6838888</v>
+        <v>6839138</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,22 +3859,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129739266</v>
+        <v>129739233</v>
       </c>
       <c r="B30" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407649</v>
+        <v>407429</v>
       </c>
       <c r="R30" t="n">
-        <v>6838875</v>
+        <v>6839067</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
         <v>129739227</v>
       </c>
       <c r="B31" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>129738155</v>
       </c>
       <c r="B32" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>129738179</v>
       </c>
       <c r="B33" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>129738197</v>
       </c>
       <c r="B34" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>129739248</v>
       </c>
       <c r="B35" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,10 +4453,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738184</v>
+        <v>129738287</v>
       </c>
       <c r="B36" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4464,21 +4464,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407445</v>
+        <v>407591</v>
       </c>
       <c r="R36" t="n">
-        <v>6838844</v>
+        <v>6838814</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129738149</v>
+        <v>129738283</v>
       </c>
       <c r="B37" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4561,34 +4561,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407199</v>
+        <v>407598</v>
       </c>
       <c r="R37" t="n">
-        <v>6838976</v>
+        <v>6838839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4623,12 +4626,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4647,10 +4656,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129738158</v>
+        <v>129739271</v>
       </c>
       <c r="B38" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,21 +4667,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4682,10 +4691,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407519</v>
+        <v>407647</v>
       </c>
       <c r="R38" t="n">
-        <v>6839207</v>
+        <v>6838874</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4732,22 +4741,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738287</v>
+        <v>129738184</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4755,21 +4764,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4779,10 +4788,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407591</v>
+        <v>407445</v>
       </c>
       <c r="R39" t="n">
-        <v>6838814</v>
+        <v>6838844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4841,10 +4850,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738283</v>
+        <v>129738149</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4852,37 +4861,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407598</v>
+        <v>407199</v>
       </c>
       <c r="R40" t="n">
-        <v>6838839</v>
+        <v>6838976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4917,18 +4923,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129739271</v>
+        <v>129738158</v>
       </c>
       <c r="B41" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4958,21 +4958,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407647</v>
+        <v>407519</v>
       </c>
       <c r="R41" t="n">
-        <v>6838874</v>
+        <v>6839207</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5032,12 +5032,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
         <v>129738246</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>129739270</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5258,54 +5258,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738247</v>
+        <v>129738292</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>78753</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407158</v>
+        <v>407528</v>
       </c>
       <c r="R44" t="n">
-        <v>6838902</v>
+        <v>6839142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5346,7 +5337,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5365,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738292</v>
+        <v>129739240</v>
       </c>
       <c r="B45" t="n">
-        <v>78750</v>
+        <v>79706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5400,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407528</v>
+        <v>407581</v>
       </c>
       <c r="R45" t="n">
-        <v>6839142</v>
+        <v>6838885</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5450,22 +5440,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129739240</v>
+        <v>129738186</v>
       </c>
       <c r="B46" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5497,10 +5487,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407581</v>
+        <v>407479</v>
       </c>
       <c r="R46" t="n">
-        <v>6838885</v>
+        <v>6838810</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5547,22 +5537,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738186</v>
+        <v>129738290</v>
       </c>
       <c r="B47" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5594,10 +5584,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407479</v>
+        <v>407575</v>
       </c>
       <c r="R47" t="n">
-        <v>6838810</v>
+        <v>6838839</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5656,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738290</v>
+        <v>129738204</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,34 +5657,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407575</v>
+        <v>407170</v>
       </c>
       <c r="R48" t="n">
-        <v>6838839</v>
+        <v>6838942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5753,10 +5751,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129738204</v>
+        <v>129739250</v>
       </c>
       <c r="B49" t="n">
-        <v>57734</v>
+        <v>79677</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5764,31 +5762,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5796,10 +5789,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407170</v>
+        <v>407493</v>
       </c>
       <c r="R49" t="n">
-        <v>6838942</v>
+        <v>6839112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5840,55 +5833,62 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129739250</v>
+        <v>129738247</v>
       </c>
       <c r="B50" t="n">
-        <v>79674</v>
+        <v>8451</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407493</v>
+        <v>407158</v>
       </c>
       <c r="R50" t="n">
-        <v>6839112</v>
+        <v>6838902</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5947,22 +5947,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129738152</v>
+        <v>129738196</v>
       </c>
       <c r="B51" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5970,21 +5970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407440</v>
+        <v>407436</v>
       </c>
       <c r="R51" t="n">
-        <v>6839113</v>
+        <v>6838838</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,10 +6056,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129739234</v>
+        <v>129738152</v>
       </c>
       <c r="B52" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407466</v>
+        <v>407440</v>
       </c>
       <c r="R52" t="n">
-        <v>6839082</v>
+        <v>6839113</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6141,22 +6141,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129738196</v>
+        <v>129739234</v>
       </c>
       <c r="B53" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407436</v>
+        <v>407466</v>
       </c>
       <c r="R53" t="n">
-        <v>6838838</v>
+        <v>6839082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6238,12 +6238,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6253,7 +6253,7 @@
         <v>129738160</v>
       </c>
       <c r="B54" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,10 +6347,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738291</v>
+        <v>129738168</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6358,21 +6358,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407574</v>
+        <v>407717</v>
       </c>
       <c r="R55" t="n">
-        <v>6838848</v>
+        <v>6839236</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,10 +6444,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738168</v>
+        <v>129739229</v>
       </c>
       <c r="B56" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407717</v>
+        <v>407296</v>
       </c>
       <c r="R56" t="n">
-        <v>6839236</v>
+        <v>6838974</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6529,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129739229</v>
+        <v>129738198</v>
       </c>
       <c r="B57" t="n">
-        <v>79703</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,34 +6552,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407296</v>
+        <v>407575</v>
       </c>
       <c r="R57" t="n">
-        <v>6838974</v>
+        <v>6838839</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,66 +6634,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738255</v>
+        <v>129738291</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407645</v>
+        <v>407574</v>
       </c>
       <c r="R58" t="n">
-        <v>6838797</v>
+        <v>6838848</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6725,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6745,40 +6743,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738198</v>
+        <v>129738255</v>
       </c>
       <c r="B59" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6788,10 +6787,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407575</v>
+        <v>407645</v>
       </c>
       <c r="R59" t="n">
-        <v>6838839</v>
+        <v>6838797</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6832,6 +6831,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6850,54 +6850,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129738243</v>
+        <v>129739232</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407117</v>
+        <v>407441</v>
       </c>
       <c r="R60" t="n">
-        <v>6838831</v>
+        <v>6839017</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6938,29 +6929,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129738277</v>
+        <v>129739244</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6968,21 +6958,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6992,10 +6982,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407593</v>
+        <v>407448</v>
       </c>
       <c r="R61" t="n">
-        <v>6838795</v>
+        <v>6838869</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7042,22 +7032,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129739232</v>
+        <v>129739228</v>
       </c>
       <c r="B62" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7089,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407441</v>
+        <v>407244</v>
       </c>
       <c r="R62" t="n">
-        <v>6839017</v>
+        <v>6839107</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7151,10 +7141,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129739244</v>
+        <v>129738189</v>
       </c>
       <c r="B63" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7186,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407448</v>
+        <v>407407</v>
       </c>
       <c r="R63" t="n">
-        <v>6838869</v>
+        <v>6838839</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7236,57 +7226,66 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129738289</v>
+        <v>129738243</v>
       </c>
       <c r="B64" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407581</v>
+        <v>407117</v>
       </c>
       <c r="R64" t="n">
-        <v>6838815</v>
+        <v>6838831</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7327,6 +7326,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7345,10 +7345,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129739228</v>
+        <v>129738289</v>
       </c>
       <c r="B65" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407244</v>
+        <v>407581</v>
       </c>
       <c r="R65" t="n">
-        <v>6839107</v>
+        <v>6838815</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7430,22 +7430,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129738189</v>
+        <v>129738277</v>
       </c>
       <c r="B66" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7453,21 +7453,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>407407</v>
+        <v>407593</v>
       </c>
       <c r="R66" t="n">
-        <v>6838839</v>
+        <v>6838795</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129738199</v>
+        <v>129739292</v>
       </c>
       <c r="B67" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7550,31 +7550,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7582,10 +7577,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407576</v>
+        <v>407632</v>
       </c>
       <c r="R67" t="n">
-        <v>6838847</v>
+        <v>6838901</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7626,71 +7621,64 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738257</v>
+        <v>129738169</v>
       </c>
       <c r="B68" t="n">
-        <v>58108</v>
+        <v>79706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407464</v>
+        <v>407672</v>
       </c>
       <c r="R68" t="n">
-        <v>6839159</v>
+        <v>6838825</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7749,10 +7737,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129738193</v>
+        <v>129739245</v>
       </c>
       <c r="B69" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7760,21 +7748,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7784,10 +7772,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407714</v>
+        <v>407443</v>
       </c>
       <c r="R69" t="n">
-        <v>6839244</v>
+        <v>6838872</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7834,22 +7822,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129739264</v>
+        <v>129739225</v>
       </c>
       <c r="B70" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7857,21 +7845,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7881,10 +7869,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407129</v>
+        <v>407184</v>
       </c>
       <c r="R70" t="n">
-        <v>6838913</v>
+        <v>6839011</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7943,10 +7931,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129739292</v>
+        <v>129738193</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7954,37 +7942,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407632</v>
+        <v>407714</v>
       </c>
       <c r="R71" t="n">
-        <v>6838901</v>
+        <v>6839244</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8025,29 +8010,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129738169</v>
+        <v>129739264</v>
       </c>
       <c r="B72" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8055,21 +8039,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8079,10 +8063,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407672</v>
+        <v>407129</v>
       </c>
       <c r="R72" t="n">
-        <v>6838825</v>
+        <v>6838913</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8129,22 +8113,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129739245</v>
+        <v>129738199</v>
       </c>
       <c r="B73" t="n">
-        <v>79703</v>
+        <v>57740</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8152,34 +8136,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407443</v>
+        <v>407576</v>
       </c>
       <c r="R73" t="n">
-        <v>6838872</v>
+        <v>6838847</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8226,57 +8218,65 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129739225</v>
+        <v>129738257</v>
       </c>
       <c r="B74" t="n">
-        <v>79703</v>
+        <v>58111</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407184</v>
+        <v>407464</v>
       </c>
       <c r="R74" t="n">
-        <v>6839011</v>
+        <v>6839159</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8323,66 +8323,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129738244</v>
+        <v>129738275</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407231</v>
+        <v>407608</v>
       </c>
       <c r="R75" t="n">
-        <v>6838827</v>
+        <v>6839252</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8423,7 +8414,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8442,10 +8432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129738275</v>
+        <v>129738285</v>
       </c>
       <c r="B76" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8477,10 +8467,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407608</v>
+        <v>407587</v>
       </c>
       <c r="R76" t="n">
-        <v>6839252</v>
+        <v>6838806</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8539,10 +8529,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738285</v>
+        <v>129738147</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8550,21 +8540,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8574,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407587</v>
+        <v>407190</v>
       </c>
       <c r="R77" t="n">
-        <v>6838806</v>
+        <v>6838950</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,10 +8626,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738147</v>
+        <v>129738176</v>
       </c>
       <c r="B78" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8671,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407190</v>
+        <v>407519</v>
       </c>
       <c r="R78" t="n">
-        <v>6838950</v>
+        <v>6838831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8733,10 +8723,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738176</v>
+        <v>129738171</v>
       </c>
       <c r="B79" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8768,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407519</v>
+        <v>407620</v>
       </c>
       <c r="R79" t="n">
-        <v>6838831</v>
+        <v>6838898</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8830,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738171</v>
+        <v>129738181</v>
       </c>
       <c r="B80" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8865,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407620</v>
+        <v>407467</v>
       </c>
       <c r="R80" t="n">
-        <v>6838898</v>
+        <v>6838834</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8927,10 +8917,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738181</v>
+        <v>129738194</v>
       </c>
       <c r="B81" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8938,21 +8928,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8962,10 +8952,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407467</v>
+        <v>407549</v>
       </c>
       <c r="R81" t="n">
-        <v>6838834</v>
+        <v>6838809</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9024,45 +9014,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B82" t="n">
-        <v>79674</v>
+        <v>8451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R82" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,6 +9102,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129738174</v>
+        <v>129739267</v>
       </c>
       <c r="B83" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9132,21 +9132,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407572</v>
+        <v>407597</v>
       </c>
       <c r="R83" t="n">
-        <v>6838852</v>
+        <v>6838888</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9206,22 +9206,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738143</v>
+        <v>129738174</v>
       </c>
       <c r="B84" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407137</v>
+        <v>407572</v>
       </c>
       <c r="R84" t="n">
-        <v>6838823</v>
+        <v>6838852</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9315,10 +9315,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738165</v>
+        <v>129738143</v>
       </c>
       <c r="B85" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407691</v>
+        <v>407137</v>
       </c>
       <c r="R85" t="n">
-        <v>6839279</v>
+        <v>6838823</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9412,10 +9412,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129739238</v>
+        <v>129738165</v>
       </c>
       <c r="B86" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407627</v>
+        <v>407691</v>
       </c>
       <c r="R86" t="n">
-        <v>6839039</v>
+        <v>6839279</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,22 +9497,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129738148</v>
+        <v>129739238</v>
       </c>
       <c r="B87" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407233</v>
+        <v>407627</v>
       </c>
       <c r="R87" t="n">
-        <v>6838964</v>
+        <v>6839039</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9594,22 +9594,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129739259</v>
+        <v>129738148</v>
       </c>
       <c r="B88" t="n">
-        <v>57895</v>
+        <v>79706</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,42 +9617,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407549</v>
+        <v>407233</v>
       </c>
       <c r="R88" t="n">
-        <v>6839053</v>
+        <v>6838964</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,22 +9691,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129739267</v>
+        <v>129739259</v>
       </c>
       <c r="B89" t="n">
-        <v>78842</v>
+        <v>57898</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9722,34 +9714,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407597</v>
+        <v>407549</v>
       </c>
       <c r="R89" t="n">
-        <v>6838888</v>
+        <v>6839053</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129739246</v>
+        <v>129739258</v>
       </c>
       <c r="B90" t="n">
-        <v>79703</v>
+        <v>57740</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9819,34 +9819,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407427</v>
+        <v>407616</v>
       </c>
       <c r="R90" t="n">
-        <v>6838886</v>
+        <v>6838890</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9905,10 +9913,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739239</v>
+        <v>129739246</v>
       </c>
       <c r="B91" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9940,10 +9948,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407614</v>
+        <v>407427</v>
       </c>
       <c r="R91" t="n">
-        <v>6838900</v>
+        <v>6838886</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10002,10 +10010,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129738170</v>
+        <v>129739239</v>
       </c>
       <c r="B92" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10037,10 +10045,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407660</v>
+        <v>407614</v>
       </c>
       <c r="R92" t="n">
-        <v>6838791</v>
+        <v>6838900</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10087,22 +10095,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129738188</v>
+        <v>129738170</v>
       </c>
       <c r="B93" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10134,10 +10142,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407408</v>
+        <v>407660</v>
       </c>
       <c r="R93" t="n">
-        <v>6838841</v>
+        <v>6838791</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10196,54 +10204,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129738227</v>
+        <v>129738188</v>
       </c>
       <c r="B94" t="n">
-        <v>5480</v>
+        <v>79706</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407545</v>
+        <v>407408</v>
       </c>
       <c r="R94" t="n">
-        <v>6839241</v>
+        <v>6838841</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10284,7 +10283,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10303,45 +10301,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129739255</v>
+        <v>129738227</v>
       </c>
       <c r="B95" t="n">
-        <v>79674</v>
+        <v>5480</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>101920</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407411</v>
+        <v>407545</v>
       </c>
       <c r="R95" t="n">
-        <v>6838819</v>
+        <v>6839241</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10382,28 +10389,29 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129739258</v>
+        <v>129739255</v>
       </c>
       <c r="B96" t="n">
-        <v>57737</v>
+        <v>79677</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10411,42 +10419,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407616</v>
+        <v>407411</v>
       </c>
       <c r="R96" t="n">
-        <v>6838890</v>
+        <v>6838819</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
         <v>129739289</v>
       </c>
       <c r="B97" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>129738144</v>
       </c>
       <c r="B98" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>129738185</v>
       </c>
       <c r="B99" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>129738172</v>
       </c>
       <c r="B100" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>129739242</v>
       </c>
       <c r="B101" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10990,45 +10990,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129739252</v>
+        <v>129738250</v>
       </c>
       <c r="B102" t="n">
-        <v>79674</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407615</v>
+        <v>407525</v>
       </c>
       <c r="R102" t="n">
-        <v>6839041</v>
+        <v>6839244</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11069,28 +11078,29 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129739251</v>
+        <v>129739252</v>
       </c>
       <c r="B103" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11122,10 +11132,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407563</v>
+        <v>407615</v>
       </c>
       <c r="R103" t="n">
-        <v>6839056</v>
+        <v>6839041</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11187,7 +11197,7 @@
         <v>129738191</v>
       </c>
       <c r="B104" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11281,54 +11291,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129738250</v>
+        <v>129739251</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79677</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407525</v>
+        <v>407563</v>
       </c>
       <c r="R105" t="n">
-        <v>6839244</v>
+        <v>6839056</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11369,19 +11370,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
         <v>129739273</v>
       </c>
       <c r="B106" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>129738173</v>
       </c>
       <c r="B107" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>129738182</v>
       </c>
       <c r="B108" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11679,10 +11679,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738180</v>
+        <v>129738276</v>
       </c>
       <c r="B109" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11690,21 +11690,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407480</v>
+        <v>407607</v>
       </c>
       <c r="R109" t="n">
-        <v>6838840</v>
+        <v>6838798</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11776,10 +11776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738276</v>
+        <v>129738180</v>
       </c>
       <c r="B110" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407607</v>
+        <v>407480</v>
       </c>
       <c r="R110" t="n">
-        <v>6838798</v>
+        <v>6838840</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11876,7 +11876,7 @@
         <v>129738190</v>
       </c>
       <c r="B111" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>129738175</v>
       </c>
       <c r="B112" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>129738268</v>
       </c>
       <c r="B113" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>129738249</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129739243</v>
+        <v>129738280</v>
       </c>
       <c r="B115" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,34 +12290,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407451</v>
+        <v>407623</v>
       </c>
       <c r="R115" t="n">
-        <v>6838866</v>
+        <v>6838894</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12352,34 +12355,40 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129738280</v>
+        <v>129739290</v>
       </c>
       <c r="B116" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12414,10 +12423,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407623</v>
+        <v>407657</v>
       </c>
       <c r="R116" t="n">
-        <v>6838894</v>
+        <v>6839033</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12454,7 +12463,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12470,22 +12479,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129739224</v>
+        <v>129738282</v>
       </c>
       <c r="B117" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12493,21 +12502,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12517,10 +12526,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407121</v>
+        <v>407588</v>
       </c>
       <c r="R117" t="n">
-        <v>6838895</v>
+        <v>6838831</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12555,6 +12564,11 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12567,22 +12581,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129738282</v>
+        <v>129739243</v>
       </c>
       <c r="B118" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12590,21 +12604,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12614,10 +12628,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407588</v>
+        <v>407451</v>
       </c>
       <c r="R118" t="n">
-        <v>6838831</v>
+        <v>6838866</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12652,11 +12666,6 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12669,22 +12678,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129738145</v>
+        <v>129739224</v>
       </c>
       <c r="B119" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12716,10 +12725,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407194</v>
+        <v>407121</v>
       </c>
       <c r="R119" t="n">
-        <v>6838873</v>
+        <v>6838895</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12766,22 +12775,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129739290</v>
+        <v>129738145</v>
       </c>
       <c r="B120" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12789,37 +12798,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407657</v>
+        <v>407194</v>
       </c>
       <c r="R120" t="n">
-        <v>6839033</v>
+        <v>6838873</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12854,30 +12860,24 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12887,7 +12887,7 @@
         <v>129738192</v>
       </c>
       <c r="B121" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>129739286</v>
       </c>
       <c r="B122" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>129738279</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>129738288</v>
       </c>
       <c r="B124" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13272,10 +13272,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738146</v>
+        <v>129739249</v>
       </c>
       <c r="B125" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407163</v>
+        <v>407437</v>
       </c>
       <c r="R125" t="n">
-        <v>6838891</v>
+        <v>6839060</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13357,22 +13357,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129739241</v>
+        <v>129738146</v>
       </c>
       <c r="B126" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407524</v>
+        <v>407163</v>
       </c>
       <c r="R126" t="n">
-        <v>6838914</v>
+        <v>6838891</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13454,22 +13454,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739249</v>
+        <v>129739241</v>
       </c>
       <c r="B127" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407437</v>
+        <v>407524</v>
       </c>
       <c r="R127" t="n">
-        <v>6839060</v>
+        <v>6838914</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13563,10 +13563,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129738242</v>
+        <v>129739287</v>
       </c>
       <c r="B128" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13574,21 +13574,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13598,10 +13598,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407719</v>
+        <v>407622</v>
       </c>
       <c r="R128" t="n">
-        <v>6839222</v>
+        <v>6839045</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,22 +13648,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129739254</v>
+        <v>129738281</v>
       </c>
       <c r="B129" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,21 +13671,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13695,10 +13695,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407418</v>
+        <v>407587</v>
       </c>
       <c r="R129" t="n">
-        <v>6838867</v>
+        <v>6838872</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13745,22 +13745,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129739268</v>
+        <v>129738157</v>
       </c>
       <c r="B130" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,37 +13768,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407573</v>
+        <v>407535</v>
       </c>
       <c r="R130" t="n">
-        <v>6838884</v>
+        <v>6839193</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13839,73 +13836,63 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129738248</v>
+        <v>129738177</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>407481</v>
+        <v>407476</v>
       </c>
       <c r="R131" t="n">
-        <v>6839152</v>
+        <v>6838854</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13946,7 +13933,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13965,54 +13951,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129738256</v>
+        <v>129738156</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>407616</v>
+        <v>407477</v>
       </c>
       <c r="R132" t="n">
-        <v>6838794</v>
+        <v>6839132</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14053,7 +14030,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14072,10 +14048,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129738281</v>
+        <v>129739230</v>
       </c>
       <c r="B133" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14083,21 +14059,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14107,10 +14083,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>407587</v>
+        <v>407404</v>
       </c>
       <c r="R133" t="n">
-        <v>6838872</v>
+        <v>6839005</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14157,22 +14133,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129738157</v>
+        <v>129738151</v>
       </c>
       <c r="B134" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14204,10 +14180,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>407535</v>
+        <v>407378</v>
       </c>
       <c r="R134" t="n">
-        <v>6839193</v>
+        <v>6839143</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14266,10 +14242,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129739287</v>
+        <v>129739235</v>
       </c>
       <c r="B135" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14277,21 +14253,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14301,10 +14277,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>407622</v>
+        <v>407604</v>
       </c>
       <c r="R135" t="n">
-        <v>6839045</v>
+        <v>6839024</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14363,10 +14339,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129738177</v>
+        <v>129739231</v>
       </c>
       <c r="B136" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14398,10 +14374,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>407476</v>
+        <v>407422</v>
       </c>
       <c r="R136" t="n">
-        <v>6838854</v>
+        <v>6839006</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14448,22 +14424,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129738156</v>
+        <v>129738242</v>
       </c>
       <c r="B137" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14471,21 +14447,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14495,10 +14471,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>407477</v>
+        <v>407719</v>
       </c>
       <c r="R137" t="n">
-        <v>6839132</v>
+        <v>6839222</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14557,10 +14533,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129739230</v>
+        <v>129739254</v>
       </c>
       <c r="B138" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14568,21 +14544,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14592,10 +14568,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>407404</v>
+        <v>407418</v>
       </c>
       <c r="R138" t="n">
-        <v>6839005</v>
+        <v>6838867</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14654,10 +14630,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129738151</v>
+        <v>129739268</v>
       </c>
       <c r="B139" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14665,34 +14641,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>407378</v>
+        <v>407573</v>
       </c>
       <c r="R139" t="n">
-        <v>6839143</v>
+        <v>6838884</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14733,63 +14712,73 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129739235</v>
+        <v>129738248</v>
       </c>
       <c r="B140" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407604</v>
+        <v>407481</v>
       </c>
       <c r="R140" t="n">
-        <v>6839024</v>
+        <v>6839152</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14830,63 +14819,73 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129739231</v>
+        <v>129738256</v>
       </c>
       <c r="B141" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407422</v>
+        <v>407616</v>
       </c>
       <c r="R141" t="n">
-        <v>6839006</v>
+        <v>6838794</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14927,18 +14926,19 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -14948,7 +14948,7 @@
         <v>129738201</v>
       </c>
       <c r="B142" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15050,10 +15050,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738150</v>
+        <v>129739253</v>
       </c>
       <c r="B143" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15061,34 +15061,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407203</v>
+        <v>407589</v>
       </c>
       <c r="R143" t="n">
-        <v>6839015</v>
+        <v>6838889</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15129,28 +15132,29 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738286</v>
+        <v>129738195</v>
       </c>
       <c r="B144" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15158,21 +15162,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15182,10 +15186,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407586</v>
+        <v>407479</v>
       </c>
       <c r="R144" t="n">
-        <v>6838820</v>
+        <v>6838852</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15244,10 +15248,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738284</v>
+        <v>129738286</v>
       </c>
       <c r="B145" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15279,10 +15283,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407595</v>
+        <v>407586</v>
       </c>
       <c r="R145" t="n">
-        <v>6838836</v>
+        <v>6838820</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15341,10 +15345,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129739253</v>
+        <v>129738284</v>
       </c>
       <c r="B146" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15352,37 +15356,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407589</v>
+        <v>407595</v>
       </c>
       <c r="R146" t="n">
-        <v>6838889</v>
+        <v>6838836</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15423,29 +15424,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738195</v>
+        <v>129738150</v>
       </c>
       <c r="B147" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15453,21 +15453,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15477,10 +15477,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407479</v>
+        <v>407203</v>
       </c>
       <c r="R147" t="n">
-        <v>6838852</v>
+        <v>6839015</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738164</v>
+        <v>129738274</v>
       </c>
       <c r="B148" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15550,21 +15550,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407666</v>
+        <v>407522</v>
       </c>
       <c r="R148" t="n">
-        <v>6839269</v>
+        <v>6839200</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129738153</v>
+        <v>129739288</v>
       </c>
       <c r="B149" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407474</v>
+        <v>407625</v>
       </c>
       <c r="R149" t="n">
-        <v>6839108</v>
+        <v>6839051</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15721,22 +15721,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129738166</v>
+        <v>129739247</v>
       </c>
       <c r="B150" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15744,21 +15744,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407704</v>
+        <v>407319</v>
       </c>
       <c r="R150" t="n">
-        <v>6839251</v>
+        <v>6838979</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15818,22 +15818,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738274</v>
+        <v>129738164</v>
       </c>
       <c r="B151" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407522</v>
+        <v>407666</v>
       </c>
       <c r="R151" t="n">
-        <v>6839200</v>
+        <v>6839269</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15927,10 +15927,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129739288</v>
+        <v>129738153</v>
       </c>
       <c r="B152" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15938,21 +15938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407625</v>
+        <v>407474</v>
       </c>
       <c r="R152" t="n">
-        <v>6839051</v>
+        <v>6839108</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16012,22 +16012,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129739247</v>
+        <v>129738166</v>
       </c>
       <c r="B153" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>407319</v>
+        <v>407704</v>
       </c>
       <c r="R153" t="n">
-        <v>6838979</v>
+        <v>6839251</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16109,12 +16109,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -5959,10 +5959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129738196</v>
+        <v>129738152</v>
       </c>
       <c r="B51" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5970,21 +5970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407436</v>
+        <v>407440</v>
       </c>
       <c r="R51" t="n">
-        <v>6838838</v>
+        <v>6839113</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129738152</v>
+        <v>129739234</v>
       </c>
       <c r="B52" t="n">
         <v>79706</v>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407440</v>
+        <v>407466</v>
       </c>
       <c r="R52" t="n">
-        <v>6839113</v>
+        <v>6839082</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6141,22 +6141,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129739234</v>
+        <v>129738196</v>
       </c>
       <c r="B53" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407466</v>
+        <v>407436</v>
       </c>
       <c r="R53" t="n">
-        <v>6839082</v>
+        <v>6838838</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6238,22 +6238,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738160</v>
+        <v>129738291</v>
       </c>
       <c r="B54" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,21 +6261,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6285,10 +6285,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407512</v>
+        <v>407574</v>
       </c>
       <c r="R54" t="n">
-        <v>6839214</v>
+        <v>6838848</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738168</v>
+        <v>129738160</v>
       </c>
       <c r="B55" t="n">
         <v>79706</v>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407717</v>
+        <v>407512</v>
       </c>
       <c r="R55" t="n">
-        <v>6839236</v>
+        <v>6839214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129739229</v>
+        <v>129738168</v>
       </c>
       <c r="B56" t="n">
         <v>79706</v>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407296</v>
+        <v>407717</v>
       </c>
       <c r="R56" t="n">
-        <v>6838974</v>
+        <v>6839236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6529,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738198</v>
+        <v>129739229</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,42 +6552,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407575</v>
+        <v>407296</v>
       </c>
       <c r="R57" t="n">
-        <v>6838839</v>
+        <v>6838974</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6634,57 +6626,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738291</v>
+        <v>129738255</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407574</v>
+        <v>407645</v>
       </c>
       <c r="R58" t="n">
-        <v>6838848</v>
+        <v>6838797</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6725,6 +6726,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6743,41 +6745,40 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738255</v>
+        <v>129738198</v>
       </c>
       <c r="B59" t="n">
-        <v>8451</v>
+        <v>57740</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6787,10 +6788,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407645</v>
+        <v>407575</v>
       </c>
       <c r="R59" t="n">
-        <v>6838797</v>
+        <v>6838839</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6831,7 +6832,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129739292</v>
+        <v>129738169</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7550,37 +7550,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407632</v>
+        <v>407672</v>
       </c>
       <c r="R67" t="n">
-        <v>6838901</v>
+        <v>6838825</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7621,26 +7618,25 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738169</v>
+        <v>129739245</v>
       </c>
       <c r="B68" t="n">
         <v>79706</v>
@@ -7675,10 +7671,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407672</v>
+        <v>407443</v>
       </c>
       <c r="R68" t="n">
-        <v>6838825</v>
+        <v>6838872</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7725,19 +7721,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739245</v>
+        <v>129739225</v>
       </c>
       <c r="B69" t="n">
         <v>79706</v>
@@ -7772,10 +7768,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407443</v>
+        <v>407184</v>
       </c>
       <c r="R69" t="n">
-        <v>6838872</v>
+        <v>6839011</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7834,45 +7830,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129739225</v>
+        <v>129738257</v>
       </c>
       <c r="B70" t="n">
-        <v>79706</v>
+        <v>58111</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407184</v>
+        <v>407464</v>
       </c>
       <c r="R70" t="n">
-        <v>6839011</v>
+        <v>6839159</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7919,22 +7923,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129738193</v>
+        <v>129739264</v>
       </c>
       <c r="B71" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7942,21 +7946,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7966,10 +7970,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407714</v>
+        <v>407129</v>
       </c>
       <c r="R71" t="n">
-        <v>6839244</v>
+        <v>6838913</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8016,22 +8020,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129739264</v>
+        <v>129738193</v>
       </c>
       <c r="B72" t="n">
-        <v>78845</v>
+        <v>79677</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8039,21 +8043,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8063,10 +8067,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407129</v>
+        <v>407714</v>
       </c>
       <c r="R72" t="n">
-        <v>6838913</v>
+        <v>6839244</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8113,22 +8117,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129738199</v>
+        <v>129739292</v>
       </c>
       <c r="B73" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8136,31 +8140,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8168,10 +8167,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407576</v>
+        <v>407632</v>
       </c>
       <c r="R73" t="n">
-        <v>6838847</v>
+        <v>6838901</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8212,45 +8211,46 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129738257</v>
+        <v>129738199</v>
       </c>
       <c r="B74" t="n">
-        <v>58111</v>
+        <v>57740</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8263,7 +8263,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407464</v>
+        <v>407576</v>
       </c>
       <c r="R74" t="n">
-        <v>6839159</v>
+        <v>6838847</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8917,45 +8917,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B81" t="n">
-        <v>79677</v>
+        <v>8451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R81" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8996,6 +9005,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9014,54 +9024,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738244</v>
+        <v>129738194</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>79677</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407231</v>
+        <v>407549</v>
       </c>
       <c r="R82" t="n">
-        <v>6838827</v>
+        <v>6838809</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9102,7 +9103,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129739267</v>
+        <v>129738165</v>
       </c>
       <c r="B83" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9132,21 +9132,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407597</v>
+        <v>407691</v>
       </c>
       <c r="R83" t="n">
-        <v>6838888</v>
+        <v>6839279</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9206,19 +9206,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129738174</v>
+        <v>129739238</v>
       </c>
       <c r="B84" t="n">
         <v>79706</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407572</v>
+        <v>407627</v>
       </c>
       <c r="R84" t="n">
-        <v>6838852</v>
+        <v>6839039</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9303,19 +9303,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738143</v>
+        <v>129738174</v>
       </c>
       <c r="B85" t="n">
         <v>79706</v>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407137</v>
+        <v>407572</v>
       </c>
       <c r="R85" t="n">
-        <v>6838823</v>
+        <v>6838852</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9412,7 +9412,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129738165</v>
+        <v>129738143</v>
       </c>
       <c r="B86" t="n">
         <v>79706</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407691</v>
+        <v>407137</v>
       </c>
       <c r="R86" t="n">
-        <v>6839279</v>
+        <v>6838823</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9509,7 +9509,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129739238</v>
+        <v>129738148</v>
       </c>
       <c r="B87" t="n">
         <v>79706</v>
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>407627</v>
+        <v>407233</v>
       </c>
       <c r="R87" t="n">
-        <v>6839039</v>
+        <v>6838964</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9594,22 +9594,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129738148</v>
+        <v>129739259</v>
       </c>
       <c r="B88" t="n">
-        <v>79706</v>
+        <v>57898</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9617,34 +9617,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>407233</v>
+        <v>407549</v>
       </c>
       <c r="R88" t="n">
-        <v>6838964</v>
+        <v>6839053</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9691,22 +9699,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129739259</v>
+        <v>129739267</v>
       </c>
       <c r="B89" t="n">
-        <v>57898</v>
+        <v>78845</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9714,42 +9722,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407549</v>
+        <v>407597</v>
       </c>
       <c r="R89" t="n">
-        <v>6839053</v>
+        <v>6838888</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129739289</v>
+        <v>129739252</v>
       </c>
       <c r="B97" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10516,21 +10516,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407649</v>
+        <v>407615</v>
       </c>
       <c r="R97" t="n">
         <v>6839041</v>
@@ -10602,10 +10602,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129738144</v>
+        <v>129738191</v>
       </c>
       <c r="B98" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10613,21 +10613,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407223</v>
+        <v>407474</v>
       </c>
       <c r="R98" t="n">
-        <v>6838821</v>
+        <v>6839108</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129738185</v>
+        <v>129739251</v>
       </c>
       <c r="B99" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407439</v>
+        <v>407563</v>
       </c>
       <c r="R99" t="n">
-        <v>6838837</v>
+        <v>6839056</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10784,57 +10784,66 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129738172</v>
+        <v>129738250</v>
       </c>
       <c r="B100" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407585</v>
+        <v>407525</v>
       </c>
       <c r="R100" t="n">
-        <v>6838872</v>
+        <v>6839244</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10875,6 +10884,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10893,10 +10903,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129739242</v>
+        <v>129739289</v>
       </c>
       <c r="B101" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10904,21 +10914,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10928,10 +10938,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407515</v>
+        <v>407649</v>
       </c>
       <c r="R101" t="n">
-        <v>6838875</v>
+        <v>6839041</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10990,54 +11000,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129738250</v>
+        <v>129738144</v>
       </c>
       <c r="B102" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407525</v>
+        <v>407223</v>
       </c>
       <c r="R102" t="n">
-        <v>6839244</v>
+        <v>6838821</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11078,7 +11079,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11097,10 +11097,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129739252</v>
+        <v>129738185</v>
       </c>
       <c r="B103" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11108,21 +11108,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11132,10 +11132,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407615</v>
+        <v>407439</v>
       </c>
       <c r="R103" t="n">
-        <v>6839041</v>
+        <v>6838837</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11182,22 +11182,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129738191</v>
+        <v>129738172</v>
       </c>
       <c r="B104" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11205,21 +11205,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407474</v>
+        <v>407585</v>
       </c>
       <c r="R104" t="n">
-        <v>6839108</v>
+        <v>6838872</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11291,10 +11291,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129739251</v>
+        <v>129739242</v>
       </c>
       <c r="B105" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11302,21 +11302,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11326,10 +11326,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407563</v>
+        <v>407515</v>
       </c>
       <c r="R105" t="n">
-        <v>6839056</v>
+        <v>6838875</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13272,10 +13272,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129739249</v>
+        <v>129738146</v>
       </c>
       <c r="B125" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407437</v>
+        <v>407163</v>
       </c>
       <c r="R125" t="n">
-        <v>6839060</v>
+        <v>6838891</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13357,19 +13357,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129738146</v>
+        <v>129739241</v>
       </c>
       <c r="B126" t="n">
         <v>79706</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407163</v>
+        <v>407524</v>
       </c>
       <c r="R126" t="n">
-        <v>6838891</v>
+        <v>6838914</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13454,22 +13454,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739241</v>
+        <v>129739249</v>
       </c>
       <c r="B127" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407524</v>
+        <v>407437</v>
       </c>
       <c r="R127" t="n">
-        <v>6838914</v>
+        <v>6839060</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15733,10 +15733,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129739247</v>
+        <v>129738164</v>
       </c>
       <c r="B150" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15744,21 +15744,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407319</v>
+        <v>407666</v>
       </c>
       <c r="R150" t="n">
-        <v>6838979</v>
+        <v>6839269</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15818,19 +15818,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738164</v>
+        <v>129738153</v>
       </c>
       <c r="B151" t="n">
         <v>79706</v>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407666</v>
+        <v>407474</v>
       </c>
       <c r="R151" t="n">
-        <v>6839269</v>
+        <v>6839108</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15927,7 +15927,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129738153</v>
+        <v>129738166</v>
       </c>
       <c r="B152" t="n">
         <v>79706</v>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407474</v>
+        <v>407704</v>
       </c>
       <c r="R152" t="n">
-        <v>6839108</v>
+        <v>6839251</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16024,10 +16024,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129738166</v>
+        <v>129739247</v>
       </c>
       <c r="B153" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>407704</v>
+        <v>407319</v>
       </c>
       <c r="R153" t="n">
-        <v>6839251</v>
+        <v>6838979</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16109,12 +16109,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,7 +2479,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129738266</v>
+        <v>129739256</v>
       </c>
       <c r="B16" t="n">
         <v>57740</v>
@@ -2512,7 +2512,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407598</v>
+        <v>407082</v>
       </c>
       <c r="R16" t="n">
-        <v>6838839</v>
+        <v>6838747</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2572,22 +2572,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129739257</v>
+        <v>129738278</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,42 +2595,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407574</v>
+        <v>407601</v>
       </c>
       <c r="R17" t="n">
-        <v>6839050</v>
+        <v>6838838</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2677,22 +2669,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129738278</v>
+        <v>129739237</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,21 +2692,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2724,10 +2716,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407601</v>
+        <v>407617</v>
       </c>
       <c r="R18" t="n">
-        <v>6838838</v>
+        <v>6839035</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2774,19 +2766,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129739237</v>
+        <v>129738187</v>
       </c>
       <c r="B19" t="n">
         <v>79706</v>
@@ -2821,10 +2813,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407617</v>
+        <v>407437</v>
       </c>
       <c r="R19" t="n">
-        <v>6839035</v>
+        <v>6838840</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2871,19 +2863,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738187</v>
+        <v>129738167</v>
       </c>
       <c r="B20" t="n">
         <v>79706</v>
@@ -2918,10 +2910,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407437</v>
+        <v>407714</v>
       </c>
       <c r="R20" t="n">
-        <v>6838840</v>
+        <v>6839244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2980,7 +2972,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738167</v>
+        <v>129738159</v>
       </c>
       <c r="B21" t="n">
         <v>79706</v>
@@ -3015,10 +3007,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407714</v>
+        <v>407516</v>
       </c>
       <c r="R21" t="n">
-        <v>6839244</v>
+        <v>6839209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3077,10 +3069,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738159</v>
+        <v>129738266</v>
       </c>
       <c r="B22" t="n">
-        <v>79706</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,34 +3080,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407516</v>
+        <v>407598</v>
       </c>
       <c r="R22" t="n">
-        <v>6839209</v>
+        <v>6838839</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739256</v>
+        <v>129739257</v>
       </c>
       <c r="B23" t="n">
         <v>57740</v>
@@ -3207,7 +3207,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407082</v>
+        <v>407574</v>
       </c>
       <c r="R23" t="n">
-        <v>6838747</v>
+        <v>6839050</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738292</v>
+        <v>129739240</v>
       </c>
       <c r="B44" t="n">
-        <v>78753</v>
+        <v>79706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407528</v>
+        <v>407581</v>
       </c>
       <c r="R44" t="n">
-        <v>6839142</v>
+        <v>6838885</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5343,19 +5343,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129739240</v>
+        <v>129738186</v>
       </c>
       <c r="B45" t="n">
         <v>79706</v>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407581</v>
+        <v>407479</v>
       </c>
       <c r="R45" t="n">
-        <v>6838885</v>
+        <v>6838810</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5440,22 +5440,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738186</v>
+        <v>129738204</v>
       </c>
       <c r="B46" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5463,34 +5463,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407479</v>
+        <v>407170</v>
       </c>
       <c r="R46" t="n">
-        <v>6838810</v>
+        <v>6838942</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5549,10 +5557,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738290</v>
+        <v>129739250</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,34 +5568,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407575</v>
+        <v>407493</v>
       </c>
       <c r="R47" t="n">
-        <v>6838839</v>
+        <v>6839112</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5628,58 +5639,60 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738204</v>
+        <v>129738247</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5689,10 +5702,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407170</v>
+        <v>407158</v>
       </c>
       <c r="R48" t="n">
-        <v>6838942</v>
+        <v>6838902</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5733,6 +5746,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5751,10 +5765,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129739250</v>
+        <v>129738292</v>
       </c>
       <c r="B49" t="n">
-        <v>79677</v>
+        <v>78753</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5762,37 +5776,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407493</v>
+        <v>407528</v>
       </c>
       <c r="R49" t="n">
-        <v>6839112</v>
+        <v>6839142</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5833,73 +5844,63 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129738247</v>
+        <v>129738290</v>
       </c>
       <c r="B50" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407158</v>
+        <v>407575</v>
       </c>
       <c r="R50" t="n">
-        <v>6838902</v>
+        <v>6838839</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5940,7 +5941,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738291</v>
+        <v>129738160</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,21 +6261,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6285,10 +6285,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407574</v>
+        <v>407512</v>
       </c>
       <c r="R54" t="n">
-        <v>6838848</v>
+        <v>6839214</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738160</v>
+        <v>129738168</v>
       </c>
       <c r="B55" t="n">
         <v>79706</v>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407512</v>
+        <v>407717</v>
       </c>
       <c r="R55" t="n">
-        <v>6839214</v>
+        <v>6839236</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738168</v>
+        <v>129739229</v>
       </c>
       <c r="B56" t="n">
         <v>79706</v>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407717</v>
+        <v>407296</v>
       </c>
       <c r="R56" t="n">
-        <v>6839236</v>
+        <v>6838974</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6529,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129739229</v>
+        <v>129738198</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,34 +6552,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407296</v>
+        <v>407575</v>
       </c>
       <c r="R57" t="n">
-        <v>6838974</v>
+        <v>6838839</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,66 +6634,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738255</v>
+        <v>129738291</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407645</v>
+        <v>407574</v>
       </c>
       <c r="R58" t="n">
-        <v>6838797</v>
+        <v>6838848</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6725,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6745,40 +6743,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129738198</v>
+        <v>129738255</v>
       </c>
       <c r="B59" t="n">
-        <v>57740</v>
+        <v>8451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6788,10 +6787,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407575</v>
+        <v>407645</v>
       </c>
       <c r="R59" t="n">
-        <v>6838839</v>
+        <v>6838797</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6832,6 +6831,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129738169</v>
+        <v>129739292</v>
       </c>
       <c r="B67" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7550,34 +7550,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407672</v>
+        <v>407632</v>
       </c>
       <c r="R67" t="n">
-        <v>6838825</v>
+        <v>6838901</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7618,25 +7621,26 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129739245</v>
+        <v>129738169</v>
       </c>
       <c r="B68" t="n">
         <v>79706</v>
@@ -7671,10 +7675,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407443</v>
+        <v>407672</v>
       </c>
       <c r="R68" t="n">
-        <v>6838872</v>
+        <v>6838825</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7721,19 +7725,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739225</v>
+        <v>129739245</v>
       </c>
       <c r="B69" t="n">
         <v>79706</v>
@@ -7768,10 +7772,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407184</v>
+        <v>407443</v>
       </c>
       <c r="R69" t="n">
-        <v>6839011</v>
+        <v>6838872</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7830,53 +7834,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129738257</v>
+        <v>129739225</v>
       </c>
       <c r="B70" t="n">
-        <v>58111</v>
+        <v>79706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407464</v>
+        <v>407184</v>
       </c>
       <c r="R70" t="n">
-        <v>6839159</v>
+        <v>6839011</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7923,22 +7919,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129739264</v>
+        <v>129738193</v>
       </c>
       <c r="B71" t="n">
-        <v>78845</v>
+        <v>79677</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,21 +7942,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7970,10 +7966,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407129</v>
+        <v>407714</v>
       </c>
       <c r="R71" t="n">
-        <v>6838913</v>
+        <v>6839244</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8020,22 +8016,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129738193</v>
+        <v>129739264</v>
       </c>
       <c r="B72" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8043,21 +8039,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8067,10 +8063,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407714</v>
+        <v>407129</v>
       </c>
       <c r="R72" t="n">
-        <v>6839244</v>
+        <v>6838913</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8117,22 +8113,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129739292</v>
+        <v>129738199</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8140,26 +8136,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8167,10 +8168,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407632</v>
+        <v>407576</v>
       </c>
       <c r="R73" t="n">
-        <v>6838901</v>
+        <v>6838847</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8211,46 +8212,45 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129738199</v>
+        <v>129738257</v>
       </c>
       <c r="B74" t="n">
-        <v>57740</v>
+        <v>58111</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8263,7 +8263,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407576</v>
+        <v>407464</v>
       </c>
       <c r="R74" t="n">
-        <v>6838847</v>
+        <v>6839159</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8529,10 +8529,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738147</v>
+        <v>129738194</v>
       </c>
       <c r="B77" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407190</v>
+        <v>407549</v>
       </c>
       <c r="R77" t="n">
-        <v>6838950</v>
+        <v>6838809</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738176</v>
+        <v>129738147</v>
       </c>
       <c r="B78" t="n">
         <v>79706</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407519</v>
+        <v>407190</v>
       </c>
       <c r="R78" t="n">
-        <v>6838831</v>
+        <v>6838950</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,7 +8723,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738171</v>
+        <v>129738176</v>
       </c>
       <c r="B79" t="n">
         <v>79706</v>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407620</v>
+        <v>407519</v>
       </c>
       <c r="R79" t="n">
-        <v>6838898</v>
+        <v>6838831</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,7 +8820,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738181</v>
+        <v>129738171</v>
       </c>
       <c r="B80" t="n">
         <v>79706</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407467</v>
+        <v>407620</v>
       </c>
       <c r="R80" t="n">
-        <v>6838834</v>
+        <v>6838898</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,54 +8917,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738244</v>
+        <v>129738181</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407231</v>
+        <v>407467</v>
       </c>
       <c r="R81" t="n">
-        <v>6838827</v>
+        <v>6838834</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9005,7 +8996,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9024,45 +9014,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129738194</v>
+        <v>129738244</v>
       </c>
       <c r="B82" t="n">
-        <v>79677</v>
+        <v>8451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407549</v>
+        <v>407231</v>
       </c>
       <c r="R82" t="n">
-        <v>6838809</v>
+        <v>6838827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,6 +9102,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129739258</v>
+        <v>129738188</v>
       </c>
       <c r="B90" t="n">
-        <v>57740</v>
+        <v>79706</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9819,42 +9819,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407616</v>
+        <v>407408</v>
       </c>
       <c r="R90" t="n">
-        <v>6838890</v>
+        <v>6838841</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9901,22 +9893,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739246</v>
+        <v>129739258</v>
       </c>
       <c r="B91" t="n">
-        <v>79706</v>
+        <v>57740</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9924,34 +9916,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407427</v>
+        <v>407616</v>
       </c>
       <c r="R91" t="n">
-        <v>6838886</v>
+        <v>6838890</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10010,10 +10010,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129739239</v>
+        <v>129739255</v>
       </c>
       <c r="B92" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,21 +10021,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10045,10 +10045,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407614</v>
+        <v>407411</v>
       </c>
       <c r="R92" t="n">
-        <v>6838900</v>
+        <v>6838819</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10107,45 +10107,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129738170</v>
+        <v>129738227</v>
       </c>
       <c r="B93" t="n">
-        <v>79706</v>
+        <v>5480</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407660</v>
+        <v>407545</v>
       </c>
       <c r="R93" t="n">
-        <v>6838791</v>
+        <v>6839241</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10186,6 +10195,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10204,7 +10214,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129738188</v>
+        <v>129739246</v>
       </c>
       <c r="B94" t="n">
         <v>79706</v>
@@ -10239,10 +10249,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407408</v>
+        <v>407427</v>
       </c>
       <c r="R94" t="n">
-        <v>6838841</v>
+        <v>6838886</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10289,66 +10299,57 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129738227</v>
+        <v>129739239</v>
       </c>
       <c r="B95" t="n">
-        <v>5480</v>
+        <v>79706</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407545</v>
+        <v>407614</v>
       </c>
       <c r="R95" t="n">
-        <v>6839241</v>
+        <v>6838900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10389,29 +10390,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129739255</v>
+        <v>129738170</v>
       </c>
       <c r="B96" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10419,21 +10419,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10443,10 +10443,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407411</v>
+        <v>407660</v>
       </c>
       <c r="R96" t="n">
-        <v>6838819</v>
+        <v>6838791</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10493,12 +10493,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -14945,10 +14945,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738201</v>
+        <v>129738286</v>
       </c>
       <c r="B142" t="n">
-        <v>57898</v>
+        <v>79087</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,42 +14956,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407530</v>
+        <v>407586</v>
       </c>
       <c r="R142" t="n">
-        <v>6839196</v>
+        <v>6838820</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15050,10 +15042,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129739253</v>
+        <v>129738284</v>
       </c>
       <c r="B143" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15061,37 +15053,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407589</v>
+        <v>407595</v>
       </c>
       <c r="R143" t="n">
-        <v>6838889</v>
+        <v>6838836</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15132,29 +15121,28 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129738195</v>
+        <v>129738150</v>
       </c>
       <c r="B144" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15162,21 +15150,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15186,10 +15174,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407479</v>
+        <v>407203</v>
       </c>
       <c r="R144" t="n">
-        <v>6838852</v>
+        <v>6839015</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15248,10 +15236,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129738286</v>
+        <v>129739253</v>
       </c>
       <c r="B145" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15259,34 +15247,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407586</v>
+        <v>407589</v>
       </c>
       <c r="R145" t="n">
-        <v>6838820</v>
+        <v>6838889</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15327,28 +15318,29 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129738284</v>
+        <v>129738195</v>
       </c>
       <c r="B146" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15356,21 +15348,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15380,10 +15372,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407595</v>
+        <v>407479</v>
       </c>
       <c r="R146" t="n">
-        <v>6838836</v>
+        <v>6838852</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15442,10 +15434,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129738150</v>
+        <v>129738201</v>
       </c>
       <c r="B147" t="n">
-        <v>79706</v>
+        <v>57898</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15453,34 +15445,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407203</v>
+        <v>407530</v>
       </c>
       <c r="R147" t="n">
-        <v>6839015</v>
+        <v>6839196</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129739256</v>
+        <v>129738278</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2490,42 +2490,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407082</v>
+        <v>407601</v>
       </c>
       <c r="R16" t="n">
-        <v>6838747</v>
+        <v>6838838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2572,22 +2564,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129738278</v>
+        <v>129739237</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,21 +2587,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2619,10 +2611,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407601</v>
+        <v>407617</v>
       </c>
       <c r="R17" t="n">
-        <v>6838838</v>
+        <v>6839035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2669,22 +2661,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129739237</v>
+        <v>129738187</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2716,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407617</v>
+        <v>407437</v>
       </c>
       <c r="R18" t="n">
-        <v>6839035</v>
+        <v>6838840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2766,22 +2758,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129738187</v>
+        <v>129738167</v>
       </c>
       <c r="B19" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2813,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407437</v>
+        <v>407714</v>
       </c>
       <c r="R19" t="n">
-        <v>6838840</v>
+        <v>6839244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2875,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129738167</v>
+        <v>129738159</v>
       </c>
       <c r="B20" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,10 +2902,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407714</v>
+        <v>407516</v>
       </c>
       <c r="R20" t="n">
-        <v>6839244</v>
+        <v>6839209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2972,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129738159</v>
+        <v>129738266</v>
       </c>
       <c r="B21" t="n">
-        <v>79706</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2983,34 +2975,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407516</v>
+        <v>407598</v>
       </c>
       <c r="R21" t="n">
-        <v>6839209</v>
+        <v>6838839</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129738266</v>
+        <v>129739257</v>
       </c>
       <c r="B22" t="n">
         <v>57740</v>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407598</v>
+        <v>407574</v>
       </c>
       <c r="R22" t="n">
-        <v>6838839</v>
+        <v>6839050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3162,19 +3162,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129739257</v>
+        <v>129739256</v>
       </c>
       <c r="B23" t="n">
         <v>57740</v>
@@ -3207,7 +3207,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407574</v>
+        <v>407082</v>
       </c>
       <c r="R23" t="n">
-        <v>6839050</v>
+        <v>6838747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3282,7 +3282,7 @@
         <v>129739265</v>
       </c>
       <c r="B24" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>129739266</v>
       </c>
       <c r="B26" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>129739291</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129739272</v>
+        <v>129738154</v>
       </c>
       <c r="B28" t="n">
-        <v>78844</v>
+        <v>79707</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407597</v>
+        <v>407536</v>
       </c>
       <c r="R28" t="n">
-        <v>6838888</v>
+        <v>6839138</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3762,22 +3762,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129738154</v>
+        <v>129739233</v>
       </c>
       <c r="B29" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407536</v>
+        <v>407429</v>
       </c>
       <c r="R29" t="n">
-        <v>6839138</v>
+        <v>6839067</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,22 +3859,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129739233</v>
+        <v>129739272</v>
       </c>
       <c r="B30" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407429</v>
+        <v>407597</v>
       </c>
       <c r="R30" t="n">
-        <v>6839067</v>
+        <v>6838888</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
         <v>129739227</v>
       </c>
       <c r="B31" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>129738155</v>
       </c>
       <c r="B32" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>129738179</v>
       </c>
       <c r="B33" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>129738197</v>
       </c>
       <c r="B34" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>129739248</v>
       </c>
       <c r="B35" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,10 +4453,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129738287</v>
+        <v>129738184</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4464,21 +4464,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407591</v>
+        <v>407445</v>
       </c>
       <c r="R36" t="n">
-        <v>6838814</v>
+        <v>6838844</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129738283</v>
+        <v>129738149</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4561,37 +4561,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407598</v>
+        <v>407199</v>
       </c>
       <c r="R37" t="n">
-        <v>6838839</v>
+        <v>6838976</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,18 +4623,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4656,10 +4647,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129739271</v>
+        <v>129738158</v>
       </c>
       <c r="B38" t="n">
-        <v>78844</v>
+        <v>79707</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,21 +4658,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4691,10 +4682,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407647</v>
+        <v>407519</v>
       </c>
       <c r="R38" t="n">
-        <v>6838874</v>
+        <v>6839207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4741,22 +4732,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129738184</v>
+        <v>129738287</v>
       </c>
       <c r="B39" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4764,21 +4755,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4788,10 +4779,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407445</v>
+        <v>407591</v>
       </c>
       <c r="R39" t="n">
-        <v>6838844</v>
+        <v>6838814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4850,10 +4841,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129738149</v>
+        <v>129738283</v>
       </c>
       <c r="B40" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,34 +4852,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407199</v>
+        <v>407598</v>
       </c>
       <c r="R40" t="n">
-        <v>6838976</v>
+        <v>6838839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4923,12 +4917,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129738158</v>
+        <v>129739271</v>
       </c>
       <c r="B41" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4958,21 +4958,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>407519</v>
+        <v>407647</v>
       </c>
       <c r="R41" t="n">
-        <v>6839207</v>
+        <v>6838874</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5032,12 +5032,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129739240</v>
+        <v>129738204</v>
       </c>
       <c r="B44" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,34 +5269,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407581</v>
+        <v>407170</v>
       </c>
       <c r="R44" t="n">
-        <v>6838885</v>
+        <v>6838942</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5343,22 +5351,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738186</v>
+        <v>129738292</v>
       </c>
       <c r="B45" t="n">
-        <v>79706</v>
+        <v>78754</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5374,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,10 +5398,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407479</v>
+        <v>407528</v>
       </c>
       <c r="R45" t="n">
-        <v>6838810</v>
+        <v>6839142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5452,10 +5460,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129738204</v>
+        <v>129739240</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5463,42 +5471,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407170</v>
+        <v>407581</v>
       </c>
       <c r="R46" t="n">
-        <v>6838942</v>
+        <v>6838885</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5545,22 +5545,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129739250</v>
+        <v>129738186</v>
       </c>
       <c r="B47" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5568,37 +5568,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407493</v>
+        <v>407479</v>
       </c>
       <c r="R47" t="n">
-        <v>6839112</v>
+        <v>6838810</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5639,73 +5636,63 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738247</v>
+        <v>129738290</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407158</v>
+        <v>407575</v>
       </c>
       <c r="R48" t="n">
-        <v>6838902</v>
+        <v>6838839</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5746,7 +5733,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5765,10 +5751,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129738292</v>
+        <v>129739250</v>
       </c>
       <c r="B49" t="n">
-        <v>78753</v>
+        <v>79678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5776,34 +5762,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>407528</v>
+        <v>407493</v>
       </c>
       <c r="R49" t="n">
-        <v>6839142</v>
+        <v>6839112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5844,63 +5833,73 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129738290</v>
+        <v>129738247</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>407575</v>
+        <v>407158</v>
       </c>
       <c r="R50" t="n">
-        <v>6838839</v>
+        <v>6838902</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,6 +5940,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>129738152</v>
       </c>
       <c r="B51" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>129739234</v>
       </c>
       <c r="B52" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>129738196</v>
       </c>
       <c r="B53" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>129738160</v>
       </c>
       <c r="B54" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,10 +6347,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738168</v>
+        <v>129738291</v>
       </c>
       <c r="B55" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6358,21 +6358,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407717</v>
+        <v>407574</v>
       </c>
       <c r="R55" t="n">
-        <v>6839236</v>
+        <v>6838848</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,10 +6444,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129739229</v>
+        <v>129738168</v>
       </c>
       <c r="B56" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407296</v>
+        <v>407717</v>
       </c>
       <c r="R56" t="n">
-        <v>6838974</v>
+        <v>6839236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6529,22 +6529,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129738198</v>
+        <v>129739229</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>79707</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6552,42 +6552,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407575</v>
+        <v>407296</v>
       </c>
       <c r="R57" t="n">
-        <v>6838839</v>
+        <v>6838974</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6634,22 +6626,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738291</v>
+        <v>129738198</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6657,34 +6649,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407574</v>
+        <v>407575</v>
       </c>
       <c r="R58" t="n">
-        <v>6838848</v>
+        <v>6838839</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
         <v>129739232</v>
       </c>
       <c r="B60" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>129739244</v>
       </c>
       <c r="B61" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,10 +7044,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129739228</v>
+        <v>129738289</v>
       </c>
       <c r="B62" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407244</v>
+        <v>407581</v>
       </c>
       <c r="R62" t="n">
-        <v>6839107</v>
+        <v>6838815</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7129,22 +7129,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129738189</v>
+        <v>129738277</v>
       </c>
       <c r="B63" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407407</v>
+        <v>407593</v>
       </c>
       <c r="R63" t="n">
-        <v>6838839</v>
+        <v>6838795</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7238,54 +7238,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129738243</v>
+        <v>129739228</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407117</v>
+        <v>407244</v>
       </c>
       <c r="R64" t="n">
-        <v>6838831</v>
+        <v>6839107</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,29 +7317,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129738289</v>
+        <v>129738189</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7356,21 +7346,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7380,10 +7370,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407581</v>
+        <v>407407</v>
       </c>
       <c r="R65" t="n">
-        <v>6838815</v>
+        <v>6838839</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7442,45 +7432,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129738277</v>
+        <v>129738243</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>407593</v>
+        <v>407117</v>
       </c>
       <c r="R66" t="n">
-        <v>6838795</v>
+        <v>6838831</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7521,6 +7520,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7539,37 +7539,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129739292</v>
+        <v>129738257</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>58111</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7577,10 +7582,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407632</v>
+        <v>407464</v>
       </c>
       <c r="R67" t="n">
-        <v>6838901</v>
+        <v>6839159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7621,29 +7626,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129738169</v>
+        <v>129739292</v>
       </c>
       <c r="B68" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7651,34 +7655,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407672</v>
+        <v>407632</v>
       </c>
       <c r="R68" t="n">
-        <v>6838825</v>
+        <v>6838901</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7719,28 +7726,29 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129739245</v>
+        <v>129738169</v>
       </c>
       <c r="B69" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7772,10 +7780,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407443</v>
+        <v>407672</v>
       </c>
       <c r="R69" t="n">
-        <v>6838872</v>
+        <v>6838825</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7822,22 +7830,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129739225</v>
+        <v>129739245</v>
       </c>
       <c r="B70" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7869,10 +7877,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407184</v>
+        <v>407443</v>
       </c>
       <c r="R70" t="n">
-        <v>6839011</v>
+        <v>6838872</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7931,10 +7939,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129738193</v>
+        <v>129739225</v>
       </c>
       <c r="B71" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7942,21 +7950,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7966,10 +7974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407714</v>
+        <v>407184</v>
       </c>
       <c r="R71" t="n">
-        <v>6839244</v>
+        <v>6839011</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8016,22 +8024,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129739264</v>
+        <v>129738199</v>
       </c>
       <c r="B72" t="n">
-        <v>78845</v>
+        <v>57740</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8039,34 +8047,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407129</v>
+        <v>407576</v>
       </c>
       <c r="R72" t="n">
-        <v>6838913</v>
+        <v>6838847</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8113,22 +8129,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129738199</v>
+        <v>129739264</v>
       </c>
       <c r="B73" t="n">
-        <v>57740</v>
+        <v>78846</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8136,42 +8152,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407576</v>
+        <v>407129</v>
       </c>
       <c r="R73" t="n">
-        <v>6838847</v>
+        <v>6838913</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8218,65 +8226,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129738257</v>
+        <v>129738193</v>
       </c>
       <c r="B74" t="n">
-        <v>58111</v>
+        <v>79678</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407464</v>
+        <v>407714</v>
       </c>
       <c r="R74" t="n">
-        <v>6839159</v>
+        <v>6839244</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8338,7 +8338,7 @@
         <v>129738275</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>129738285</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129738194</v>
+        <v>129738147</v>
       </c>
       <c r="B77" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407549</v>
+        <v>407190</v>
       </c>
       <c r="R77" t="n">
-        <v>6838809</v>
+        <v>6838950</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8626,10 +8626,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129738147</v>
+        <v>129738176</v>
       </c>
       <c r="B78" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407190</v>
+        <v>407519</v>
       </c>
       <c r="R78" t="n">
-        <v>6838950</v>
+        <v>6838831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129738176</v>
+        <v>129738171</v>
       </c>
       <c r="B79" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407519</v>
+        <v>407620</v>
       </c>
       <c r="R79" t="n">
-        <v>6838831</v>
+        <v>6838898</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129738171</v>
+        <v>129738181</v>
       </c>
       <c r="B80" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407620</v>
+        <v>407467</v>
       </c>
       <c r="R80" t="n">
-        <v>6838898</v>
+        <v>6838834</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,10 +8917,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129738181</v>
+        <v>129738194</v>
       </c>
       <c r="B81" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8928,21 +8928,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8952,10 +8952,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407467</v>
+        <v>407549</v>
       </c>
       <c r="R81" t="n">
-        <v>6838834</v>
+        <v>6838809</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129738165</v>
+        <v>129738174</v>
       </c>
       <c r="B83" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407691</v>
+        <v>407572</v>
       </c>
       <c r="R83" t="n">
-        <v>6839279</v>
+        <v>6838852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9218,10 +9218,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129739238</v>
+        <v>129738143</v>
       </c>
       <c r="B84" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407627</v>
+        <v>407137</v>
       </c>
       <c r="R84" t="n">
-        <v>6839039</v>
+        <v>6838823</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9303,22 +9303,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129738174</v>
+        <v>129738165</v>
       </c>
       <c r="B85" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>407572</v>
+        <v>407691</v>
       </c>
       <c r="R85" t="n">
-        <v>6838852</v>
+        <v>6839279</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9412,10 +9412,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129738143</v>
+        <v>129739238</v>
       </c>
       <c r="B86" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>407137</v>
+        <v>407627</v>
       </c>
       <c r="R86" t="n">
-        <v>6838823</v>
+        <v>6839039</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9497,12 +9497,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9512,7 +9512,7 @@
         <v>129738148</v>
       </c>
       <c r="B87" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>129739267</v>
       </c>
       <c r="B89" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129738188</v>
+        <v>129739255</v>
       </c>
       <c r="B90" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9819,21 +9819,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407408</v>
+        <v>407411</v>
       </c>
       <c r="R90" t="n">
-        <v>6838841</v>
+        <v>6838819</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9893,22 +9893,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129739258</v>
+        <v>129739239</v>
       </c>
       <c r="B91" t="n">
-        <v>57740</v>
+        <v>79707</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9916,42 +9916,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407616</v>
+        <v>407614</v>
       </c>
       <c r="R91" t="n">
-        <v>6838890</v>
+        <v>6838900</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10010,10 +10002,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129739255</v>
+        <v>129738170</v>
       </c>
       <c r="B92" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,21 +10013,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10045,10 +10037,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407411</v>
+        <v>407660</v>
       </c>
       <c r="R92" t="n">
-        <v>6838819</v>
+        <v>6838791</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10095,66 +10087,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129738227</v>
+        <v>129738188</v>
       </c>
       <c r="B93" t="n">
-        <v>5480</v>
+        <v>79707</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407545</v>
+        <v>407408</v>
       </c>
       <c r="R93" t="n">
-        <v>6839241</v>
+        <v>6838841</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10195,7 +10178,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10217,7 +10199,7 @@
         <v>129739246</v>
       </c>
       <c r="B94" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10311,10 +10293,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129739239</v>
+        <v>129739258</v>
       </c>
       <c r="B95" t="n">
-        <v>79706</v>
+        <v>57740</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10322,34 +10304,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407614</v>
+        <v>407616</v>
       </c>
       <c r="R95" t="n">
-        <v>6838900</v>
+        <v>6838890</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10408,45 +10398,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129738170</v>
+        <v>129738227</v>
       </c>
       <c r="B96" t="n">
-        <v>79706</v>
+        <v>5480</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407660</v>
+        <v>407545</v>
       </c>
       <c r="R96" t="n">
-        <v>6838791</v>
+        <v>6839241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10487,6 +10486,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10505,45 +10505,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129739252</v>
+        <v>129738250</v>
       </c>
       <c r="B97" t="n">
-        <v>79677</v>
+        <v>8451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407615</v>
+        <v>407525</v>
       </c>
       <c r="R97" t="n">
-        <v>6839041</v>
+        <v>6839244</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10584,28 +10593,29 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129738191</v>
+        <v>129738144</v>
       </c>
       <c r="B98" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10613,21 +10623,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10637,10 +10647,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407474</v>
+        <v>407223</v>
       </c>
       <c r="R98" t="n">
-        <v>6839108</v>
+        <v>6838821</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10699,10 +10709,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129739251</v>
+        <v>129738185</v>
       </c>
       <c r="B99" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10710,21 +10720,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10734,10 +10744,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407563</v>
+        <v>407439</v>
       </c>
       <c r="R99" t="n">
-        <v>6839056</v>
+        <v>6838837</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10784,66 +10794,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129738250</v>
+        <v>129739289</v>
       </c>
       <c r="B100" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407525</v>
+        <v>407649</v>
       </c>
       <c r="R100" t="n">
-        <v>6839244</v>
+        <v>6839041</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10884,29 +10885,28 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129739289</v>
+        <v>129738172</v>
       </c>
       <c r="B101" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10914,21 +10914,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407649</v>
+        <v>407585</v>
       </c>
       <c r="R101" t="n">
-        <v>6839041</v>
+        <v>6838872</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10988,22 +10988,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129738144</v>
+        <v>129739242</v>
       </c>
       <c r="B102" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11035,10 +11035,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407223</v>
+        <v>407515</v>
       </c>
       <c r="R102" t="n">
-        <v>6838821</v>
+        <v>6838875</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11085,22 +11085,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129738185</v>
+        <v>129739252</v>
       </c>
       <c r="B103" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11108,21 +11108,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11132,10 +11132,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407439</v>
+        <v>407615</v>
       </c>
       <c r="R103" t="n">
-        <v>6838837</v>
+        <v>6839041</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11182,22 +11182,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129738172</v>
+        <v>129738191</v>
       </c>
       <c r="B104" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11205,21 +11205,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407585</v>
+        <v>407474</v>
       </c>
       <c r="R104" t="n">
-        <v>6838872</v>
+        <v>6839108</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11291,10 +11291,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129739242</v>
+        <v>129739251</v>
       </c>
       <c r="B105" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11302,21 +11302,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11326,10 +11326,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407515</v>
+        <v>407563</v>
       </c>
       <c r="R105" t="n">
-        <v>6838875</v>
+        <v>6839056</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11391,7 +11391,7 @@
         <v>129739273</v>
       </c>
       <c r="B106" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>129738173</v>
       </c>
       <c r="B107" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>129738182</v>
       </c>
       <c r="B108" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11679,10 +11679,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129738276</v>
+        <v>129738180</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11690,21 +11690,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407607</v>
+        <v>407480</v>
       </c>
       <c r="R109" t="n">
-        <v>6838798</v>
+        <v>6838840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11776,10 +11776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129738180</v>
+        <v>129738276</v>
       </c>
       <c r="B110" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407480</v>
+        <v>407607</v>
       </c>
       <c r="R110" t="n">
-        <v>6838840</v>
+        <v>6838798</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11876,7 +11876,7 @@
         <v>129738190</v>
       </c>
       <c r="B111" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>129738175</v>
       </c>
       <c r="B112" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12067,40 +12067,41 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129738268</v>
+        <v>129738249</v>
       </c>
       <c r="B113" t="n">
-        <v>57740</v>
+        <v>8451</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12110,10 +12111,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>407593</v>
+        <v>407512</v>
       </c>
       <c r="R113" t="n">
-        <v>6838811</v>
+        <v>6839241</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12154,6 +12155,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12172,41 +12174,40 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129738249</v>
+        <v>129738268</v>
       </c>
       <c r="B114" t="n">
-        <v>8451</v>
+        <v>57740</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12216,10 +12217,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>407512</v>
+        <v>407593</v>
       </c>
       <c r="R114" t="n">
-        <v>6839241</v>
+        <v>6838811</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12260,7 +12261,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129738280</v>
+        <v>129738192</v>
       </c>
       <c r="B115" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12290,37 +12290,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407623</v>
+        <v>407464</v>
       </c>
       <c r="R115" t="n">
-        <v>6838894</v>
+        <v>6839157</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12355,18 +12352,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12385,10 +12376,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129739290</v>
+        <v>129739243</v>
       </c>
       <c r="B116" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12396,37 +12387,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407657</v>
+        <v>407451</v>
       </c>
       <c r="R116" t="n">
-        <v>6839033</v>
+        <v>6838866</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12461,18 +12449,12 @@
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12491,10 +12473,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129738282</v>
+        <v>129738280</v>
       </c>
       <c r="B117" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12520,16 +12502,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407588</v>
+        <v>407623</v>
       </c>
       <c r="R117" t="n">
-        <v>6838831</v>
+        <v>6838894</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12575,6 +12560,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12593,10 +12579,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129739243</v>
+        <v>129739224</v>
       </c>
       <c r="B118" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12628,10 +12614,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407451</v>
+        <v>407121</v>
       </c>
       <c r="R118" t="n">
-        <v>6838866</v>
+        <v>6838895</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12690,10 +12676,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129739224</v>
+        <v>129739290</v>
       </c>
       <c r="B119" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12701,34 +12687,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407121</v>
+        <v>407657</v>
       </c>
       <c r="R119" t="n">
-        <v>6838895</v>
+        <v>6839033</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12763,12 +12752,18 @@
           <t>2025-11-17</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12787,10 +12782,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129738145</v>
+        <v>129738282</v>
       </c>
       <c r="B120" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12798,21 +12793,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12822,10 +12817,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407194</v>
+        <v>407588</v>
       </c>
       <c r="R120" t="n">
-        <v>6838873</v>
+        <v>6838831</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12858,6 +12853,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12884,10 +12884,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129738192</v>
+        <v>129738145</v>
       </c>
       <c r="B121" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12895,21 +12895,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12919,10 +12919,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407464</v>
+        <v>407194</v>
       </c>
       <c r="R121" t="n">
-        <v>6839157</v>
+        <v>6838873</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12981,10 +12981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129739286</v>
+        <v>129739249</v>
       </c>
       <c r="B122" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407570</v>
+        <v>407437</v>
       </c>
       <c r="R122" t="n">
-        <v>6839041</v>
+        <v>6839060</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13078,10 +13078,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129738279</v>
+        <v>129739286</v>
       </c>
       <c r="B123" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407617</v>
+        <v>407570</v>
       </c>
       <c r="R123" t="n">
-        <v>6838855</v>
+        <v>6839041</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13163,22 +13163,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129738288</v>
+        <v>129738279</v>
       </c>
       <c r="B124" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407592</v>
+        <v>407617</v>
       </c>
       <c r="R124" t="n">
-        <v>6838822</v>
+        <v>6838855</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13272,10 +13272,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129738146</v>
+        <v>129738288</v>
       </c>
       <c r="B125" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13283,21 +13283,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407163</v>
+        <v>407592</v>
       </c>
       <c r="R125" t="n">
-        <v>6838891</v>
+        <v>6838822</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,10 +13369,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129739241</v>
+        <v>129738146</v>
       </c>
       <c r="B126" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407524</v>
+        <v>407163</v>
       </c>
       <c r="R126" t="n">
-        <v>6838914</v>
+        <v>6838891</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13454,22 +13454,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129739249</v>
+        <v>129739241</v>
       </c>
       <c r="B127" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13477,21 +13477,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>407437</v>
+        <v>407524</v>
       </c>
       <c r="R127" t="n">
-        <v>6839060</v>
+        <v>6838914</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13563,10 +13563,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129739287</v>
+        <v>129738157</v>
       </c>
       <c r="B128" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13574,21 +13574,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13598,10 +13598,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>407622</v>
+        <v>407535</v>
       </c>
       <c r="R128" t="n">
-        <v>6839045</v>
+        <v>6839193</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13648,22 +13648,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129738281</v>
+        <v>129739287</v>
       </c>
       <c r="B129" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13695,10 +13695,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>407587</v>
+        <v>407622</v>
       </c>
       <c r="R129" t="n">
-        <v>6838872</v>
+        <v>6839045</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13745,22 +13745,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129738157</v>
+        <v>129738281</v>
       </c>
       <c r="B130" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,21 +13768,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13792,10 +13792,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>407535</v>
+        <v>407587</v>
       </c>
       <c r="R130" t="n">
-        <v>6839193</v>
+        <v>6838872</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13857,7 +13857,7 @@
         <v>129738177</v>
       </c>
       <c r="B131" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>129738156</v>
       </c>
       <c r="B132" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>129739230</v>
       </c>
       <c r="B133" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>129738151</v>
       </c>
       <c r="B134" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>129739235</v>
       </c>
       <c r="B135" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>129739231</v>
       </c>
       <c r="B136" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>129738242</v>
       </c>
       <c r="B137" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>129739254</v>
       </c>
       <c r="B138" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>129739268</v>
       </c>
       <c r="B139" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14945,10 +14945,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129738286</v>
+        <v>129739253</v>
       </c>
       <c r="B142" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14956,34 +14956,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407586</v>
+        <v>407589</v>
       </c>
       <c r="R142" t="n">
-        <v>6838820</v>
+        <v>6838889</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15024,28 +15027,29 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129738284</v>
+        <v>129738195</v>
       </c>
       <c r="B143" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15053,21 +15057,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15077,10 +15081,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407595</v>
+        <v>407479</v>
       </c>
       <c r="R143" t="n">
-        <v>6838836</v>
+        <v>6838852</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15142,7 +15146,7 @@
         <v>129738150</v>
       </c>
       <c r="B144" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15236,10 +15240,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129739253</v>
+        <v>129738286</v>
       </c>
       <c r="B145" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15247,37 +15251,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407589</v>
+        <v>407586</v>
       </c>
       <c r="R145" t="n">
-        <v>6838889</v>
+        <v>6838820</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15318,29 +15319,28 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129738195</v>
+        <v>129738284</v>
       </c>
       <c r="B146" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15348,21 +15348,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15372,10 +15372,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407479</v>
+        <v>407595</v>
       </c>
       <c r="R146" t="n">
-        <v>6838852</v>
+        <v>6838836</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129738274</v>
+        <v>129739247</v>
       </c>
       <c r="B148" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15550,21 +15550,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407522</v>
+        <v>407319</v>
       </c>
       <c r="R148" t="n">
-        <v>6839200</v>
+        <v>6838979</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15624,22 +15624,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129739288</v>
+        <v>129738164</v>
       </c>
       <c r="B149" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407625</v>
+        <v>407666</v>
       </c>
       <c r="R149" t="n">
-        <v>6839051</v>
+        <v>6839269</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15721,22 +15721,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129738164</v>
+        <v>129738153</v>
       </c>
       <c r="B150" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407666</v>
+        <v>407474</v>
       </c>
       <c r="R150" t="n">
-        <v>6839269</v>
+        <v>6839108</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129738153</v>
+        <v>129738166</v>
       </c>
       <c r="B151" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407474</v>
+        <v>407704</v>
       </c>
       <c r="R151" t="n">
-        <v>6839108</v>
+        <v>6839251</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15927,10 +15927,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129738166</v>
+        <v>129738274</v>
       </c>
       <c r="B152" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15938,21 +15938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407704</v>
+        <v>407522</v>
       </c>
       <c r="R152" t="n">
-        <v>6839251</v>
+        <v>6839200</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16024,10 +16024,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129739247</v>
+        <v>129739288</v>
       </c>
       <c r="B153" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>407319</v>
+        <v>407625</v>
       </c>
       <c r="R153" t="n">
-        <v>6838979</v>
+        <v>6839051</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>

--- a/artfynd/A 53732-2025 artfynd.xlsx
+++ b/artfynd/A 53732-2025 artfynd.xlsx
@@ -5258,10 +5258,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129738204</v>
+        <v>129738292</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>78754</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,42 +5269,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>407170</v>
+        <v>407528</v>
       </c>
       <c r="R44" t="n">
-        <v>6838942</v>
+        <v>6839142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129738292</v>
+        <v>129739240</v>
       </c>
       <c r="B45" t="n">
-        <v>78754</v>
+        <v>79707</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5374,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5398,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>407528</v>
+        <v>407581</v>
       </c>
       <c r="R45" t="n">
-        <v>6839142</v>
+        <v>6838885</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5448,19 +5440,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129739240</v>
+        <v>129738186</v>
       </c>
       <c r="B46" t="n">
         <v>79707</v>
@@ -5495,10 +5487,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>407581</v>
+        <v>407479</v>
       </c>
       <c r="R46" t="n">
-        <v>6838885</v>
+        <v>6838810</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5545,22 +5537,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129738186</v>
+        <v>129738290</v>
       </c>
       <c r="B47" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5568,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5592,10 +5584,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>407479</v>
+        <v>407575</v>
       </c>
       <c r="R47" t="n">
-        <v>6838810</v>
+        <v>6838839</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5654,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129738290</v>
+        <v>129738204</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5665,34 +5657,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>407575</v>
+        <v>407170</v>
       </c>
       <c r="R48" t="n">
-        <v>6838839</v>
+        <v>6838942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6250,10 +6250,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129738160</v>
+        <v>129738198</v>
       </c>
       <c r="B54" t="n">
-        <v>79707</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6261,34 +6261,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407512</v>
+        <v>407575</v>
       </c>
       <c r="R54" t="n">
-        <v>6839214</v>
+        <v>6838839</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129738291</v>
+        <v>129738160</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6358,21 +6366,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6382,10 +6390,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407574</v>
+        <v>407512</v>
       </c>
       <c r="R55" t="n">
-        <v>6838848</v>
+        <v>6839214</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,10 +6452,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129738168</v>
+        <v>129738291</v>
       </c>
       <c r="B56" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6455,21 +6463,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6479,10 +6487,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407717</v>
+        <v>407574</v>
       </c>
       <c r="R56" t="n">
-        <v>6839236</v>
+        <v>6838848</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6541,7 +6549,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129739229</v>
+        <v>129738168</v>
       </c>
       <c r="B57" t="n">
         <v>79707</v>
@@ -6576,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407296</v>
+        <v>407717</v>
       </c>
       <c r="R57" t="n">
-        <v>6838974</v>
+        <v>6839236</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,22 +6634,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129738198</v>
+        <v>129739229</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>79707</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6649,42 +6657,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fjätfallen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407575</v>
+        <v>407296</v>
       </c>
       <c r="R58" t="n">
-        <v>6838839</v>
+        <v>6838974</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6731,12 +6731,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7539,27 +7539,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129738257</v>
+        <v>129738199</v>
       </c>
       <c r="B67" t="n">
-        <v>58111</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
